--- a/workspaces/nasdaq_hourly_24hrs/vix/vix_level.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/vix/vix_level.xlsx
@@ -625,76 +625,76 @@
         <v>55</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>8.099220320979093</v>
+        <v>8.118985889402509</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4.127242962039389</v>
+        <v>4.176325461607028</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.890727562897375</v>
+        <v>0.9418833870032515</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1816679338981118</v>
+        <v>0.2338765673418735</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>5.242512023812033</v>
+        <v>5.32419554342313</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.85522007531283</v>
+        <v>10.93672575938405</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>6.47181114703249</v>
+        <v>6.554443592988356</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8.00579483673237</v>
+        <v>8.088888233468808</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.04986686552656</v>
+        <v>8.132945600243076</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.471126209688919</v>
+        <v>5.555355055153832</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>3.935225661407493</v>
+        <v>4.019095304737093</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>3.658508634814694</v>
+        <v>3.742829195184918</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>2.538715060655299</v>
+        <v>2.624710053119152</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>5.94426570019521</v>
+        <v>6.03064759146865</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>5.288818646974704</v>
+        <v>5.376203987915851</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>5.884058631104331</v>
+        <v>5.970631579876041</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>9.380360115284688</v>
+        <v>9.467189462768076</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>9.278326181742322</v>
+        <v>9.365356023148337</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>9.497086037346698</v>
+        <v>9.583849369512258</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>9.686748673818308</v>
+        <v>9.773287815315783</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>7.330367000811485</v>
+        <v>7.417742250470148</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>9.07370751816493</v>
+        <v>9.161244429920195</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>9.351262687369463</v>
+        <v>9.438446975876957</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>7.45991650934657</v>
+        <v>7.547259983007642</v>
       </c>
     </row>
     <row r="7">
@@ -707,76 +707,76 @@
         <v>81</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-3.02451686225502</v>
+        <v>-3.004872418746388</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.160919336616729</v>
+        <v>-2.111913367955268</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-4.818638573768347</v>
+        <v>-4.767553175901519</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-10.43697855735134</v>
+        <v>-10.38488508576628</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-8.348470933437525</v>
+        <v>-8.266927653967414</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-10.62073035062024</v>
+        <v>-10.53942181440552</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-17.53281731180827</v>
+        <v>-17.45039498410729</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-15.35877332599755</v>
+        <v>-15.2758719320075</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-14.0930009480445</v>
+        <v>-14.0100934730133</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-11.18010471344692</v>
+        <v>-11.09600038089959</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-8.45079525692438</v>
+        <v>-8.367015303802511</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-7.501274878231662</v>
+        <v>-7.417030291516724</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-6.163606390525374</v>
+        <v>-6.077668792321397</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-5.155495588136041</v>
+        <v>-5.069176197164325</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-5.814232238479839</v>
+        <v>-5.726903552003293</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-6.453940458379023</v>
+        <v>-6.367422358862306</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-6.590179365598232</v>
+        <v>-6.503409309334089</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-6.697048511798108</v>
+        <v>-6.610069551324344</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-7.715793734578234</v>
+        <v>-7.629075759552869</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-8.764405926960471</v>
+        <v>-8.677905418287935</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-9.309820752862898</v>
+        <v>-9.222472185563959</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-10.62245841589598</v>
+        <v>-10.53494211531775</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-11.58510081408003</v>
+        <v>-11.49792742501896</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-9.195526812764108</v>
+        <v>-9.108183339102062</v>
       </c>
     </row>
     <row r="8">
@@ -786,79 +786,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.03158819242047173</v>
+        <v>-1.334362166550619</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3.489205659627061</v>
+        <v>2.326985878730412</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2.060861843603746</v>
+        <v>0.9003134808636446</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.463596958477439</v>
+        <v>1.335612153244952</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3.211627137679272</v>
+        <v>2.144590732681849</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.6217300840790401</v>
+        <v>0.04558677241995923</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.256435550715516</v>
+        <v>-2.435116735896123</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.757554592194417</v>
+        <v>-5.000109235046068</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-7.608727164763962</v>
+        <v>-8.391709393887957</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-10.60619638125245</v>
+        <v>-10.88016331309858</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-10.89279238745588</v>
+        <v>-11.18319736479584</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-11.73073707458052</v>
+        <v>-12.03679667828891</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-11.18531769956252</v>
+        <v>-11.44181469049161</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-10.29615057996219</v>
+        <v>-10.52035953871966</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-9.842529239849512</v>
+        <v>-10.03380079569763</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-12.03822218387761</v>
+        <v>-11.7372519424454</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-14.96334332635989</v>
+        <v>-14.16874816248465</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-14.5155684248564</v>
+        <v>-13.70449169422183</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-15.97760055798539</v>
+        <v>-14.64084928845116</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-18.58570548182622</v>
+        <v>-17.3289164631498</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-18.01831501439479</v>
+        <v>-16.72819792985428</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-16.98366284475601</v>
+        <v>-15.66087624988511</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-16.71449063361237</v>
+        <v>-15.39162469049521</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-18.47202864047595</v>
+        <v>-17.19673165753572</v>
       </c>
     </row>
     <row r="9">
@@ -868,79 +868,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.595922879640632</v>
+        <v>2.408325880771734</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.817173509873285</v>
+        <v>-2.885097662044679</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.719995488334398</v>
+        <v>-1.830642844080565</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-3.067333060883172</v>
+        <v>-2.183107085422897</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-1.264713293833083</v>
+        <v>-0.3895029226201672</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.7280108565363861</v>
+        <v>1.215989176749034</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.3237722580963975</v>
+        <v>1.16173561034924</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.7700437419960124</v>
+        <v>1.595802505933442</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.9954458781647233</v>
+        <v>-0.4925702904328801</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.04366621914134328</v>
+        <v>0.1600456490106552</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.04536793476717094</v>
+        <v>0.07714919261919562</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.3231753441243654</v>
+        <v>-0.2001879541759237</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.979245947070339</v>
+        <v>-3.809314742065851</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.651154852029691</v>
+        <v>-5.454939278298639</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-3.773112128739285</v>
+        <v>-3.621135828467565</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-6.806852014442121</v>
+        <v>-6.947125249877544</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-8.39433960429588</v>
+        <v>-8.864844462810098</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-9.228293461135671</v>
+        <v>-9.685799901340204</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-9.741791160536472</v>
+        <v>-10.54331327008823</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-8.469369733691408</v>
+        <v>-9.290830571524644</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-7.92577614909932</v>
+        <v>-8.766130015467688</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-11.63880626268347</v>
+        <v>-12.41439726139946</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-12.82264997263384</v>
+        <v>-13.57288395195075</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-14.72190167247201</v>
+        <v>-15.43975300400542</v>
       </c>
     </row>
     <row r="10">
@@ -953,76 +953,76 @@
         <v>349</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.4843522488680136</v>
+        <v>0.5039652834386104</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>2.965877864106638</v>
+        <v>3.014759061415283</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.256229774992939</v>
+        <v>1.307181384181916</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.291083025844834</v>
+        <v>-2.239134083496758</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-2.087861754880379</v>
+        <v>-2.006569275456684</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.334618577982397</v>
+        <v>-1.25351512953894</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.1767533961503602</v>
+        <v>0.2590452963393162</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.9540487328248162</v>
+        <v>-0.8713043282816315</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.5133629053482878</v>
+        <v>0.5961226681516365</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.5407495448485236</v>
+        <v>-0.4568194108648029</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.408278803483746</v>
+        <v>-1.324686091046701</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.82674846064706</v>
+        <v>-2.742699725400215</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-2.234915671635186</v>
+        <v>-2.149168581351965</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.312567997863461</v>
+        <v>-3.226438015467345</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-4.828080002408605</v>
+        <v>-4.740930038699908</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-1.951335483810581</v>
+        <v>-1.86495844760352</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-1.229063263879958</v>
+        <v>-1.142414993800891</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-1.906656751974985</v>
+        <v>-1.819786037083261</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-1.406037731040854</v>
+        <v>-1.319406812809611</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-2.078881818106439</v>
+        <v>-1.992451313145025</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-1.192330903851534</v>
+        <v>-1.10503223597145</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-1.555693307053218</v>
+        <v>-1.468210692544602</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-3.287385204385757</v>
+        <v>-3.200229936454868</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-3.07928640808025</v>
+        <v>-2.991942934418766</v>
       </c>
     </row>
     <row r="11">
@@ -1032,79 +1032,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.613744869649359</v>
+        <v>1.525973806055013</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.4319928924202188</v>
+        <v>0.1022483323231356</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.655633060661678</v>
+        <v>-2.702496806893322</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.024543119689895</v>
+        <v>-2.058336631950517</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.208496412841022</v>
+        <v>-3.486335887777706</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-4.925450103903827</v>
+        <v>-5.20954760140441</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-5.167940357443655</v>
+        <v>-5.443034347780603</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-4.908955158933054</v>
+        <v>-4.906835876288206</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.963873771536377</v>
+        <v>-2.956612711688116</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.224976863947042</v>
+        <v>-2.370497062842297</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.515596736224616</v>
+        <v>-1.823595667370618</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.5452638540801189</v>
+        <v>-1.013655186286698</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.1275933907448206</v>
+        <v>-0.5063403466608278</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.45993118418717</v>
+        <v>-2.101999427997882</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-1.303162150971879</v>
+        <v>-1.77391496833058</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-1.527724926848684</v>
+        <v>-1.829587074626289</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-2.484167184374257</v>
+        <v>-2.616456184074003</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-2.318874867544842</v>
+        <v>-2.277388007721328</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-2.378493272675264</v>
+        <v>-2.337833873665552</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-2.841955199480083</v>
+        <v>-2.976121002516741</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-1.74662643285064</v>
+        <v>-1.874746037298173</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-1.278047145545969</v>
+        <v>-1.403407995364837</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.6378105995202787</v>
+        <v>0.5166406867025017</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>1.831024853057187</v>
+        <v>1.538268974016702</v>
       </c>
     </row>
     <row r="12">
@@ -1114,79 +1114,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.447776695378323</v>
+        <v>-2.265318917197781</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.3857524612040066</v>
+        <v>0.8495548746655359</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.234240962944149</v>
+        <v>3.14998188692519</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.271972682293885</v>
+        <v>3.987153773511409</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.616845538178367</v>
+        <v>2.704283133268206</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.312302142821942</v>
+        <v>3.209677007047226</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>5.920003999645225</v>
+        <v>5.570575189953885</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>4.993274903697554</v>
+        <v>4.524390355668096</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>5.037233457894338</v>
+        <v>4.751093968337443</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>4.56891551495881</v>
+        <v>4.28341742234646</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>6.135728297835229</v>
+        <v>6.009757675490391</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>5.52510130667882</v>
+        <v>5.59908617579876</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.663530184867483</v>
+        <v>5.730664803373237</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.984121253239415</v>
+        <v>4.873546514922495</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>5.161395912032418</v>
+        <v>4.841946664991632</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>4.353116255414044</v>
+        <v>3.860931317827479</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>4.861094192544599</v>
+        <v>4.356195359744717</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>4.755040970151093</v>
+        <v>4.249847380926411</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>4.326653237582839</v>
+        <v>4.032355502860163</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>3.546004659022188</v>
+        <v>3.470101723489002</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>3.204211410614185</v>
+        <v>3.12679792367264</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>2.040778108077944</v>
+        <v>1.786944864664598</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>1.876061120543227</v>
+        <v>1.427794327599479</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>3.412995688231788</v>
+        <v>2.932760558381496</v>
       </c>
     </row>
     <row r="13">
@@ -1199,76 +1199,76 @@
         <v>251</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.860719324871013</v>
+        <v>2.868491228952685</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.9061252340627277</v>
+        <v>0.9497370003769205</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.027357073038281</v>
+        <v>1.07555265762872</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.485204864729447</v>
+        <v>1.535805209802561</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.920087498705726</v>
+        <v>4.771136062375284</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.7331645398395708</v>
+        <v>0.5901529864984454</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.435673121503967</v>
+        <v>-2.581067169900543</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.887314808200102</v>
+        <v>-3.26551690433665</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.614418882910407</v>
+        <v>-3.223192909588185</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.993341135173743</v>
+        <v>-3.378731927541601</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.115413657613722</v>
+        <v>-3.497064751991665</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-3.794281798230209</v>
+        <v>-4.180987909765669</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-4.525022755957586</v>
+        <v>-4.680260341170573</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-5.544916209179682</v>
+        <v>-5.458293373667786</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-7.001602869090725</v>
+        <v>-6.913994812072573</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-6.405465390415756</v>
+        <v>-6.318698981063996</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-4.954174961882551</v>
+        <v>-4.861892896876633</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-5.862275476787069</v>
+        <v>-5.76307986276796</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-4.599359571061505</v>
+        <v>-4.751751128839118</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-4.013859839636531</v>
+        <v>-4.167489612057295</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-4.158817680767292</v>
+        <v>-4.31292304289812</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-5.430019180803683</v>
+        <v>-5.590773009927709</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-5.553575172992097</v>
+        <v>-5.721797997555377</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-7.223169329118072</v>
+        <v>-7.135825855456588</v>
       </c>
     </row>
     <row r="14">
@@ -1278,79 +1278,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>5.300021515017427</v>
+        <v>5.461101070739794</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.633466246543129</v>
+        <v>2.791909137140344</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.39930185391956</v>
+        <v>4.619768897802224</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.827713076137812</v>
+        <v>2.026453703668736</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.002123031112653</v>
+        <v>1.224195970341533</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.184995719225924</v>
+        <v>1.877140698411914</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.06133417104810235</v>
+        <v>0.1544321586049122</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.035691221263228</v>
+        <v>1.277720786517619</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.538664231711927</v>
+        <v>1.789323412103684</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.089263305089588</v>
+        <v>-0.8722684213708192</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.270696697909813</v>
+        <v>-1.062637342513383</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.207037133918014</v>
+        <v>1.467300279737003</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.06732766107293742</v>
+        <v>0.328973198568896</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.7551556815177705</v>
+        <v>1.03422394634589</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>1.009002954927432</v>
+        <v>1.306201526566909</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.6961945721814615</v>
+        <v>-0.4430381382876476</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.8450160255143118</v>
+        <v>0.8308635533638764</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>1.494702142688951</v>
+        <v>1.191715164039834</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.514923123304143</v>
+        <v>-1.878778431561663</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-1.78865925946873</v>
+        <v>-2.162679940861501</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-3.253682461276583</v>
+        <v>-3.646720747363055</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-1.025517372369414</v>
+        <v>-1.077110808082736</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.6318214892068355</v>
+        <v>0.4442616771186181</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>2.399170803439162</v>
+        <v>2.246363696195864</v>
       </c>
     </row>
     <row r="15">
@@ -1360,161 +1360,161 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.61901100849655</v>
+        <v>-2.630544292631775</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-7.670826068003478</v>
+        <v>-8.058643787251718</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-9.110949612403047</v>
+        <v>-9.518722318461087</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-8.783288504410137</v>
+        <v>-8.946556053209243</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-7.586169284467658</v>
+        <v>-7.47003289457539</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-8.440621666181691</v>
+        <v>-8.818152692585706</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-8.692884167636784</v>
+        <v>-8.577982195493718</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-7.409024745269285</v>
+        <v>-7.325581395348834</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-6.325834789361295</v>
+        <v>-6.263686050168822</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.974900475774341</v>
+        <v>-3.975377236409393</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.5754662004662023</v>
+        <v>-0.6400931044515588</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.1870203050616865</v>
+        <v>0.1015656553657536</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.4169703595723959</v>
+        <v>-0.5113923298577063</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.1175634295712982</v>
+        <v>-0.2222671246716459</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.2649747180085527</v>
+        <v>0.1399977410131044</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>1.901869954284543</v>
+        <v>1.754792826221397</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>2.288565382370116</v>
+        <v>2.131079770876575</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>3.225212895377183</v>
+        <v>3.046647230320701</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>4.483060747663608</v>
+        <v>4.282946774510386</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>4.14932077125335</v>
+        <v>3.959588502845826</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>3.605956555620494</v>
+        <v>3.417042334879682</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>4.571640845756612</v>
+        <v>4.361604536735889</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>3.283991228070178</v>
+        <v>3.615671085952634</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>4.249689236618892</v>
+        <v>4.560246995994667</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 19.55</t>
+          <t>X ≈ 19.54</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>168</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.2023000656557272</v>
+        <v>-0.09258814348625322</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.498816789139404</v>
+        <v>5.200871361652375</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>8.22535991140635</v>
+        <v>8.215485570822686</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>8.106592447970648</v>
+        <v>8.070135566059193</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4.169783096484593</v>
+        <v>3.572099879734736</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4.952235476675398</v>
+        <v>4.688908703200866</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>5.369615832363216</v>
+        <v>5.452630049404242</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.11478477854024</v>
+        <v>2.198228128460691</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.942022353495851</v>
+        <v>4.02542959608968</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.167956667082805</v>
+        <v>3.25251392005319</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.061438561438564</v>
+        <v>1.145621181262733</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.00345588541451</v>
+        <v>-0.918842507899555</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>4.41933916423713</v>
+        <v>4.505614472863378</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4.793150856143065</v>
+        <v>4.879773691654961</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>3.538784241818007</v>
+        <v>3.626392298836159</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>4.729250906665477</v>
+        <v>4.816017316017238</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>3.999874906179571</v>
+        <v>4.086862083801677</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>5.08533194299617</v>
+        <v>5.172497570456756</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>3.515798842901575</v>
+        <v>3.602674665666726</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>1.917177914110368</v>
+        <v>2.003806189920475</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>3.754766079430084</v>
+        <v>3.842212402906952</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>4.86925989337572</v>
+        <v>4.956842631974048</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>5.144110275689165</v>
+        <v>5.231317344455974</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>3.877665427095081</v>
+        <v>3.965008900756565</v>
       </c>
     </row>
     <row r="17">
@@ -1524,571 +1524,571 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-4.70961345452924</v>
+        <v>-5.413896758822077</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-4.374643084320539</v>
+        <v>-5.039453699015866</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.716864530817986</v>
+        <v>-4.349813173578767</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.032268690890341</v>
+        <v>-3.644327476709336</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-4.796250869549304</v>
+        <v>-5.398557665568745</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.684669709109549</v>
+        <v>1.171387243932806</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.9115738743212987</v>
+        <v>0.3994385600425474</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.430136093891562</v>
+        <v>2.958106547913573</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>5.569561481034981</v>
+        <v>5.8364731624524</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>6.893397892524021</v>
+        <v>7.191217060884</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>4.370629370629374</v>
+        <v>5.337617128577783</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>3.392148510189848</v>
+        <v>3.640428008817771</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.8687231136210727</v>
+        <v>1.808046083805628</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>4.143800206792257</v>
+        <v>5.133066498139058</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>6.281874484908442</v>
+        <v>7.311802633182815</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>7.576403753818489</v>
+        <v>7.906189555125763</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>7.442265848570671</v>
+        <v>7.772272418148333</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>6.637945995610231</v>
+        <v>6.958211856171005</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>8.252728579831391</v>
+        <v>7.883323095251392</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>14.03422753116009</v>
+        <v>13.74392777046765</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>13.49086331552713</v>
+        <v>13.20138160250158</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>14.11418163829727</v>
+        <v>13.83475549924844</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>15.08833271991171</v>
+        <v>14.81845006988671</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>15.01236406179368</v>
+        <v>14.74261781666332</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 20.78</t>
+          <t>X ≈ 20.77</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.121946290073971</v>
+        <v>1.914708442123533</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>5.97500726532985</v>
+        <v>6.7081367719789</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>8.013144590495408</v>
+        <v>8.688921141751386</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>12.51653033616952</v>
+        <v>13.10417225051367</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>8.672888686546777</v>
+        <v>9.349578359163019</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>9.729668188890713</v>
+        <v>10.39124539996125</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>13.30439844105882</v>
+        <v>13.89280098957519</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>9.547496993861152</v>
+        <v>10.19578612601869</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>4.37162897875465</v>
+        <v>4.25436732502741</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>5.336693727124214</v>
+        <v>5.190853358392623</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.263301915475829</v>
+        <v>0.3367078723494714</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.592817406511017</v>
+        <v>3.476761887704846</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>6.815819495500065</v>
+        <v>5.772403239652142</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>6.594393092167827</v>
+        <v>5.551324363205609</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>8.543960225254935</v>
+        <v>7.457283629727606</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>12.61744966442954</v>
+        <v>12.32517482517487</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>10.74418132439911</v>
+        <v>10.48185597879564</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>11.50872738813074</v>
+        <v>11.23171612967536</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>13.46403900853311</v>
+        <v>14.01171007470221</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>14.52069758284748</v>
+        <v>15.05325673937114</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>14.84689858460604</v>
+        <v>15.36541142610587</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>15.6404814254668</v>
+        <v>16.14426631939772</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>15.91533180778037</v>
+        <v>16.41874103187972</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>14.96979793227116</v>
+        <v>15.48820792395569</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 21.4</t>
+          <t>X ≈ 21.39</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>70</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.8035195484352187</v>
+        <v>-0.7837042562890346</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-8.310707020384434</v>
+        <v>-8.261338197496066</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-6.893687707641284</v>
+        <v>-6.842214389384289</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>5.249449590827901</v>
+        <v>5.301974448315917</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>10.59835452505609</v>
+        <v>10.68046969005435</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>10.78556881000873</v>
+        <v>10.86743587615173</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>10.01247297522035</v>
+        <v>10.09548719226138</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>11.16240382615928</v>
+        <v>11.24584717607974</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>5.489641401114895</v>
+        <v>5.573048643708724</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>7.572718571844703</v>
+        <v>7.657275824815088</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>9.275724275724187</v>
+        <v>9.359906895548356</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>6.139401257442643</v>
+        <v>6.224014634957598</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>5.014577259475232</v>
+        <v>5.10085256810148</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>7.650293713285841</v>
+        <v>7.736916548797737</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>11.27687947991325</v>
+        <v>11.3644875369314</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>10.44353662095127</v>
+        <v>10.53030303030303</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>7.452255858560676</v>
+        <v>7.539243036182782</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>10.20437956204379</v>
+        <v>10.29154518950438</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>13.2777036048064</v>
+        <v>13.36457942757155</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>14.89336839030081</v>
+        <v>14.97999666611092</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>15.77857560323954</v>
+        <v>15.86602192671641</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>14.27402179813763</v>
+        <v>14.36160453673596</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>11.69172932330827</v>
+        <v>11.77893639207508</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>8.75861780804739</v>
+        <v>8.845961281708874</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 22.02</t>
+          <t>X ≈ 22.01</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-7.7147164596322</v>
+        <v>-7.807513780098638</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>5.43446672478931</v>
+        <v>5.74659831044044</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>6.697045883092471</v>
+        <v>5.69746815029842</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>5.983040324418553</v>
+        <v>4.984514130855601</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>6.969010895712394</v>
+        <v>6.037612547197213</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>9.858927883367727</v>
+        <v>9.002356511072378</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>11.78853475128214</v>
+        <v>11.0081856049598</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>10.15854282229828</v>
+        <v>9.341085271317823</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>12.90276881424231</v>
+        <v>12.16035023101031</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>10.77735177647799</v>
+        <v>9.998545666084937</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>9.700434700434855</v>
+        <v>8.883716419358045</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>12.1239572419987</v>
+        <v>11.38274479368766</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>9.647781892679859</v>
+        <v>8.870693837942746</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>10.77770684069898</v>
+        <v>10.03850385038504</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>7.415875618909453</v>
+        <v>6.602582775026626</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>8.011104188518836</v>
+        <v>7.196969696969688</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>6.525614931919591</v>
+        <v>5.674163671103344</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>9.12329848096271</v>
+        <v>8.347100745059933</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>9.33947966658247</v>
+        <v>8.562992125984259</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>8.175221672154187</v>
+        <v>7.360949047063386</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>8.983208807872749</v>
+        <v>8.207291767986256</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>10.25857778269347</v>
+        <v>9.52033469546604</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>10.53342816500712</v>
+        <v>9.794809407948094</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>10.45745950688917</v>
+        <v>9.718977154724733</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 22.63</t>
+          <t>X ≈ 22.62</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.08923383414958153</v>
+        <v>-0.192571251363006</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.239278448955858</v>
+        <v>-2.251485980747297</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-9.036544850498338</v>
+        <v>-7.137780891847257</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-6.17912183774343</v>
+        <v>-4.402459049221029</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.18735976065809</v>
+        <v>0.434164271335149</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-6.357288332848313</v>
+        <v>-4.551283335670924</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-3.558955596208214</v>
+        <v>-1.874956157492313</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-3.837596173840815</v>
+        <v>-2.153167602245489</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.2246443131708205</v>
+        <v>1.336595441738275</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.572718571844604</v>
+        <v>4.01195562777076</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.7242757242757278</v>
+        <v>0.8377394078638147</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.003455885414709</v>
+        <v>0.5589900044157119</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.3425655976677291</v>
+        <v>1.159965868593986</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-2.349706286714159</v>
+        <v>-0.7852509388869962</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.223120520086681</v>
+        <v>0.2807436945670361</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.6278919504772986</v>
+        <v>0.875130616509928</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-2.547744141439409</v>
+        <v>-0.9829244515021216</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-6.22419186652764</v>
+        <v>-4.536041017392179</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-7.793724966622158</v>
+        <v>-6.044287567502337</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-5.820917323984808</v>
+        <v>-4.133303826499827</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-4.578567253903309</v>
+        <v>-2.951712063431366</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-6.440263916148162</v>
+        <v>-4.751695955875057</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-4.379699248120197</v>
+        <v>-2.753083312358314</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-2.66995362052387</v>
+        <v>-1.104777634547013</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 23.25</t>
+          <t>X ≈ 23.24</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>42</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-6.041614786530538</v>
+        <v>-6.021799494384354</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.644040353717763</v>
+        <v>-1.594671530829395</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-3.084163898117382</v>
+        <v>-3.032690579860386</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.417217075838764</v>
+        <v>-1.364692218350747</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-6.544502617801051</v>
+        <v>-6.462387452802787</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-6.357288332848412</v>
+        <v>-6.275421266705408</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-9.511336548589171</v>
+        <v>-9.428322331548145</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-7.40902474526915</v>
+        <v>-7.325581395348699</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-9.748453836980346</v>
+        <v>-9.665046594386517</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-10.52251952339339</v>
+        <v>-10.43796227042301</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-10.24808524808538</v>
+        <v>-10.16390262826121</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-15.28917017112865</v>
+        <v>-15.2045567936137</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-16.41399416909606</v>
+        <v>-16.32771886046982</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-19.01637295338069</v>
+        <v>-18.92975011786879</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-12.5326443296105</v>
+        <v>-12.44503627259235</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-16.69932052190588</v>
+        <v>-16.61255411255411</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-12.07155366524906</v>
+        <v>-11.98456648762696</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-12.1765728189086</v>
+        <v>-12.08940719144801</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-9.579439252336314</v>
+        <v>-9.492563429571163</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-11.77329827636576</v>
+        <v>-11.68667000055566</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-9.935710111046035</v>
+        <v>-9.848263787569167</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-10.0116924875766</v>
+        <v>-9.924109748978267</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-9.736842105263293</v>
+        <v>-9.649635036496484</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-9.812810763381243</v>
+        <v>-9.725467289719759</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 23.87</t>
+          <t>X ≈ 23.86</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-9.429893174808925</v>
+        <v>-9.640847113431967</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-9.794223503900923</v>
+        <v>-7.975623911781781</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-9.311270125223615</v>
+        <v>-7.41364296081283</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-4.256044914666546</v>
+        <v>-2.126596980255513</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-6.544502617800994</v>
+        <v>-4.462387452802787</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-10.20344217900231</v>
+        <v>-8.275421266705408</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-3.284230321482937</v>
+        <v>-1.047369950595751</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-7.409024745269285</v>
+        <v>-7.325581395348834</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-13.13673222525873</v>
+        <v>-13.28409421343413</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-10.06464406551792</v>
+        <v>-10.05700988947062</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-7.867132867132867</v>
+        <v>-7.782950247308698</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-4.300159182117859</v>
+        <v>-4.061699650756694</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.267324512222423</v>
+        <v>2.815138282387245</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.045898108890079</v>
+        <v>2.594059405940541</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>1.386769589803428</v>
+        <v>1.935916108360097</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>5.828152005566601</v>
+        <v>6.530303030303031</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>7.617091023395815</v>
+        <v>8.396385893325672</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>5.58899494665912</v>
+        <v>6.291545189504376</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>5.805176132278824</v>
+        <v>6.507436570428588</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>4.069192566125025</v>
+        <v>4.694282380396729</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-2.24340241873864</v>
+        <v>-1.848263787569415</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.3963078721922244</v>
+        <v>0.07589025102154068</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.1214574898786012</v>
+        <v>0.3503649635037078</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.725650775080432</v>
+        <v>2.274532710280432</v>
       </c>
     </row>
     <row r="24">
@@ -2098,161 +2098,161 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-11.66066240557815</v>
+        <v>-11.33315480573966</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.02499273467014973</v>
+        <v>-2.052546988704854</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-11.46511627906977</v>
+        <v>-13.10595065312041</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-12.17912183774359</v>
+        <v>-13.81890467256321</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-16.54450261780111</v>
+        <v>-18.00084899126432</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-12.35728833284836</v>
+        <v>-13.9677289590131</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-5.130384167636784</v>
+        <v>-7.047369950595758</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-5.409024745269285</v>
+        <v>-5.402504472271907</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>8.632498543972041</v>
+        <v>8.100521171181256</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>11.858432857559</v>
+        <v>11.17375934129861</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>12.13286713286719</v>
+        <v>11.44781898346059</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>9.853686971728408</v>
+        <v>9.245992656935613</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>12.728862973761</v>
+        <v>11.96898443623329</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>12.50743657042876</v>
+        <v>11.7479055597867</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>9.848308051341888</v>
+        <v>9.166685339129209</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>4.443536620951328</v>
+        <v>3.991841491841491</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>4.309398715703509</v>
+        <v>3.857924354864018</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>4.204379562043847</v>
+        <v>3.753083651042836</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>4.420560747663551</v>
+        <v>3.968975031967162</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>2.607654104586679</v>
+        <v>2.232743918858269</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.06428988895388699</v>
+        <v>-0.2328791721846883</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1.988307512423269</v>
+        <v>1.614351789483081</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>4.263157894736899</v>
+        <v>3.811903425042054</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>2.187189236618892</v>
+        <v>1.812994248741859</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 25.1</t>
+          <t>X ≈ 25.09</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>54</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>5.598596853681101</v>
+        <v>5.618412145827286</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-5.876844586522004</v>
+        <v>-5.827475763633636</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.09043927648578887</v>
+        <v>0.1419125947427844</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.47541813403982</v>
+        <v>-2.422893276551804</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-6.544502617801051</v>
+        <v>-6.462387452802787</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-8.209140184700267</v>
+        <v>-8.127273118557262</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-10.83408787134054</v>
+        <v>-10.75107365429952</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-9.26087659712114</v>
+        <v>-9.177433247200689</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-16.62676071528722</v>
+        <v>-16.54335347269339</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-9.99341899429286</v>
+        <v>-9.908861741322475</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-6.015281015281062</v>
+        <v>-5.931098395456893</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.590757472716092</v>
+        <v>-2.506144095201137</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.863729618831655</v>
+        <v>-1.777454310205407</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.085156022163837</v>
+        <v>-1.99853318665194</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.9594191624530026</v>
+        <v>1.047027219471154</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-4.000907823493115</v>
+        <v>-3.914141414141355</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>1.420509826814566</v>
+        <v>1.507497004436672</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-6.0919167342525</v>
+        <v>-6.004751106791915</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-9.579439252336449</v>
+        <v>-9.492563429571298</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-9.392345895413378</v>
+        <v>-9.305717619603271</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-6.23200640734246</v>
+        <v>-6.144560083865592</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-4.456136932021174</v>
+        <v>-4.368554193422845</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.4775828460039051</v>
+        <v>-0.3903757772370966</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>1.298300347730006</v>
+        <v>1.38564382139149</v>
       </c>
     </row>
     <row r="26">
@@ -2265,732 +2265,732 @@
         <v>30</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>6.339337594421849</v>
+        <v>6.359152886568033</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>9.308340598663179</v>
+        <v>9.357709421551547</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>11.20155038759685</v>
+        <v>11.25302370585384</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.82087816225647</v>
+        <v>3.873403019744487</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>13.45549738219895</v>
+        <v>13.53761254719721</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.64271166715163</v>
+        <v>3.724578733294635</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.797050834303349</v>
+        <v>-3.714036617262323</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.7423580786025212</v>
+        <v>-0.6589147286820705</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-7.36750145602786</v>
+        <v>-7.284094213434031</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-14.80823380910758</v>
+        <v>-14.72367655613719</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-11.2004662004662</v>
+        <v>-11.11628358064203</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-11.47964636160498</v>
+        <v>-11.39503298409003</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-12.6044703595723</v>
+        <v>-12.51819505094605</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.174103237095274</v>
+        <v>7.26072607260717</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.1516919486581116</v>
+        <v>-0.0640838916399602</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-2.88979671238215</v>
+        <v>-2.80303030303039</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-3.023934617629784</v>
+        <v>-2.936947440007678</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>3.537712895377119</v>
+        <v>3.624878522837705</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.4205607476636501</v>
+        <v>0.5074365704288013</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-2.725679228746614</v>
+        <v>-2.639050952936508</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-3.269043444379406</v>
+        <v>-3.181597120902538</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-3.345025820910152</v>
+        <v>-3.257443082311823</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-3.070175438596578</v>
+        <v>-2.98296836982977</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-3.146144096714345</v>
+        <v>-3.058800623052861</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 26.33</t>
+          <t>X ≈ 26.32</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-7.7147164596322</v>
+        <v>-6.582023584020206</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.02906131938390644</v>
+        <v>1.90672902939469</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.411062225015634</v>
+        <v>-2.472466490224491</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>8.685743027121369</v>
+        <v>8.579285372685661</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>8.320362247063848</v>
+        <v>8.24349490013843</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>5.804873829313713</v>
+        <v>5.489284615647492</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>10.43718339993075</v>
+        <v>10.59968887293366</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>10.15854282229821</v>
+        <v>10.32147742818049</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>12.90276881424224</v>
+        <v>13.30414108068339</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.020595019721121</v>
+        <v>0.7665195222939971</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.110376110376066</v>
+        <v>-1.900597306132227</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>9.421254539295916</v>
+        <v>6.644182702184438</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>8.296430541328434</v>
+        <v>8.462197105916566</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.669598732590863</v>
+        <v>-0.5824111822946918</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>15.52398372701757</v>
+        <v>13.46532787306592</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>13.41650959392424</v>
+        <v>11.11853832442068</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>10.57966898597365</v>
+        <v>8.043444716854879</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>13.17735253501676</v>
+        <v>10.87978048362203</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>10.69083101793375</v>
+        <v>14.0368483351345</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>8.175221672154031</v>
+        <v>11.28251767451421</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>7.631857456521395</v>
+        <v>10.73997150654827</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>7.555875079990919</v>
+        <v>10.66412554513925</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>10.53342816500712</v>
+        <v>13.87977672820954</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>13.16016220959179</v>
+        <v>16.74512094557441</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 26.95</t>
+          <t>X ≈ 26.94</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-7.506816251731948</v>
+        <v>-8.813260906535362</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.667314957637537</v>
+        <v>1.196789881321664</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.073345259391715</v>
+        <v>6.655322556428608</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.513185854564114</v>
+        <v>2.494092674916892</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.147805074506593</v>
+        <v>2.158302202369576</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.335019359459274</v>
+        <v>2.345268388466998</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.408077370824813</v>
+        <v>5.021595566645622</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>11.82174448549994</v>
+        <v>11.63993584603048</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-3.521347609874113</v>
+        <v>-2.111680420330636</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.4492594501334182</v>
+        <v>4.011955627770703</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.1748251748252798</v>
+        <v>0.8377394078636655</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-8.146313028271706</v>
+        <v>-2.889285857653249</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-5.424983180085214</v>
+        <v>-4.012447924509409</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>5.892051955044032</v>
+        <v>9.559576647319858</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>1.386769589803372</v>
+        <v>5.453157487670332</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>5.828152005566658</v>
+        <v>9.495820271682348</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>9.540167946472621</v>
+        <v>12.81017899677379</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>9.435148792813017</v>
+        <v>12.70533829295265</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>13.49748382458662</v>
+        <v>9.472953811808019</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>13.6845771815098</v>
+        <v>9.659799621776131</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>5.44890527356916</v>
+        <v>2.220701729672122</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-2.319384795269087</v>
+        <v>-4.751695955874908</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-9.736842105262994</v>
+        <v>-11.37377296753068</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-21.35127230184259</v>
+        <v>-21.79443280696096</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 27.57</t>
+          <t>X ≈ 27.55</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>26</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.031645286729493</v>
+        <v>4.051460578875677</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-7.871146580823996</v>
+        <v>-7.821777757935628</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.618962432915922</v>
+        <v>-1.567489114658926</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.513185854564156</v>
+        <v>1.565710712052173</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.147805074506635</v>
+        <v>1.229920239504899</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>5.181173205613185</v>
+        <v>5.263040271756189</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-3.284230321482937</v>
+        <v>-3.201216104441912</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>15.66789833165378</v>
+        <v>15.75134168157423</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>19.55557546704897</v>
+        <v>19.6389827096428</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>14.93535593448212</v>
+        <v>15.0199131874525</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>19.05594405594411</v>
+        <v>19.14012667576828</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>18.77676389480533</v>
+        <v>18.86137727232028</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>17.65193989683787</v>
+        <v>17.73821520546412</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>17.43051349350574</v>
+        <v>17.51713632901763</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>16.77138497441886</v>
+        <v>16.85899303143702</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>13.52045969787434</v>
+        <v>13.6072261072261</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>13.38632179262657</v>
+        <v>13.47330897024868</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>17.12745648512072</v>
+        <v>17.21462211258131</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>13.49748382458667</v>
+        <v>13.58435964735182</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>13.68457718150969</v>
+        <v>13.77120545731979</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>13.14121296587685</v>
+        <v>13.22865928935372</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>16.91138443550025</v>
+        <v>16.99896717409857</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>21.03238866396756</v>
+        <v>21.11959573273437</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>13.26411231354192</v>
+        <v>13.3514557872034</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 28.18</t>
+          <t>X ≈ 28.17</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>13</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-22.89143163634743</v>
+        <v>-22.87161634420125</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-30.94806965774707</v>
+        <v>-30.8987008348587</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-1.618962432915922</v>
+        <v>-1.567489114658926</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.35933970071801</v>
+        <v>5.411864558206027</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-2.698348771647204</v>
+        <v>-2.61623360664894</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>12.8734808979207</v>
+        <v>12.95534796406371</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>19.79269275544015</v>
+        <v>19.87570697248118</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>11.82174448549983</v>
+        <v>11.90518783542028</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>19.55557546704886</v>
+        <v>19.63898270964269</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>18.78150978063593</v>
+        <v>18.86606703360631</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>19.05594405594407</v>
+        <v>19.14012667576824</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>18.77676389480538</v>
+        <v>18.86137727232034</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>17.65193989683787</v>
+        <v>17.73821520546412</v>
       </c>
       <c r="P30" s="4" t="n">
+        <v>9.824828636709711</v>
+      </c>
+      <c r="Q30" s="4" t="n">
+        <v>9.166685339129266</v>
+      </c>
+      <c r="R30" s="4" t="n">
+        <v>9.761072261072258</v>
+      </c>
+      <c r="S30" s="4" t="n">
+        <v>1.934847431787212</v>
+      </c>
+      <c r="T30" s="4" t="n">
+        <v>1.83000672796603</v>
+      </c>
+      <c r="U30" s="4" t="n">
         <v>9.738205801197815</v>
       </c>
-      <c r="Q30" s="4" t="n">
-        <v>9.079077282111115</v>
-      </c>
-      <c r="R30" s="4" t="n">
-        <v>9.674305851720497</v>
-      </c>
-      <c r="S30" s="4" t="n">
-        <v>1.847860254165106</v>
-      </c>
-      <c r="T30" s="4" t="n">
-        <v>1.742841100505444</v>
-      </c>
-      <c r="U30" s="4" t="n">
-        <v>9.651329978432663</v>
-      </c>
       <c r="V30" s="4" t="n">
-        <v>17.53073102766356</v>
+        <v>17.61735930347366</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>16.98736681203076</v>
+        <v>17.07481313550763</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>16.9113844355002</v>
+        <v>16.99896717409853</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>24.87854251012146</v>
+        <v>24.96574957888826</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>32.4948815443112</v>
+        <v>32.58222501797268</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 28.8</t>
+          <t>X ≈ 28.79</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>13.00600426108858</v>
+        <v>19.08642561384082</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>29.30834059866319</v>
+        <v>27.84255790640005</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-13.7984496124031</v>
+        <v>-9.959097506267319</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.154211495589806</v>
+        <v>7.50976665610812</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.788830715532342</v>
+        <v>7.173976183560846</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>10.30937833381832</v>
+        <v>7.360942369658225</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>9.536282499029944</v>
+        <v>6.588993685767875</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>9.257641921397557</v>
+        <v>6.310782241014934</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>9.299165210638883</v>
+        <v>6.352269422929638</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8.525099524225652</v>
+        <v>5.579353746893013</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>8.799533799533918</v>
+        <v>5.853413389054936</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>8.520353638395008</v>
+        <v>5.574663985606811</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7.395529640427597</v>
+        <v>4.451501918750957</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.159230096237962</v>
+        <v>-4.860486048604862</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-1.818358615324662</v>
+        <v>-5.518629346185541</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-1.22313004571528</v>
+        <v>-4.92424242424255</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-9.690601284296548</v>
+        <v>-14.14906865212924</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-9.79562043795621</v>
+        <v>-14.25390935595043</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-9.579439252336449</v>
+        <v>-14.03801797502584</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-9.392345895413257</v>
+        <v>-13.85117216505768</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-1.60237677771272</v>
+        <v>-5.302809242114627</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-1.678359154243282</v>
+        <v>-5.378655203523863</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-1.403508771929822</v>
+        <v>-5.104180491041809</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>6.853855903285677</v>
+        <v>3.910896346644009</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 29.42</t>
+          <t>X ≈ 29.41</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-16.16066240557815</v>
+        <v>-20.30751378009864</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-41.52499273467015</v>
+        <v>-31.75340168955956</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-42.96511627906986</v>
+        <v>-44.30253184970174</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-43.67912183774353</v>
+        <v>-45.0154858691444</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-56.54450261780105</v>
+        <v>-56.46238745280271</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-31.35728833284841</v>
+        <v>-22.94208793337199</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-32.13038416763688</v>
+        <v>-23.71403661726243</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-32.40902474526938</v>
+        <v>-23.99224806201551</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-32.36750145602805</v>
+        <v>-23.9507608801008</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-20.641567142441</v>
+        <v>-13.61256544502618</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-32.86713286713304</v>
+        <v>-24.44961691397537</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-20.64631302827183</v>
+        <v>-13.61725520631225</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-9.27113702623906</v>
+        <v>-3.629306162057411</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>15.50743657042887</v>
+        <v>18.37183718371853</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>14.84830805134172</v>
+        <v>17.71369388613797</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>15.4435366209511</v>
+        <v>18.30808080808096</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>15.30939871570328</v>
+        <v>18.17416367110349</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>15.20437956204362</v>
+        <v>18.0693229672823</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>15.42056074766338</v>
+        <v>18.28521434820633</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>15.60765410458627</v>
+        <v>18.47206015817419</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>15.06428988895347</v>
+        <v>17.92951399020816</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>2.488307512422914</v>
+        <v>6.742556917688098</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-9.736842105263335</v>
+        <v>-4.094079480940948</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>2.687189236618536</v>
+        <v>6.941199376946876</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 30.04</t>
+          <t>X ≈ 30.02</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>11</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-17.29702604194178</v>
+        <v>-17.2772107497956</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-44.93408364376106</v>
+        <v>-44.88471482087269</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-46.37420718816067</v>
+        <v>-46.32273386990368</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-56.17912183774353</v>
+        <v>-56.12659698025551</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-47.45359352689202</v>
+        <v>-47.37147836189376</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-38.1754701510303</v>
+        <v>-38.09360308488729</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-29.85765689490951</v>
+        <v>-29.77464267786849</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-30.13629747254195</v>
+        <v>-30.0528541226215</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-30.09477418330062</v>
+        <v>-30.01136694070679</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-30.86883986971367</v>
+        <v>-30.78428261674328</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-21.5034965034965</v>
+        <v>-21.41931388367233</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-21.78267666463535</v>
+        <v>-21.6980632871204</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-31.99840975351179</v>
+        <v>-31.91213444488554</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-32.21983615684415</v>
+        <v>-32.13321332133226</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-23.78805558502169</v>
+        <v>-23.70044752800354</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-23.19282701541231</v>
+        <v>-23.10606060606055</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-14.23605582975109</v>
+        <v>-14.14906865212899</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-14.34107498341076</v>
+        <v>-14.25390935595017</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-14.124893797791</v>
+        <v>-14.03801797502584</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-13.93780044086779</v>
+        <v>-13.85117216505768</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-14.48116465650058</v>
+        <v>-14.39371833302371</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-14.55714703303114</v>
+        <v>-14.46956429443281</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-14.28229665071757</v>
+        <v>-14.19508958195076</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-14.35826530883552</v>
+        <v>-14.27092183517404</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 30.65</t>
+          <t>X ≈ 30.64</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>19</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-6.292241352946576</v>
+        <v>-6.272426060800392</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-6.656571682038575</v>
+        <v>-6.607202859150206</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-2.833537331701308</v>
+        <v>-2.782064013444312</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-14.0738586798488</v>
+        <v>-14.02133382236078</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.350234224304245</v>
+        <v>1.432349389302509</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-3.72570938548003</v>
+        <v>-3.643842319337026</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.7643526744684834</v>
+        <v>0.8473668915095089</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-4.777445797900931</v>
+        <v>-4.69400244798048</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.527235386077308</v>
+        <v>0.6106426286711368</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.2468303003357875</v>
+        <v>-0.162273047365403</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>5.2907618697092</v>
+        <v>5.37494448953337</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>5.011581708570496</v>
+        <v>5.096195086085451</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>9.149915605339885</v>
+        <v>9.236190913966134</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>8.928489202007604</v>
+        <v>9.015112037519501</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>3.006202788183955</v>
+        <v>3.093810845202107</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>3.601431357793338</v>
+        <v>3.688197767145098</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>8.73045134728244</v>
+        <v>8.817438524904546</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>8.625432193622778</v>
+        <v>8.712597821083364</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>14.10477127397942</v>
+        <v>14.19164709674457</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>14.29186463090245</v>
+        <v>14.37849290671255</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>13.74850041526965</v>
+        <v>13.83594673874652</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>13.67251803873905</v>
+        <v>13.76010077733738</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>13.94736842105262</v>
+        <v>14.03457548981943</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>13.87139976293467</v>
+        <v>13.95874323659616</v>
       </c>
     </row>
   </sheetData>
@@ -3184,79 +3184,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3349</v>
+        <v>3354</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2502234969186006</v>
+        <v>-0.2502637554218978</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.3020618536259576</v>
+        <v>-0.302638129791255</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.3315851217997334</v>
+        <v>-0.3321614793312833</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2871657676930681</v>
+        <v>-0.2878299381689686</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1608921664946408</v>
+        <v>-0.1623578056044508</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.1648321403922139</v>
+        <v>-0.166287221628302</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.1488036566445032</v>
+        <v>-0.1503067645975378</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.1727691732039105</v>
+        <v>-0.1742460837761328</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.1142315392621995</v>
+        <v>-0.1157950148588824</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.09815352364825713</v>
+        <v>-0.09976523388866809</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.07415249830479098</v>
+        <v>-0.07579254015099224</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.008853938714970866</v>
+        <v>-0.01060042318687948</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.04433916423712958</v>
+        <v>0.04247854984632937</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.1085083179726141</v>
+        <v>0.1065445426825775</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.1520602848141976</v>
+        <v>0.150010666790017</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.109905402601548</v>
+        <v>0.1079353919924984</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.006453489302515436</v>
+        <v>-0.008255582425711339</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.03407051247186388</v>
+        <v>-0.03583576287658019</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.02103779000105988</v>
+        <v>0.01919602264663212</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.04250992762333539</v>
+        <v>-0.04425246177123654</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.02849036628079915</v>
+        <v>0.02662450554955598</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>0.0002442477261652698</v>
+        <v>-0.001582931338361959</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>0.1139041633935634</v>
+        <v>0.1119148889879966</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.08566639397930231</v>
+        <v>0.08371577527739049</v>
       </c>
     </row>
     <row r="7">
@@ -3266,79 +3266,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3294</v>
+        <v>3299</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.3896343681949759</v>
+        <v>-0.3897935312525576</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.3760180663951189</v>
+        <v>-0.3773101508663999</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.3519941071240638</v>
+        <v>-0.3534019969573521</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.2949938956795606</v>
+        <v>-0.2965276822741885</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.2511129407711721</v>
+        <v>-0.2538280796864498</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.348834226568222</v>
+        <v>-0.35139353079947</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.2593482268334029</v>
+        <v>-0.2620864765306194</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.3093268600729076</v>
+        <v>-0.3120067347153537</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.2505476935619555</v>
+        <v>-0.2533156980448723</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.1911439259960233</v>
+        <v>-0.1940458085771652</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1410971852459539</v>
+        <v>-0.1440613584198118</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.07008798289959373</v>
+        <v>-0.07317654595452439</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.002690507800274133</v>
+        <v>-0.0005716874013259599</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.01106853168778343</v>
+        <v>0.007779563087773056</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.06629170256804429</v>
+        <v>0.06288104185459531</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.0134942224049297</v>
+        <v>0.01019417030907732</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.1631853497312648</v>
+        <v>-0.1662275368014789</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.1895598318956004</v>
+        <v>-0.1925697878027322</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.1371840234792145</v>
+        <v>-0.1402631874405458</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.2049596006892997</v>
+        <v>-0.2079277316226467</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.09342924965702792</v>
+        <v>-0.09659813039183263</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.1512555943728486</v>
+        <v>-0.1543430116260893</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.04033224183372397</v>
+        <v>-0.04357443043573994</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.03746164376969574</v>
+        <v>-0.04071433427858295</v>
       </c>
     </row>
     <row r="8">
@@ -3348,79 +3348,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3213</v>
+        <v>3218</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.3232087591010213</v>
+        <v>-0.323969606489662</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.331020555381123</v>
+        <v>-0.3336486031398067</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2393896247716896</v>
+        <v>-0.2422937789665198</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.03931361009119883</v>
+        <v>-0.04259450959461475</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.04697786532580039</v>
+        <v>-0.05213104254637813</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.08987886209632023</v>
+        <v>-0.09495155100702135</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1761173803508385</v>
+        <v>0.1705589520317545</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.07007094999241303</v>
+        <v>0.06464742345141161</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.09842171621491502</v>
+        <v>0.0929549668937355</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.08588869889769768</v>
+        <v>0.08036634815314159</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.06839100143501753</v>
+        <v>0.06291790496614169</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.117252863201216</v>
+        <v>0.1116749622463971</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.1581433707832716</v>
+        <v>0.1523943988319019</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.1413180473135895</v>
+        <v>0.1355711779356454</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.2145402052835337</v>
+        <v>0.208615209692546</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.1765387941893977</v>
+        <v>0.1707246050085445</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.001160290507726813</v>
+        <v>-0.006714881868241207</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.02550549542746694</v>
+        <v>-0.03103545565691235</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.05387336419556021</v>
+        <v>0.04823706686060092</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.01082476047719894</v>
+        <v>0.005269345014980331</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.1389167546254768</v>
+        <v>0.1331084570752168</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>0.1127243086907654</v>
+        <v>0.1069461516427168</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>0.2507123440212311</v>
+        <v>0.244742099260101</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>0.1934139487259614</v>
+        <v>0.1875221447116928</v>
       </c>
     </row>
     <row r="9">
@@ -3430,79 +3430,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3034</v>
+        <v>3044</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.3404137958300311</v>
+        <v>-0.2662139213876245</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.556406347235594</v>
+        <v>-0.4857348054543209</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.3750999124576495</v>
+        <v>-0.3076070717426234</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.1869803839124842</v>
+        <v>-0.121375048140635</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2392291163270883</v>
+        <v>-0.1776992386336644</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1318623826518177</v>
+        <v>-0.1029849505721643</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.2606351702852052</v>
+        <v>0.3195036201327568</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.2958932875176075</v>
+        <v>0.3541571667426666</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.553128258632583</v>
+        <v>0.5779522069646958</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.7167005740944248</v>
+        <v>0.7068880830604414</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.7150791446820364</v>
+        <v>0.705764178599054</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.816260839095392</v>
+        <v>0.8061013963637222</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.8273851412486266</v>
+        <v>0.8151382823871884</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.7571080553170049</v>
+        <v>0.7446815408456402</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.8078874138131411</v>
+        <v>0.7940883979113025</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.8971855361386432</v>
+        <v>0.8514039477342266</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.8815789195837525</v>
+        <v>0.8028100165638392</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.8293795620437834</v>
+        <v>0.7505615829470003</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.9996986219643063</v>
+        <v>0.8878891778409752</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>1.10798326851026</v>
+        <v>0.9961196507379384</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>1.210157521485932</v>
+        <v>1.096928204554104</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>1.121377341145269</v>
+        <v>1.00826057275502</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>1.251625769530918</v>
+        <v>1.138542303405124</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>1.29463814894585</v>
+        <v>1.181234418558951</v>
       </c>
     </row>
     <row r="10">
@@ -3512,79 +3512,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2759</v>
+        <v>2764</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.5334158203876385</v>
+        <v>-0.5371513832561519</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2313933100027654</v>
+        <v>-0.2426734451629713</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.1413752718755177</v>
+        <v>-0.1533198010282106</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1001152979167799</v>
+        <v>0.08748347951459579</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.137015216793138</v>
+        <v>-0.1562430043658551</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2175692114944283</v>
+        <v>-0.2366002746133873</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.2543420571470847</v>
+        <v>0.2341834474624918</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.2486329123883735</v>
+        <v>0.2283754391835373</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.7074805194587057</v>
+        <v>0.6863987696533087</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.7837844623191828</v>
+        <v>0.7622845669728591</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.7908757908757877</v>
+        <v>0.7694444231990474</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.9298327674699607</v>
+        <v>0.9080409832490659</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.306480302280789</v>
+        <v>1.283606750855661</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.395843937709309</v>
+        <v>1.372718382148243</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>1.264493022440149</v>
+        <v>1.241361474389613</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>1.665076194496628</v>
+        <v>1.641414141414145</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>1.806144919608002</v>
+        <v>1.782167199713143</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>1.831865999656813</v>
+        <v>1.807790676868997</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>2.070343670963119</v>
+        <v>2.045898108890242</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>2.06259438688847</v>
+        <v>2.038213016234877</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>2.120770699960353</v>
+        <v>2.096080267363838</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>2.393233263962564</v>
+        <v>2.368008833812631</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>2.654462242562921</v>
+        <v>2.628845976161877</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>2.891067453364094</v>
+        <v>2.864981335461273</v>
       </c>
     </row>
     <row r="11">
@@ -3594,79 +3594,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2410</v>
+        <v>2415</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.6808021507487254</v>
+        <v>-0.6876067524803631</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.6944006294069993</v>
+        <v>-0.7134162794469461</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.3437670400734731</v>
+        <v>-0.3643818770689364</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.4463925655486491</v>
+        <v>0.4237110279580421</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1454932652784109</v>
+        <v>0.1111540426779101</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.05580563103622183</v>
+        <v>-0.08964239288707887</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.2655779254822974</v>
+        <v>0.2305905757200293</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.4227971838321167</v>
+        <v>0.3872939645853464</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.7355913274771879</v>
+        <v>0.6994448812160741</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.9755945737306106</v>
+        <v>0.9384614979315984</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.109342576532008</v>
+        <v>1.072074464388173</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.473835609218028</v>
+        <v>1.435622145699831</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.819321461988949</v>
+        <v>1.779688983129148</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.077684504312991</v>
+        <v>2.037358375012765</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>2.14677849367343</v>
+        <v>2.105883105059704</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>2.188780624259792</v>
+        <v>2.148132167735966</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>2.2456833660965</v>
+        <v>2.204808684407311</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>2.373253734229216</v>
+        <v>2.332024330355267</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>2.573769857394396</v>
+        <v>2.532229958858458</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>2.662335131927144</v>
+        <v>2.620698254724964</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>2.600551803582917</v>
+        <v>2.558684103249554</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>2.965090265325429</v>
+        <v>2.922394181513944</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>3.514920648780802</v>
+        <v>3.471225890655973</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>3.755653966909343</v>
+        <v>3.711385712350769</v>
       </c>
     </row>
     <row r="12">
@@ -3676,79 +3676,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2045</v>
+        <v>2051</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.090342327983585</v>
+        <v>-1.080460640002009</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.8954439719336165</v>
+        <v>-0.858175869249159</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.06886430345449668</v>
+        <v>0.05057367361662557</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.8874153162146996</v>
+        <v>0.8642109539486427</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.7441271198082831</v>
+        <v>0.7496164194140533</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.8133485169328196</v>
+        <v>0.8190097260306715</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.235374587227035</v>
+        <v>1.237513770334481</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.374430242565261</v>
+        <v>1.326866496071425</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.395887054195995</v>
+        <v>1.348301518864609</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.546845710528814</v>
+        <v>1.525716942164507</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.577852527219612</v>
+        <v>1.585981791526258</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.834212775038964</v>
+        <v>1.870306177315186</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.121268037052083</v>
+        <v>2.185400673057735</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.709092683434058</v>
+        <v>2.771988428789406</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>2.762538070835063</v>
+        <v>2.794447950849104</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>2.85211780086351</v>
+        <v>2.854075514503322</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>3.089886520581501</v>
+        <v>3.060459787345977</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>3.210724120364929</v>
+        <v>3.15007703199344</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>3.457670122663551</v>
+        <v>3.396541628794459</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>3.644763479586622</v>
+        <v>3.613990409593811</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>3.376454031601604</v>
+        <v>3.345504469490102</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>3.722422859441842</v>
+        <v>3.690113339185267</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>4.028439068330975</v>
+        <v>3.995589135043609</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>4.099169676716699</v>
+        <v>4.097058307549993</v>
       </c>
     </row>
     <row r="13">
@@ -3761,76 +3761,76 @@
         <v>1735</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.8478036225701189</v>
+        <v>-0.8646593630026658</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.12436091387751</v>
+        <v>-1.169209249697012</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.4967073187021569</v>
+        <v>-0.513929493764067</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.2826817234282117</v>
+        <v>0.2954213683683378</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.4095203707046977</v>
+        <v>0.3936079574094933</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.3668495981860644</v>
+        <v>0.3835913624564782</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.3983514645471189</v>
+        <v>0.4483221803634621</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.7278355192505543</v>
+        <v>0.744493274381206</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.7452718466187633</v>
+        <v>0.7285422024188293</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.006879347777641</v>
+        <v>1.023449880644328</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.7634770292998141</v>
+        <v>0.7802681434958956</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.174745659875647</v>
+        <v>1.191173912461693</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.48835664464702</v>
+        <v>1.539692623962807</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.302603428886698</v>
+        <v>2.389226264398594</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>2.3339237015145</v>
+        <v>2.421531758532652</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>2.583927875266582</v>
+        <v>2.670694284618342</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>2.7734171382711</v>
+        <v>2.824464144188617</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>2.934794308587577</v>
+        <v>2.949773037605645</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>3.302405128067015</v>
+        <v>3.280739217149069</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>3.66240914781428</v>
+        <v>3.640197225045746</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>3.407229370221842</v>
+        <v>3.385338053627471</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>4.022889644988119</v>
+        <v>4.036742294775202</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>4.413013802517831</v>
+        <v>4.463268189310099</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>4.221771369183742</v>
+        <v>4.309114842845226</v>
       </c>
     </row>
     <row r="14">
@@ -3843,76 +3843,76 @@
         <v>1484</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.475053797642708</v>
+        <v>-1.496074995469499</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.467792196312146</v>
+        <v>-1.527602449675818</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.7544837084102767</v>
+        <v>-0.782770477591292</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.07929000613264492</v>
+        <v>0.08562598817967171</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3533855249342892</v>
+        <v>-0.3467960549533231</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.3048920170842848</v>
+        <v>0.3486540527296995</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.8776912024843426</v>
+        <v>0.9607054195253681</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.33929288595548</v>
+        <v>1.422736235875931</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.313521424187378</v>
+        <v>1.396928666781207</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.683466504934501</v>
+        <v>1.768023757904885</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.419542772167269</v>
+        <v>1.503725391991438</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.015194374150958</v>
+        <v>2.099807751665914</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.505444400409665</v>
+        <v>2.591719709035914</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.629913017265849</v>
+        <v>3.716535852777746</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>3.912911012310929</v>
+        <v>4.00051906932908</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>4.104371075863789</v>
+        <v>4.191137485215549</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>4.080442486747216</v>
+        <v>4.124515099247496</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>4.422708403014148</v>
+        <v>4.423442901482844</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>4.638889588633909</v>
+        <v>4.639334282407169</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>4.960753835044834</v>
+        <v>4.960769594394037</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>4.686931398387792</v>
+        <v>4.687402430465688</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>5.621730693016254</v>
+        <v>5.665115840247189</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>6.098737409561629</v>
+        <v>6.185944478328437</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>6.15753964093156</v>
+        <v>6.244883114593044</v>
       </c>
     </row>
     <row r="15">
@@ -3922,243 +3922,243 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.635425812518207</v>
+        <v>-2.661990418052177</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.1702176754752</v>
+        <v>-2.251485980747297</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.637176263284445</v>
+        <v>-1.68815276473434</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.2201636688406126</v>
+        <v>-0.2396268075710566</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.5855444488981334</v>
+        <v>-0.6100700922371942</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.1541560238998088</v>
+        <v>0.0925032615964767</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.038518752647356</v>
+        <v>1.095824384573397</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.391290961123772</v>
+        <v>1.447038588915525</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.274961053837863</v>
+        <v>1.33116935855643</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.158353930960736</v>
+        <v>2.210496011394838</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.880302018423563</v>
+        <v>1.933808210598464</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.153608045130092</v>
+        <v>2.205806250108765</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.923022405489434</v>
+        <v>2.970921130538251</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4.122274770902258</v>
+        <v>4.166049964555867</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>4.410265430978825</v>
+        <v>4.452045140618104</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>4.926567402324586</v>
+        <v>4.967753856424196</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>4.63457630054954</v>
+        <v>4.676480307172923</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>4.924190138207969</v>
+        <v>4.965030634036239</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>5.692857511673019</v>
+        <v>5.731669457918862</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>6.116730663386939</v>
+        <v>6.154549886297602</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>6.04692603733583</v>
+        <v>6.084072955152969</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>6.760209643441421</v>
+        <v>6.795009055112864</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>7.035060025754994</v>
+        <v>7.148161973731817</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>6.801238171109816</v>
+        <v>6.914973308234742</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 19.24</t>
+          <t>X &gt; 19.23</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1075</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.6383575728644</v>
+        <v>-2.667723851152083</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.187783432344567</v>
+        <v>-1.19269255742185</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.3023255813953583</v>
+        <v>-0.2604396181943898</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.309250255279721</v>
+        <v>1.347869129308094</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.6647997077803396</v>
+        <v>0.6406766140495819</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.689223295058561</v>
+        <v>1.717143789056671</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.776592576549263</v>
+        <v>2.859606793590288</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.96306827798653</v>
+        <v>3.04651162790698</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.632498543972041</v>
+        <v>2.71590578656587</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.2537816947683</v>
+        <v>3.338338947738684</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2.318913644495041</v>
+        <v>2.40309626431921</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.504849762426026</v>
+        <v>2.589463139940982</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.519560648179542</v>
+        <v>3.605835956805791</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4.879529593684516</v>
+        <v>4.966152429196413</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>5.15063363273724</v>
+        <v>5.238241689755391</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>5.466792434904754</v>
+        <v>5.553558844256514</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>5.053584762215081</v>
+        <v>5.140571939837187</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>5.227635375997274</v>
+        <v>5.314801003457859</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>5.908932840686795</v>
+        <v>5.995808663451946</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>6.468119220865681</v>
+        <v>6.554747496675787</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>6.482894540116625</v>
+        <v>6.570340863593493</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>7.151098210097693</v>
+        <v>7.238680948696022</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>7.705018359853121</v>
+        <v>7.792225428619929</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>7.256956678479355</v>
+        <v>7.344300152140839</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 19.86</t>
+          <t>X &gt; 19.85</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>907</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-3.164521280991607</v>
+        <v>-3.144705988845423</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.426315777669053</v>
+        <v>-2.376946954780685</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.88187482372247</v>
+        <v>-1.830401505465474</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.05020561539870272</v>
+        <v>0.1027304728867193</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.01558558506554419</v>
+        <v>0.09770075006380807</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.084828535949818</v>
+        <v>1.166695602092823</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.296297199507649</v>
+        <v>2.379311416548674</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.1201924542897</v>
+        <v>3.203635804210151</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.389940660840836</v>
+        <v>2.473347903434664</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.269678723049623</v>
+        <v>3.354235976020007</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>2.551830749184667</v>
+        <v>2.636013369008836</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>3.154679253977527</v>
+        <v>3.239292631492482</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>3.352898254907579</v>
+        <v>3.439173563533828</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>4.895529183438619</v>
+        <v>4.982152018950515</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>5.449190080007824</v>
+        <v>5.536798137025976</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>5.603404316651385</v>
+        <v>5.690170726003146</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>5.248759244920663</v>
+        <v>5.335746422542769</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>5.253993674502446</v>
+        <v>5.341159301963032</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>6.352203526053849</v>
+        <v>6.439079348819</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>7.311071965667104</v>
+        <v>7.39770024147721</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>6.988214916517215</v>
+        <v>7.075661239994083</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>7.573754039435393</v>
+        <v>7.661336778033721</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>8.179365171473343</v>
+        <v>8.266572240240151</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>7.882889346872474</v>
+        <v>7.970232820533958</v>
       </c>
     </row>
     <row r="18">
@@ -4168,243 +4168,243 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.875322091442023</v>
+        <v>-2.72700899332753</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.061641949329839</v>
+        <v>-1.886851065828779</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.538414708389148</v>
+        <v>-1.366645571778825</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.6271608847695589</v>
+        <v>0.7924630719638017</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.9162303664921438</v>
+        <v>1.10941411377685</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.9725545990887596</v>
+        <v>1.165831997002165</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.555479706708759</v>
+        <v>2.743752764808939</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.062179443212393</v>
+        <v>3.248831137288242</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.794802208893508</v>
+        <v>1.854286987610259</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.591417150752712</v>
+        <v>2.647950946038513</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.211401164280744</v>
+        <v>2.138720770968071</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.110231474346158</v>
+        <v>3.165454396240698</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>3.817868209363034</v>
+        <v>3.739420266721396</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>5.036232381947023</v>
+        <v>4.9543727218675</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>5.293334229352354</v>
+        <v>5.210067544391372</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>5.234112537181637</v>
+        <v>5.282261254846119</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>4.838194527221773</v>
+        <v>4.887247512124517</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>4.994955478274157</v>
+        <v>5.043503414047464</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>5.996476978030039</v>
+        <v>6.17323291507622</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>6.052680282597088</v>
+        <v>6.229530422172189</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>5.771096171676355</v>
+        <v>5.948080859950274</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>6.349564056925892</v>
+        <v>6.524976412901502</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>6.886194543951511</v>
+        <v>7.06054773112767</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>6.548445781121515</v>
+        <v>6.72361887216028</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 21.09</t>
+          <t>X &gt; 21.08</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>649</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.583620803112815</v>
+        <v>-3.563805510966631</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.485701517412828</v>
+        <v>-3.436332694524459</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-3.230909807575166</v>
+        <v>-3.179436489318171</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.479584087358326</v>
+        <v>-1.427059229870309</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.4582160230398813</v>
+        <v>-0.3761008580416174</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.5791681479485646</v>
+        <v>-0.4973010818055599</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.6508176813616799</v>
+        <v>0.7338318984027055</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.913009153035794</v>
+        <v>1.996452502956245</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.338199622554477</v>
+        <v>1.421606865148306</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.104965985448054</v>
+        <v>2.189523238418438</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.379400260756192</v>
+        <v>2.463582880580361</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.024719329201382</v>
+        <v>3.109332706716337</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>3.286644175609936</v>
+        <v>3.372919484236185</v>
       </c>
       <c r="P19" s="4" t="n">
+        <v>4.846755862026882</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>4.804945384168967</v>
+      </c>
+      <c r="R19" s="4" t="n">
+        <v>4.012583461736</v>
+      </c>
+      <c r="S19" s="4" t="n">
+        <v>3.878666324758527</v>
+      </c>
+      <c r="T19" s="4" t="n">
+        <v>3.927908825868009</v>
+      </c>
+      <c r="U19" s="4" t="n">
         <v>4.760133026514985</v>
       </c>
-      <c r="Q19" s="4" t="n">
-        <v>4.717337327150815</v>
-      </c>
-      <c r="R19" s="4" t="n">
-        <v>3.92581705238424</v>
-      </c>
-      <c r="S19" s="4" t="n">
-        <v>3.791679147136421</v>
-      </c>
-      <c r="T19" s="4" t="n">
-        <v>3.840743198407424</v>
-      </c>
-      <c r="U19" s="4" t="n">
-        <v>4.673257203749834</v>
-      </c>
       <c r="V19" s="4" t="n">
-        <v>4.552184150811577</v>
+        <v>4.638812426621683</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>4.162903140109457</v>
+        <v>4.250349463586325</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>4.703253583301539</v>
+        <v>4.790836321899867</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>5.286270375476441</v>
+        <v>5.37347744424325</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>5.056218512427819</v>
+        <v>5.143561986089303</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 21.71</t>
+          <t>X &gt; 21.7</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>579</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.919729763091105</v>
+        <v>-3.899914470944921</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.902367518780686</v>
+        <v>-2.852998695892317</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.788086918102579</v>
+        <v>-2.736613599845583</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.29311147504923</v>
+        <v>-2.240586617561213</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.794934396730241</v>
+        <v>-1.712819231731977</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.953143255128204</v>
+        <v>-1.871276188985199</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.4809886581376475</v>
+        <v>-0.3979744410966219</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.7947749093075771</v>
+        <v>0.8782182592280279</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.8362981985489029</v>
+        <v>0.9197054411427317</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.443925085538268</v>
+        <v>1.528482338508653</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.545647789171113</v>
+        <v>1.629830408995282</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.648160201434742</v>
+        <v>2.732773578949697</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3.077740348545049</v>
+        <v>3.164015657171298</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>4.410718090290537</v>
+        <v>4.497340925802433</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>3.924301142879017</v>
+        <v>4.011909199897168</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>3.137837139085988</v>
+        <v>3.224603548437749</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>3.349122377188763</v>
+        <v>3.436109554810869</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>3.071391651853808</v>
+        <v>3.158557279314394</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>3.632995980824177</v>
+        <v>3.719871803589328</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>3.30195462272134</v>
+        <v>3.388582898531446</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>2.758590407088548</v>
+        <v>2.846036730565416</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>3.546165888934489</v>
+        <v>3.633748627532817</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>4.511862557949279</v>
+        <v>4.599069626716087</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>4.608605471506635</v>
+        <v>4.695948945168119</v>
       </c>
     </row>
     <row r="21">
@@ -4414,243 +4414,243 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-3.363632702607852</v>
+        <v>-3.344989125266288</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-4.124002635660247</v>
+        <v>-4.074243241170343</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-4.177987566198482</v>
+        <v>-3.934353019984371</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-3.505854511010853</v>
+        <v>-3.266636427987265</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.079156083147581</v>
+        <v>-2.813472265426064</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.684021006115735</v>
+        <v>-3.41546071443716</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.27889901912193</v>
+        <v>-2.017784151779189</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.5773415769524561</v>
+        <v>-0.3236090087610606</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.9318578916715268</v>
+        <v>-0.6765991444005977</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.0762546397372077</v>
+        <v>0.3256331085569926</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.3506889150453461</v>
+        <v>0.5996927507189156</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.259627565787753</v>
+        <v>1.504375299933649</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.115001587622324</v>
+        <v>2.353599820848729</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.477733600131671</v>
+        <v>3.710430214619102</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>3.412664486985456</v>
+        <v>3.644002893369908</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>2.423734640753253</v>
+        <v>2.660480545095929</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>2.883656141446025</v>
+        <v>3.118279384449814</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>2.184577581845772</v>
+        <v>2.421722704297274</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>2.796798371425929</v>
+        <v>3.032091402775841</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>2.587852124388604</v>
+        <v>2.824459895189626</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>1.84646810677561</v>
+        <v>2.084675068446479</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>2.562564938165842</v>
+        <v>2.797783742145853</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>3.629494528400208</v>
+        <v>3.861213089736395</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>3.751545672262459</v>
+        <v>3.982619495290244</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 22.94</t>
+          <t>X &gt; 22.93</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>449</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-3.772020980188394</v>
+        <v>-3.75220568804221</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-4.359068458500886</v>
+        <v>-4.309699635612517</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-3.572020510695602</v>
+        <v>-3.520547192438606</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.172440323266912</v>
+        <v>-3.119915465778895</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-3.315103954103947</v>
+        <v>-3.232988789105683</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-3.350606818371794</v>
+        <v>-3.26873975222879</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.119248310175756</v>
+        <v>-2.03623409313473</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.1707173956033543</v>
+        <v>-0.08727404568290353</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.020062703243994</v>
+        <v>-0.9366554606501651</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.2351083451136091</v>
+        <v>-0.1505510921432247</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4847602286355013</v>
+        <v>0.5689428484596704</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.54188296281967</v>
+        <v>1.626496340334626</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.421513307836669</v>
+        <v>2.507788616462918</v>
       </c>
       <c r="P22" s="4" t="n">
+        <v>4.29116408300073</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>4.078455083861151</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>2.891104812040226</v>
+      </c>
+      <c r="S22" s="4" t="n">
+        <v>3.648056271944711</v>
+      </c>
+      <c r="T22" s="4" t="n">
+        <v>3.320498418903043</v>
+      </c>
+      <c r="U22" s="4" t="n">
         <v>4.204541247488834</v>
       </c>
-      <c r="Q22" s="4" t="n">
-        <v>3.990847026842999</v>
-      </c>
-      <c r="R22" s="4" t="n">
-        <v>2.804338402688465</v>
-      </c>
-      <c r="S22" s="4" t="n">
-        <v>3.561069094322605</v>
-      </c>
-      <c r="T22" s="4" t="n">
-        <v>3.233332791442457</v>
-      </c>
-      <c r="U22" s="4" t="n">
-        <v>4.117665424723683</v>
-      </c>
       <c r="V22" s="4" t="n">
-        <v>3.636607333985289</v>
+        <v>3.723235609795395</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>2.647808819911511</v>
+        <v>2.735255143388379</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>3.685412189483401</v>
+        <v>3.772994928081729</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>4.62841401945844</v>
+        <v>4.715621088225248</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>4.552445361340489</v>
+        <v>4.639788835001973</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 23.56</t>
+          <t>X &gt; 23.55</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>407</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.537812282728027</v>
+        <v>-3.517996990581842</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-4.639243348920765</v>
+        <v>-4.589874526032396</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-3.622364436317923</v>
+        <v>-3.570891118060928</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-3.353569012190704</v>
+        <v>-3.301044154702687</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.981849055147492</v>
+        <v>-2.899733890149228</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-3.040335015895096</v>
+        <v>-2.958467949752091</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.356428393681007</v>
+        <v>-1.273414176639982</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.5762332399887029</v>
+        <v>0.6596765899091537</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.1193442078707108</v>
+        <v>-0.03593696527688195</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.8264918256179641</v>
+        <v>0.9110490785883485</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.592326592326593</v>
+        <v>1.676509212150762</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.278748396789773</v>
+        <v>3.363361774304728</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4.365226610124573</v>
+        <v>4.451501918750822</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>6.600802663794788</v>
+        <v>6.687425499306684</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>5.69597389900774</v>
+        <v>5.783581956025891</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>4.817000994415643</v>
+        <v>4.903767403767404</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>5.174263580568322</v>
+        <v>5.261250758190428</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>4.823544181208412</v>
+        <v>4.910709808668997</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>5.531125858228656</v>
+        <v>5.618001680993807</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>5.226818723751244</v>
+        <v>5.31344699956135</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>3.946353771017705</v>
+        <v>4.033800094494573</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>5.098872622988374</v>
+        <v>5.186455361586702</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>6.110823742402694</v>
+        <v>6.198030811169502</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>6.034855084284743</v>
+        <v>6.122198557946227</v>
       </c>
     </row>
     <row r="24">
@@ -4660,243 +4660,243 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.674746912620407</v>
+        <v>-2.660454956569225</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-3.884147664247614</v>
+        <v>-4.115679934190744</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.7890599410416</v>
+        <v>-3.032690579860386</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-3.221375358870297</v>
+        <v>-3.4655325544852</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.459995575547538</v>
+        <v>-2.680874847760769</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.991091149749813</v>
+        <v>-2.213796616845464</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.074046139467768</v>
+        <v>-1.30507303182825</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.7459048321955</v>
+        <v>1.778060061233802</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.787428121436825</v>
+        <v>1.819547243148506</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.421813139249132</v>
+        <v>2.447191791201647</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.977937555402342</v>
+        <v>3.001363478181496</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.38889823933399</v>
+        <v>4.403286343641064</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.672524945591931</v>
+        <v>4.680684500874577</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>7.267999950710397</v>
+        <v>7.260726072607255</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>6.327181290778512</v>
+        <v>6.322470730208771</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>4.668888733627334</v>
+        <v>4.675961293608353</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>4.816440969224587</v>
+        <v>4.822156201448806</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>4.711421815564925</v>
+        <v>4.717315497627624</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>5.490983282874815</v>
+        <v>5.493430968187802</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>5.396386498952829</v>
+        <v>5.400164733337903</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>4.853022283320037</v>
+        <v>4.857618565371872</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>5.903800470169749</v>
+        <v>5.902220783234476</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>7.023721275018538</v>
+        <v>7.017031630170308</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>6.666062476055515</v>
+        <v>6.661087332129107</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 24.79</t>
+          <t>X &gt; 24.78</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>305</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.201646012135527</v>
+        <v>-1.181830719989343</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-4.516796013358672</v>
+        <v>-4.467427190470303</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.366755623332061</v>
+        <v>-1.315282305075065</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.75289232954681</v>
+        <v>-1.700367472058794</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.151059994850236</v>
+        <v>-0.06894482985197214</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.29171456235661</v>
+        <v>-0.2098474962136052</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.4090726922269425</v>
+        <v>-0.326058475185917</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.918844107189734</v>
+        <v>3.002287457110185</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.6652854292179455</v>
+        <v>0.7486926718117743</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.8748263001819439</v>
+        <v>0.9593835531523283</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.477129427949095</v>
+        <v>1.561312047773264</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.493031234023434</v>
+        <v>3.577644611538389</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.351813793433067</v>
+        <v>3.438089102059315</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>6.409075914690995</v>
+        <v>6.495698750202891</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>5.749947395604181</v>
+        <v>5.837555452622333</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>4.705831702918481</v>
+        <v>4.792598112270241</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>4.899562650129681</v>
+        <v>4.986549827751787</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>4.79454349647002</v>
+        <v>4.881709123930605</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>5.666462387007819</v>
+        <v>5.75333820977297</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>5.85355574393089</v>
+        <v>5.940184019740997</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>5.638060380757103</v>
+        <v>5.725506704233972</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>6.545684561603601</v>
+        <v>6.633267300201929</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>7.476272648835199</v>
+        <v>7.563479717602007</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>7.400303990717248</v>
+        <v>7.487647464378732</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 25.41</t>
+          <t>X &gt; 25.4</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>251</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-2.664646469323174</v>
+        <v>-2.644831177176989</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-4.224195921921144</v>
+        <v>-4.174827099032775</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.680255721300846</v>
+        <v>-1.62878240304385</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.597448530970624</v>
+        <v>-1.544923673482607</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.224421684987796</v>
+        <v>1.30653684998606</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.411635969940434</v>
+        <v>1.493503036083439</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.833759258658041</v>
+        <v>1.916773475699067</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.539182426045457</v>
+        <v>5.622625775965908</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.385486591780804</v>
+        <v>4.468893834374633</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.21301453086577</v>
+        <v>3.297571783836155</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.089042431671913</v>
+        <v>3.173225051496082</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.801894143043093</v>
+        <v>4.886507520558048</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.473882894079665</v>
+        <v>4.560158202705914</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>8.236520235767337</v>
+        <v>8.323143071279233</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>6.780578967676547</v>
+        <v>6.868187024694699</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>6.578994788281939</v>
+        <v>6.665761197633699</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>5.648044134030144</v>
+        <v>5.73503131165225</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>7.136650478378449</v>
+        <v>7.223816105839035</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>8.946457162006176</v>
+        <v>9.033332984771327</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>9.133550518929248</v>
+        <v>9.220178794739354</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>8.191779928794467</v>
+        <v>8.279226252271336</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>8.912610301267897</v>
+        <v>9.000193039866225</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>9.18746068358147</v>
+        <v>9.274667752348279</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>8.713085650961517</v>
+        <v>8.800429124623001</v>
       </c>
     </row>
     <row r="27">
@@ -4909,732 +4909,732 @@
         <v>221</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.886906749469553</v>
+        <v>-3.867091457323369</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-6.061191829692774</v>
+        <v>-6.011823006804406</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.428917184047137</v>
+        <v>-3.377443865790141</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-2.332967991589683</v>
+        <v>-2.280443134101667</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.4359053327331779</v>
+        <v>-0.353790167734914</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.108775015567872</v>
+        <v>1.190642081710877</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.598122619693534</v>
+        <v>2.681136836734559</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>6.391880232106274</v>
+        <v>6.475323582026725</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5.980914833564796</v>
+        <v>6.064322076158625</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.659337834934554</v>
+        <v>5.743895087904939</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.028794734677085</v>
+        <v>5.112977354501254</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>7.012058012452329</v>
+        <v>7.096671389967284</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.792211390050525</v>
+        <v>6.878486698676774</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>8.380739737849517</v>
+        <v>8.467362573361413</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>7.721611218762703</v>
+        <v>7.809219275780855</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>7.864351100589282</v>
+        <v>7.951117509941042</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>6.825235819775841</v>
+        <v>6.912222997397947</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>7.625194041681802</v>
+        <v>7.712359669142387</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>10.10381866621558</v>
+        <v>10.19069448898073</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>10.74340071092146</v>
+        <v>10.83002898673156</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>9.74754780750586</v>
+        <v>9.834994130982729</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>10.57654280654092</v>
+        <v>10.66412554513925</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>10.85139318885449</v>
+        <v>10.9386002576213</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>10.32293584295373</v>
+        <v>10.41027931661521</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 26.64</t>
+          <t>X &gt; 26.63</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-3.117184144708581</v>
+        <v>-3.373467434287583</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-7.28586229988754</v>
+        <v>-7.451559740658787</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-3.83468149646108</v>
+        <v>-3.541985206802082</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-4.548687055134842</v>
+        <v>-4.254939226244822</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-2.196676530844535</v>
+        <v>-1.916932907348247</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.1644507975863689</v>
+        <v>0.4090707119042207</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.0217897454067</v>
+        <v>1.241400102880178</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>5.634453515600285</v>
+        <v>5.776022882726032</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.589020283102471</v>
+        <v>4.747991348063202</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>5.988867640167683</v>
+        <v>6.648872463470553</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.263301915475822</v>
+        <v>6.38817274734371</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>6.527600015206616</v>
+        <v>7.178942060473261</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>6.48973253897833</v>
+        <v>6.590539351905896</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>9.529175700863483</v>
+        <v>10.1127759834807</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>6.152655877428842</v>
+        <v>6.780835894456295</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>6.747884447038224</v>
+        <v>7.375222816399287</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>6.070268280920843</v>
+        <v>6.706546321133047</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>6.508727388130744</v>
+        <v>7.136464975600632</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>9.985778138967895</v>
+        <v>9.491393789680039</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>11.25982801763011</v>
+        <v>10.74775831622561</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>10.17298554112774</v>
+        <v>9.670452789970803</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>11.18395968633632</v>
+        <v>10.66412554513925</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>10.91533180778033</v>
+        <v>10.40384089933254</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>9.752406627923236</v>
+        <v>9.258489929531713</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 27.26</t>
+          <t>X &gt; 27.25</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>158</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.394839620768032</v>
+        <v>-2.375024328621848</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-9.088283873910655</v>
+        <v>-9.038915051022286</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-5.465116279069768</v>
+        <v>-5.413642960812773</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-5.546210445338467</v>
+        <v>-5.49368558785045</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-2.747034263370672</v>
+        <v>-2.664919098372408</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.02817440879778133</v>
+        <v>0.05369265734522344</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.4645525412239735</v>
+        <v>0.547566758264999</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.616291710426914</v>
+        <v>4.699735060347365</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.923637784478373</v>
+        <v>6.007045027072202</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.048306275280524</v>
+        <v>7.132863528250908</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>7.322740550588662</v>
+        <v>7.406923170412831</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.942294566665069</v>
+        <v>9.026907944180024</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>8.450381961102707</v>
+        <v>8.536657269728956</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>10.12768973498567</v>
+        <v>10.21431257049757</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>6.936915646278607</v>
+        <v>7.024523703296758</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>6.899232823482912</v>
+        <v>6.985999232834672</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>5.499272133424981</v>
+        <v>5.586259311047087</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>6.027164372170368</v>
+        <v>6.114329999630954</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>9.407902519815444</v>
+        <v>9.494778342580595</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>10.86081866154864</v>
+        <v>10.94744693735875</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>10.95036583832091</v>
+        <v>11.03781216179778</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>13.40602903141062</v>
+        <v>13.49361177000895</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>14.31379080612924</v>
+        <v>14.40099787489605</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>14.87073354041635</v>
+        <v>14.95807701407784</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 27.87</t>
+          <t>X &gt; 27.86</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>132</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.660662405578151</v>
+        <v>-3.640847113431967</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-9.328023037700454</v>
+        <v>-9.278654214812086</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-6.222692036645526</v>
+        <v>-6.171218718388531</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-6.936697595319288</v>
+        <v>-6.884172737831271</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-3.51419958749802</v>
+        <v>-3.432084422499756</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.054258029818115</v>
+        <v>-0.9723909636751102</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.202949165696552</v>
+        <v>1.285963382737577</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2.439460103215566</v>
+        <v>2.522903453136017</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.23855915003265</v>
+        <v>3.321966392626479</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>5.494796493922628</v>
+        <v>5.579353746893013</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.011655011655009</v>
+        <v>5.095837631479178</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>7.005202123243507</v>
+        <v>7.089815500758462</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>6.637953882851846</v>
+        <v>6.724229191478095</v>
       </c>
       <c r="P30" s="4" t="n">
+        <v>8.775877587758771</v>
+      </c>
+      <c r="Q30" s="4" t="n">
+        <v>5.087431259875196</v>
+      </c>
+      <c r="R30" s="4" t="n">
+        <v>5.681818181818187</v>
+      </c>
+      <c r="S30" s="4" t="n">
+        <v>4.032749529689191</v>
+      </c>
+      <c r="T30" s="4" t="n">
+        <v>3.927908825868009</v>
+      </c>
+      <c r="U30" s="4" t="n">
         <v>8.689254752246875</v>
       </c>
-      <c r="Q30" s="4" t="n">
-        <v>4.999823202857044</v>
-      </c>
-      <c r="R30" s="4" t="n">
-        <v>5.595051772466427</v>
-      </c>
-      <c r="S30" s="4" t="n">
-        <v>3.945762352067085</v>
-      </c>
-      <c r="T30" s="4" t="n">
-        <v>3.840743198407424</v>
-      </c>
-      <c r="U30" s="4" t="n">
-        <v>8.602378929481723</v>
-      </c>
       <c r="V30" s="4" t="n">
-        <v>10.30462380155632</v>
+        <v>10.39125207736643</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>10.51883534349928</v>
+        <v>10.60628166697615</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>12.715580239696</v>
+        <v>12.80316297829433</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>12.99043062200958</v>
+        <v>13.07763769077638</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>15.18718923661889</v>
+        <v>15.27453271028038</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 28.49</t>
+          <t>X &gt; 28.48</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>119</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-1.55982206944369</v>
+        <v>-1.540006777297506</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-6.966169205258389</v>
+        <v>-6.91680038237002</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-6.725620480750443</v>
+        <v>-6.674147162493448</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-8.279962173877983</v>
+        <v>-8.227437316389967</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-3.603326147212812</v>
+        <v>-3.521210982214548</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-2.575775727806395</v>
+        <v>-2.49390866166339</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.8278631592334236</v>
+        <v>-0.7448489421923981</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.414504666495425</v>
+        <v>1.497948016415876</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1.456027955736751</v>
+        <v>1.53943519833058</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>4.043306807138826</v>
+        <v>4.127864060109211</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3.477404947993186</v>
+        <v>3.561587567817355</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>5.719233190215739</v>
+        <v>5.803846567730695</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>5.434745326702114</v>
+        <v>5.521020635328362</v>
       </c>
       <c r="P31" s="4" t="n">
+        <v>8.6612862966969</v>
+      </c>
+      <c r="Q31" s="4" t="n">
+        <v>4.641798461301214</v>
+      </c>
+      <c r="R31" s="4" t="n">
+        <v>5.236185383244205</v>
+      </c>
+      <c r="S31" s="4" t="n">
+        <v>4.261932111812946</v>
+      </c>
+      <c r="T31" s="4" t="n">
+        <v>4.157091407991764</v>
+      </c>
+      <c r="U31" s="4" t="n">
         <v>8.574663461185004</v>
       </c>
-      <c r="Q31" s="4" t="n">
-        <v>4.554190404283062</v>
-      </c>
-      <c r="R31" s="4" t="n">
-        <v>5.149418973892445</v>
-      </c>
-      <c r="S31" s="4" t="n">
-        <v>4.17494493419084</v>
-      </c>
-      <c r="T31" s="4" t="n">
-        <v>4.069925780531179</v>
-      </c>
-      <c r="U31" s="4" t="n">
-        <v>8.487787638419853</v>
-      </c>
       <c r="V31" s="4" t="n">
-        <v>9.515217129796703</v>
+        <v>9.601845405606809</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>9.812189048617689</v>
+        <v>9.899635372094558</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>12.25721507544848</v>
+        <v>12.34479781404681</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>11.69172932330827</v>
+        <v>11.77893639207508</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>13.29643293409788</v>
+        <v>13.38377640775936</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 29.11</t>
+          <t>X &gt; 29.1</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-3.193372685951985</v>
+        <v>-3.640847113431967</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-11.03433852906267</v>
+        <v>-10.45710539326326</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-5.932405998695934</v>
+        <v>-6.339568886738697</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-9.450149875126705</v>
+        <v>-9.830300683959216</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-4.208054019670215</v>
+        <v>-4.610535600950939</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-4.020839734717576</v>
+        <v>-3.497643488927629</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.990197251748938</v>
+        <v>-1.491814395040201</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.5349004883755697</v>
+        <v>1.007751937984501</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.5764237776168954</v>
+        <v>1.049239119899205</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>3.540675848213198</v>
+        <v>3.980027147566418</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>2.880530684268997</v>
+        <v>3.328160863802417</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.405088840887224</v>
+        <v>5.827189238132192</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.214844282172152</v>
+        <v>5.629953097201998</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>9.6663150751016</v>
+        <v>10.03850385038504</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>5.268868799005432</v>
+        <v>5.676656849100787</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>5.864097368614814</v>
+        <v>6.271043771043779</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>5.729959463366995</v>
+        <v>6.137126634066306</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>5.624940309707334</v>
+        <v>6.032285930245123</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>10.51401869158878</v>
+        <v>10.87780694079907</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>11.63569148776418</v>
+        <v>11.99057867669302</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>11.09232727213139</v>
+        <v>11.44803250872699</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>13.82008321335784</v>
+        <v>14.14996432509567</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>13.16035415641908</v>
+        <v>13.4985131116518</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>14.01896493755346</v>
+        <v>14.34860678435445</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 29.73</t>
+          <t>X &gt; 29.71</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>99</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.145510890426635</v>
+        <v>-2.125695598280451</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-8.570447280124696</v>
+        <v>-8.521078457236328</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-2.939863753817235</v>
+        <v>-2.88839043556024</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-6.684172342794035</v>
+        <v>-6.631647485306019</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.02115394785550961</v>
+        <v>0.1032691128537735</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.811833787393873</v>
+        <v>-1.729966721250868</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.4453734081207941</v>
+        <v>0.5283876251618196</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>3.197035860791324</v>
+        <v>3.280479210711775</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3.23855915003265</v>
+        <v>3.321966392626479</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>5.494796493922628</v>
+        <v>5.579353746893013</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>5.769230769230766</v>
+        <v>5.853413389054936</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.510252628294012</v>
+        <v>7.594866005808967</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>6.385428630326601</v>
+        <v>6.471703938952849</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>9.19430525729738</v>
+        <v>9.280928092809276</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>4.494772697806539</v>
+        <v>4.58238075482469</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>5.090001267415921</v>
+        <v>5.176767676767682</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>4.955863362168103</v>
+        <v>5.042850539790209</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>4.850844208508441</v>
+        <v>4.938009835969027</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>10.11753044463325</v>
+        <v>10.2044062673984</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>11.31472481165734</v>
+        <v>11.40135308746744</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>10.77136059602454</v>
+        <v>10.85880691950141</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>14.73578225989802</v>
+        <v>14.82336499849635</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>15.0106326422116</v>
+        <v>15.09783971097841</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>14.93466398409365</v>
+        <v>15.02200745775513</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 30.34</t>
+          <t>X &gt; 30.33</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>88</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.2515714964872444</v>
+        <v>-0.2317562043410604</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-4.02499273467015</v>
+        <v>-3.975623911781781</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.489429175475692</v>
+        <v>2.540902493732688</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.4973036559253501</v>
+        <v>-0.4447787984373335</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>5.955497382198949</v>
+        <v>6.037612547197213</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2.733620758060681</v>
+        <v>2.815487824203686</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>4.233252195999583</v>
+        <v>4.316266413040609</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>7.363702527457981</v>
+        <v>7.447145877378432</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>7.405225816699307</v>
+        <v>7.488633059293136</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>10.04025103937717</v>
+        <v>10.12480829234755</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>9.17832167832168</v>
+        <v>9.262504298145849</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>11.17186878991018</v>
+        <v>11.25648216742513</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>11.18340842830639</v>
+        <v>11.26968373693264</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>14.37107293406506</v>
+        <v>14.45769576957696</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>8.030126233160061</v>
+        <v>8.117734290178213</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>8.625354802769444</v>
+        <v>8.712121212121204</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>7.354853261157999</v>
+        <v>7.441840438780105</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>7.249834107498337</v>
+        <v>7.336999734958923</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>13.14783347493628</v>
+        <v>13.23470929770144</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>14.47129046822298</v>
+        <v>14.55791874403309</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>13.92792625259019</v>
+        <v>14.01537257606706</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>18.39739842151418</v>
+        <v>18.4849811601125</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>18.67224880382775</v>
+        <v>18.75945587259456</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>18.5962801457098</v>
+        <v>18.68362361937128</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 30.96</t>
+          <t>X &gt; 30.95</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.411801362537794</v>
+        <v>1.431616654683978</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-3.300355053510728</v>
+        <v>-3.25098623062236</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>3.955173576002693</v>
+        <v>4.006646894259688</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3.241168017328931</v>
+        <v>3.293692874816948</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>7.223613324227927</v>
+        <v>7.30572848922619</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>4.512276884542899</v>
+        <v>4.594143950685904</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>5.188456412073357</v>
+        <v>5.271470629114383</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>10.70691728371623</v>
+        <v>10.79036063363668</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>9.299165210638698</v>
+        <v>9.382572453232527</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>12.87292561118218</v>
+        <v>12.95748286415257</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>10.24880916185265</v>
+        <v>10.33299178167682</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>12.86817972535154</v>
+        <v>12.95279310286649</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>11.74335572738413</v>
+        <v>11.82963103601038</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>15.86975541100842</v>
+        <v>15.95637824652032</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>9.413525442646232</v>
+        <v>9.501133499664384</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>10.00875401225561</v>
+        <v>10.09552042160738</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>6.976065382370109</v>
+        <v>7.063052559992215</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>6.871046228710448</v>
+        <v>6.958211856171033</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>12.88432886360558</v>
+        <v>12.97120468637073</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>14.52069758284748</v>
+        <v>14.60732585865759</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>13.97733336721469</v>
+        <v>14.06477969069156</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>19.6984524399595</v>
+        <v>19.78603517855783</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>19.97330282227308</v>
+        <v>20.06050989103989</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>19.89733416415513</v>
+        <v>19.98467763781661</v>
       </c>
     </row>
   </sheetData>
@@ -5831,76 +5831,76 @@
         <v>67</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>13.50351669889946</v>
+        <v>13.52333199104564</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>16.12426099667314</v>
+        <v>16.17362981956151</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>17.66921207913919</v>
+        <v>17.72068539739619</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>13.97013189359976</v>
+        <v>14.02265675108778</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>9.127139173243727</v>
+        <v>9.20925433824199</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.8068907716292</v>
+        <v>10.8887578377722</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10.03379493684083</v>
+        <v>10.11680915388185</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>11.24769167264116</v>
+        <v>11.33113502256161</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.304140335016818</v>
+        <v>8.387547577610647</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>7.530074648603772</v>
+        <v>7.614631901574157</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>6.311971610479077</v>
+        <v>6.396154230303246</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>3.047716822474619</v>
+        <v>3.132330199989575</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.4303555110743673</v>
+        <v>0.516630819700616</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-2.776145519123538</v>
+        <v>-2.689522683611642</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-4.927811351643186</v>
+        <v>-4.840203294625034</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-2.84004546860097</v>
+        <v>-2.753279059249209</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>2.995965879882561</v>
+        <v>3.082953057504668</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>4.383484039655734</v>
+        <v>4.470649667116319</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>1.614590598409819</v>
+        <v>1.70146642117497</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>4.786758582198566</v>
+        <v>4.873386858008672</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>1.258319739700099</v>
+        <v>1.345766063176967</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>2.674874676602379</v>
+        <v>2.762457415200707</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-3.020424194815398</v>
+        <v>-2.933217126048589</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-1.603855539500508</v>
+        <v>-1.516512065839024</v>
       </c>
     </row>
     <row r="7">
@@ -5913,76 +5913,76 @@
         <v>125</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10.33933759442185</v>
+        <v>10.35915288656803</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>9.97500726532985</v>
+        <v>10.02437608821822</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>9.334883720930229</v>
+        <v>9.386357039187224</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.82087816225647</v>
+        <v>7.873403019744487</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6.655497382198952</v>
+        <v>6.737612547197216</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>9.242711667151596</v>
+        <v>9.324578733294601</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6.869615832363216</v>
+        <v>6.952630049404242</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>8.190975254730724</v>
+        <v>8.274418604651174</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>6.632498543972041</v>
+        <v>6.71590578656587</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.058432857558998</v>
+        <v>5.142990110529382</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3.732867132867135</v>
+        <v>3.817049752691304</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.853686971728351</v>
+        <v>1.938300349243306</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.07113702623906448</v>
+        <v>0.01513828238718418</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.2925634295713024</v>
+        <v>-0.2059405940594061</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-1.751691948658113</v>
+        <v>-1.664083891639962</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.3564633790487335</v>
+        <v>-0.2696969696969731</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>4.309398715703452</v>
+        <v>4.396385893325558</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>5.004379562043788</v>
+        <v>5.091545189504373</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>3.620560747663554</v>
+        <v>3.707436570428705</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>5.407654104586619</v>
+        <v>5.494282380396726</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>2.464289888953829</v>
+        <v>2.551736212430697</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>3.988307512423269</v>
+        <v>4.075890251021598</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>1.06315789473684</v>
+        <v>1.150364963503648</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.9871892366188888</v>
+        <v>1.074532710280373</v>
       </c>
     </row>
     <row r="8">
@@ -5995,76 +5995,76 @@
         <v>206</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5.077201672091746</v>
+        <v>5.09701696423793</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5.19830823620363</v>
+        <v>5.247677059091998</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3.758184691804011</v>
+        <v>3.809658010061007</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.6169946671108377</v>
+        <v>0.6695195245988543</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.7370507802571993</v>
+        <v>0.8191659452554632</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.40970195841372</v>
+        <v>1.491569024556725</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-2.761452128801835</v>
+        <v>-2.67843791176081</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.0983451336188</v>
+        <v>-1.014901783698349</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.542258737581356</v>
+        <v>-1.458851494987528</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.345450637586637</v>
+        <v>-1.260893384616253</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.071016362278499</v>
+        <v>-0.9868337424543299</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.835633416621164</v>
+        <v>-1.751020039106209</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-2.475020521384693</v>
+        <v>-2.388745212758444</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-2.211010031513048</v>
+        <v>-2.124387196001152</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-3.355575443803744</v>
+        <v>-3.267967386785593</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-2.760346874194362</v>
+        <v>-2.673580464842601</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.01813657978111394</v>
+        <v>0.10512375740322</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.398554319325342</v>
+        <v>0.4857199467859274</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.8415751746665521</v>
+        <v>-0.7546993519014009</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.1690449245395982</v>
+        <v>-0.08241664872949173</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-2.168719819784037</v>
+        <v>-2.081273496307169</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-1.759265303110716</v>
+        <v>-1.671682564512388</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-3.911599386816555</v>
+        <v>-3.824392318049746</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-3.016694258526741</v>
+        <v>-2.929350784865257</v>
       </c>
     </row>
     <row r="9">
@@ -6074,79 +6074,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.702973958058209</v>
+        <v>2.148626570778553</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.416565706888292</v>
+        <v>3.919112930323486</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.976442162488674</v>
+        <v>2.481093881292495</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.483215824594133</v>
+        <v>0.9786661776392265</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.897055823757391</v>
+        <v>1.43234938930248</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.045309069748988</v>
+        <v>0.8298418911893322</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.06544910270172</v>
+        <v>-2.573685740069443</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.344089680334221</v>
+        <v>-2.851897184822519</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.380488469014978</v>
+        <v>-4.652515266065713</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-5.67403467490854</v>
+        <v>-5.688588836839045</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-5.659340659340664</v>
+        <v>-5.677687089413965</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-6.458001339959964</v>
+        <v>-6.482752282335639</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-6.543864298966341</v>
+        <v>-6.553282770244394</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.9860699230778</v>
+        <v>-5.984887962480457</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-6.385458182424351</v>
+        <v>-6.379873365324173</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-7.088930911516265</v>
+        <v>-6.838118022328551</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-6.963328557023829</v>
+        <v>-6.445719369832339</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-6.548867191202966</v>
+        <v>-6.024244284179836</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-7.891127564024764</v>
+        <v>-7.124142376939723</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-8.742995246062733</v>
+        <v>-7.989928145919059</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-9.546099721435787</v>
+        <v>-8.795632208621932</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-8.84286131874557</v>
+        <v>-8.082004485820512</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-9.866712235133285</v>
+        <v>-9.123319247022664</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-10.2024211529915</v>
+        <v>-9.462309394982782</v>
       </c>
     </row>
     <row r="10">
@@ -6159,76 +6159,76 @@
         <v>660</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.248428503512756</v>
+        <v>2.26824379565894</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.9750072653298574</v>
+        <v>1.024376088218226</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.595489781536287</v>
+        <v>0.6469630997932825</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.4215460801677651</v>
+        <v>-0.3690212226797485</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.5767095034110667</v>
+        <v>0.6588246684093306</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.9154389398788609</v>
+        <v>0.9973060060218657</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.069778107030729</v>
+        <v>-0.9867638899897031</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.045388381632925</v>
+        <v>-0.9619450317124745</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2.973562062088568</v>
+        <v>-2.89015481949474</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-3.293082293956161</v>
+        <v>-3.208525040985776</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.321678321678327</v>
+        <v>-3.237495701854158</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.9038887858474</v>
+        <v>-3.819275408332444</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-5.483258238360278</v>
+        <v>-5.39698292973403</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-5.856199793207658</v>
+        <v>-5.769576957695762</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-5.303207100173267</v>
+        <v>-5.215599043155116</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-6.980705803291151</v>
+        <v>-6.893939393939391</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-7.569389163084423</v>
+        <v>-7.482401985462317</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-7.674408316744085</v>
+        <v>-7.587242689283499</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-8.670348343245543</v>
+        <v>-8.583472520480392</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-8.63477013783762</v>
+        <v>-8.548141862027514</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-8.875104050440108</v>
+        <v>-8.787657726963239</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-10.01169248757673</v>
+        <v>-9.924109748978402</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-11.10047846889952</v>
+        <v>-11.01327140013271</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-12.08553803610838</v>
+        <v>-11.9981945624469</v>
       </c>
     </row>
     <row r="11">
@@ -6241,76 +6241,76 @@
         <v>1009</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.641617079060097</v>
+        <v>1.661432371206281</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.673718860969103</v>
+        <v>1.723087683857472</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.8282434830709704</v>
+        <v>0.8797168013279659</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.07505840860577</v>
+        <v>-1.022533551117753</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.3502508834105598</v>
+        <v>-0.2681357184122959</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.1342874847928144</v>
+        <v>0.2161545509358191</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.638808349995557</v>
+        <v>-0.5557941329545315</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.016556955378306</v>
+        <v>-0.933113605457855</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.767897888138961</v>
+        <v>-1.684490645545132</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.343747519051504</v>
+        <v>-2.25919026608112</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.663961410244852</v>
+        <v>-2.579778790420683</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.537789737885127</v>
+        <v>-3.453176360370172</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.365289652601795</v>
+        <v>-4.279014343975547</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.983148166935024</v>
+        <v>-4.896525331423128</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-5.146736547270599</v>
+        <v>-5.059128490252448</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-5.245264171912957</v>
+        <v>-5.158497762561197</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-5.379402077160776</v>
+        <v>-5.29241489953867</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-5.682637286320926</v>
+        <v>-5.59547165886034</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-6.160212294952899</v>
+        <v>-6.073336472187748</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-6.369551049030818</v>
+        <v>-6.282922773220712</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-6.219159070411884</v>
+        <v>-6.131712746935015</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-7.088005668944419</v>
+        <v>-7.00042293034609</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-8.398883730634815</v>
+        <v>-8.311676661868006</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-8.970392527504004</v>
+        <v>-8.88304905384252</v>
       </c>
     </row>
     <row r="12">
@@ -6320,79 +6320,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.629192666885615</v>
+        <v>1.624221877127219</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.337326105909554</v>
+        <v>1.289445078777405</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.1027974384900645</v>
+        <v>-0.07595232900449389</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.324049373975413</v>
+        <v>-1.297257837190877</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.109720009105395</v>
+        <v>-1.124696820994508</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.21236079661653</v>
+        <v>-1.2282171998935</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.840529095173018</v>
+        <v>-1.854922601285665</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.046705904689581</v>
+        <v>-1.987890763540555</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.077646383564193</v>
+        <v>-2.019025222874944</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.304003690664352</v>
+        <v>-2.283589410167785</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.35189338962924</v>
+        <v>-2.372637974251326</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.736000755214278</v>
+        <v>-2.796630660197508</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.166485863448365</v>
+        <v>-3.266197955811798</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.041982034222457</v>
+        <v>-4.140871603500216</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-4.119715204472058</v>
+        <v>-4.177455984663212</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-4.251230820909193</v>
+        <v>-4.269696969696966</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-4.603391981970972</v>
+        <v>-4.581780045539077</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-4.781085554235275</v>
+        <v>-4.719379792287327</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-5.146299717452727</v>
+        <v>-5.086154106920169</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-5.42870953177701</v>
+        <v>-5.40914078056467</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-5.026619201955263</v>
+        <v>-5.004855193250293</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-5.538965214849462</v>
+        <v>-5.517700426327274</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-5.991387559808615</v>
+        <v>-5.971557833291683</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-6.101020370368005</v>
+        <v>-6.120223298459614</v>
       </c>
     </row>
     <row r="13">
@@ -6402,79 +6402,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1684</v>
+        <v>1689</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.8687493591277331</v>
+        <v>0.8885646512739171</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.15147785356514</v>
+        <v>1.200846676453509</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.5089861341144584</v>
+        <v>0.5275335097754663</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.2898403300874648</v>
+        <v>-0.3030675684908104</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.4196498498387413</v>
+        <v>-0.403563923391026</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.3761451389768737</v>
+        <v>-0.3930683255289367</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.4086860544292321</v>
+        <v>-0.4591346564781063</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.7462888962126826</v>
+        <v>-0.7628974636242916</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.763727871122299</v>
+        <v>-0.7469917399358934</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.032422599668145</v>
+        <v>-1.048764895359895</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.7833076014894189</v>
+        <v>-0.8000392278626194</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.205970441148203</v>
+        <v>-1.222077009247258</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.52882024136909</v>
+        <v>-1.57872964214112</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.36660245973097</v>
+        <v>-2.448393424248081</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-2.40021265871728</v>
+        <v>-2.482962947687156</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-2.65889085092558</v>
+        <v>-2.740062967335696</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-2.852235387316092</v>
+        <v>-2.899538501240293</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-3.016461172118433</v>
+        <v>-3.029967812859688</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-3.392346297925563</v>
+        <v>-3.371924754231259</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-3.764383810105322</v>
+        <v>-3.743587442088483</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-3.504174841336628</v>
+        <v>-3.483550939730343</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-4.139806366580295</v>
+        <v>-4.151463212566327</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-4.543963766984227</v>
+        <v>-4.587468073796529</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-4.349627865518883</v>
+        <v>-4.426473802449046</v>
       </c>
     </row>
     <row r="14">
@@ -6484,79 +6484,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1935</v>
+        <v>1940</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.121946290074021</v>
+        <v>1.141761582220205</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.11567222696668</v>
+        <v>1.165041049855049</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.5737782961605262</v>
+        <v>0.5965872182153547</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.06033023508096136</v>
+        <v>-0.06521590608670635</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.2690219723628857</v>
+        <v>0.263955258194656</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2322242631405729</v>
+        <v>-0.2651910876772803</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.6688457060983239</v>
+        <v>-0.7302344007236385</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.021133518999406</v>
+        <v>-1.081978529432767</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.001998375945824</v>
+        <v>-1.062896056752102</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.284864523026528</v>
+        <v>-1.34594431570013</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.083987954491555</v>
+        <v>-1.145328514863799</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.539629223644404</v>
+        <v>-1.600161189218234</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.915169948049765</v>
+        <v>-1.976036679131539</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.776145519123538</v>
+        <v>-2.835098704942361</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-2.994122432695185</v>
+        <v>-3.053298067294818</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-3.142243904551044</v>
+        <v>-3.200426671649687</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-3.121822304389283</v>
+        <v>-3.151171947291409</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-3.381400963458525</v>
+        <v>-3.381294316668466</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-3.548511417284899</v>
+        <v>-3.548147577795689</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-3.796678025377275</v>
+        <v>-3.795933891487927</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-3.588960885039981</v>
+        <v>-3.588603818481211</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-4.306994500999551</v>
+        <v>-4.334207636665163</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-4.674858634188773</v>
+        <v>-4.729490780957967</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-4.722371486895319</v>
+        <v>-4.777013681472198</v>
       </c>
     </row>
     <row r="15">
@@ -6566,243 +6566,243 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.537129682738318</v>
+        <v>1.566526158457435</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.264795673793508</v>
+        <v>1.323915258725137</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.9545799933646606</v>
+        <v>0.9918869931042806</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.1284288068236847</v>
+        <v>0.1406841257352696</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.3417249271091336</v>
+        <v>0.3578890448930707</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.09000722685762952</v>
+        <v>-0.05422311002337921</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.6066405069636644</v>
+        <v>-0.6418399966787049</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.8130837858596891</v>
+        <v>-0.8479419301575035</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.7454433111271683</v>
+        <v>-0.7804041765337644</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.262527437916532</v>
+        <v>-1.296511504606755</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.100389218172126</v>
+        <v>-1.134750801325318</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.260915616072012</v>
+        <v>-1.294956001795953</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.712191117778595</v>
+        <v>-1.74493565476623</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.415782671014412</v>
+        <v>-2.448011791470407</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-2.585750254997777</v>
+        <v>-2.617275381001654</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-2.889796712382065</v>
+        <v>-2.921802476406825</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-2.719781460303956</v>
+        <v>-2.751762254822587</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-2.891079196065569</v>
+        <v>-2.922905945280249</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-3.343926966754623</v>
+        <v>-3.37578863809771</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-3.594572240496859</v>
+        <v>-3.626533567679303</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-3.555199670210904</v>
+        <v>-3.586668240259471</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-3.976409293519161</v>
+        <v>-4.007636431112971</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-4.140000488913877</v>
+        <v>-4.217880161844541</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-4.004260577507502</v>
+        <v>-4.0821788549774</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 19.24</t>
+          <t>X &lt; 19.23</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2344</v>
+        <v>2349</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.199861685715163</v>
+        <v>1.215571805486945</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.5396733684574997</v>
+        <v>0.5429571692993065</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.1374207188160668</v>
+        <v>0.1184516337818238</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.5953654925658682</v>
+        <v>-0.613288995464643</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3024374464087529</v>
+        <v>-0.2916351282043053</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.7688039975393508</v>
+        <v>-0.7809157721999114</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.264225760182313</v>
+        <v>-1.299271894805393</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.349702711370981</v>
+        <v>-1.384778012684983</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.199633715459925</v>
+        <v>-1.235024839491658</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.483382239981296</v>
+        <v>-1.518711116724113</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.057629260853702</v>
+        <v>-1.093703845953911</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.142917442533111</v>
+        <v>-1.179022818905786</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.606593501822928</v>
+        <v>-1.642488836256881</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.228332333564495</v>
+        <v>-2.263083451202263</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-2.353136912534012</v>
+        <v>-2.388087284345637</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-2.49864024979702</v>
+        <v>-2.532912922178937</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-2.310762917644055</v>
+        <v>-2.345549590545403</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.391365118807279</v>
+        <v>-2.426076891175029</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-2.704173181668075</v>
+        <v>-2.738102936793048</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-2.961340784680843</v>
+        <v>-2.994625396908837</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-2.96937010252465</v>
+        <v>-3.003025692331207</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-3.276824627389175</v>
+        <v>-3.309903028433958</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-3.532151273706653</v>
+        <v>-3.564528653517627</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-3.328169125155853</v>
+        <v>-3.361056902320733</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 19.86</t>
+          <t>X &lt; 19.85</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2512</v>
+        <v>2517</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.132237002705871</v>
+        <v>1.122932414127085</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.8684563576739635</v>
+        <v>0.8491102355203068</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.6738493743056679</v>
+        <v>0.6541269367443547</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.01798439698524135</v>
+        <v>-0.03672705514711794</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.005585193857946535</v>
+        <v>-0.03494265785010242</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.3889088862080996</v>
+        <v>-0.4174331010249333</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.8235435191591236</v>
+        <v>-0.8516319869019995</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.119467783243977</v>
+        <v>-1.14713686317355</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.8578061651692295</v>
+        <v>-0.8859899480312805</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.174029533573226</v>
+        <v>-1.202011864974367</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.9166378176279224</v>
+        <v>-0.945005583277073</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.133634739840588</v>
+        <v>-1.16173919207737</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.205342337376599</v>
+        <v>-1.2339123505242</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.760604666684706</v>
+        <v>-1.788212062203442</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-1.960497978011539</v>
+        <v>-1.988074390452304</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-2.016780839366191</v>
+        <v>-2.043954395439549</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-1.889886715023025</v>
+        <v>-1.91740174534322</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1.892522741371614</v>
+        <v>-1.920107604788136</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-2.289014143079399</v>
+        <v>-2.315719654789383</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-2.63558913865662</v>
+        <v>-2.661528805640557</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-2.520203152795673</v>
+        <v>-2.546676485982005</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-2.732456210727086</v>
+        <v>-2.758567867279311</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-2.952122646448984</v>
+        <v>-2.977673161992776</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-2.846250253826966</v>
+        <v>-2.872070388646918</v>
       </c>
     </row>
     <row r="18">
@@ -6812,243 +6812,243 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2655</v>
+        <v>2658</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.8202935316884634</v>
+        <v>0.7791454266650177</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.5883804442614817</v>
+        <v>0.5393014613525438</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.439218549031871</v>
+        <v>0.3907616677799908</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.1791218377435229</v>
+        <v>-0.2266716628544714</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.2617801047120523</v>
+        <v>-0.3174490889626611</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.2779766979812237</v>
+        <v>-0.3337172308309704</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.7306835688343867</v>
+        <v>-0.7856877076051063</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.8758910874632164</v>
+        <v>-0.9306674088118143</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.5135688717582951</v>
+        <v>-0.5313819051662705</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.7417919457381217</v>
+        <v>-0.7591056978538546</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.6332498086621001</v>
+        <v>-0.6133508463352868</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.8909699461569076</v>
+        <v>-0.9081415983222314</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.094092765173791</v>
+        <v>-1.073209413379018</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.443782941766422</v>
+        <v>-1.42243234818234</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.518058315024483</v>
+        <v>-1.496404851519983</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.501637994144488</v>
+        <v>-1.517708972697712</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-1.388572734334112</v>
+        <v>-1.404739810239164</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.434102211725474</v>
+        <v>-1.450196552237372</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.722296395193588</v>
+        <v>-1.775702746131564</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.7390927927432</v>
+        <v>-1.792569610587492</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-1.658810186290715</v>
+        <v>-1.712224704517816</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.8257685131695</v>
+        <v>-1.878996967023511</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-1.98081800887762</v>
+        <v>-2.033990057180823</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.884373851893351</v>
+        <v>-1.937656905972453</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 21.09</t>
+          <t>X &lt; 21.08</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2770</v>
+        <v>2775</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.8327138923094211</v>
+        <v>0.8266296556888406</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.8102508183384458</v>
+        <v>0.7973471286186467</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.7512936098589265</v>
+        <v>0.7380022466264222</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3441756532958991</v>
+        <v>0.3313636637516382</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.106626819273167</v>
+        <v>0.08736201033250524</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.1348207058890338</v>
+        <v>0.1155561769036169</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.1515538841778721</v>
+        <v>-0.1705791196501991</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.4456363748457335</v>
+        <v>-0.4642413738511593</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.3118461597981579</v>
+        <v>-0.3306891955129885</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.490705073475489</v>
+        <v>-0.5095018220629512</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.5548799027059843</v>
+        <v>-0.5734810937936317</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.7056228773011171</v>
+        <v>-0.7240606123641555</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.7670018230747289</v>
+        <v>-0.7857231677204979</v>
       </c>
       <c r="P19" s="4" t="n">
+        <v>-1.129459445046834</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>-1.120118374398579</v>
+      </c>
+      <c r="R19" s="4" t="n">
+        <v>-0.9357408072823148</v>
+      </c>
+      <c r="S19" s="4" t="n">
+        <v>-0.9048362490180821</v>
+      </c>
+      <c r="T19" s="4" t="n">
+        <v>-0.9166533002475177</v>
+      </c>
+      <c r="U19" s="4" t="n">
         <v>-1.111268465542523</v>
       </c>
-      <c r="Q19" s="4" t="n">
-        <v>-1.101673956574629</v>
-      </c>
-      <c r="R19" s="4" t="n">
-        <v>-0.917154523757155</v>
-      </c>
-      <c r="S19" s="4" t="n">
-        <v>-0.886136034026471</v>
-      </c>
-      <c r="T19" s="4" t="n">
-        <v>-0.8979259134605257</v>
-      </c>
-      <c r="U19" s="4" t="n">
-        <v>-1.092952765849958</v>
-      </c>
       <c r="V19" s="4" t="n">
-        <v>-1.065020733192753</v>
+        <v>-1.083335467750089</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.9742964796000777</v>
+        <v>-0.992972210895438</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-1.101158577042817</v>
+        <v>-1.119644498708325</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-1.238105187183038</v>
+        <v>-1.256263278571275</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.184651918615764</v>
+        <v>-1.202944767197103</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 21.71</t>
+          <t>X &lt; 21.7</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2840</v>
+        <v>2845</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.7927081847117563</v>
+        <v>0.7873258293853311</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.5871665944703111</v>
+        <v>0.5761723909737171</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.564244084439494</v>
+        <v>0.5528608772891133</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.4642348056131169</v>
+        <v>0.4528096515071383</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.3635071758330923</v>
+        <v>0.346271765074313</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.3956857749192579</v>
+        <v>0.3784383211395053</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.09747722543287551</v>
+        <v>0.08051264898495702</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.1611255856054257</v>
+        <v>-0.1777309933914779</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.1696030322100981</v>
+        <v>-0.1861921155320303</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.2929336455944664</v>
+        <v>-0.3095457411670139</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.3136803609989727</v>
+        <v>-0.3301860765599258</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.5376173760977352</v>
+        <v>-0.5538242569869993</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.6250479346922333</v>
+        <v>-0.6414443506660277</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.89607220150112</v>
+        <v>-0.9120701912572926</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.7975325944987617</v>
+        <v>-0.8139086989279747</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.637924053206028</v>
+        <v>-0.6544148105662231</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.6811176172786304</v>
+        <v>-0.6975832511344748</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.6248544506055396</v>
+        <v>-0.6414607733156927</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.7393689535666752</v>
+        <v>-0.7557213243081478</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.6722333778325051</v>
+        <v>-0.6886590025446537</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.5618093020415955</v>
+        <v>-0.5786008662209952</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.7224595530236044</v>
+        <v>-0.7390026186657934</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.9195242594342261</v>
+        <v>-0.9356504967915029</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.9395713267613885</v>
+        <v>-0.9556957607213832</v>
       </c>
     </row>
     <row r="21">
@@ -7058,243 +7058,243 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2914</v>
+        <v>2917</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.5783570019805779</v>
+        <v>0.5768399613979653</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.7093396903979752</v>
+        <v>0.7028381501440464</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.7188700923101337</v>
+        <v>0.6789370255725231</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.6034275828426985</v>
+        <v>0.563903530469716</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.5301649580598422</v>
+        <v>0.4858414300309946</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.6345261282702808</v>
+        <v>0.5899961097852255</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.392645515065368</v>
+        <v>0.3486764025058093</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.09950767793890947</v>
+        <v>0.05593923199518258</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.1606651537364598</v>
+        <v>0.1169971917500519</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.01315184189456176</v>
+        <v>-0.05632752850167577</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.0605049204297643</v>
+        <v>-0.1037693599366776</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.2173998362005634</v>
+        <v>-0.2604022796402745</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.3651541202561575</v>
+        <v>-0.4075393132412302</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.6006345650022098</v>
+        <v>-0.6427017829900521</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.5895982093491838</v>
+        <v>-0.6314113010726317</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.4188863769953386</v>
+        <v>-0.4611499611499639</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.498543769746739</v>
+        <v>-0.5406866100944114</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.377812218778125</v>
+        <v>-0.4200524841186137</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.4838585740219514</v>
+        <v>-0.5261021017136684</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.4478633731378423</v>
+        <v>-0.4902434669158424</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.3196662303468258</v>
+        <v>-0.3619624177062875</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.4437912530088326</v>
+        <v>-0.4859459942678868</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.6287803556919727</v>
+        <v>-0.6708824662427446</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.6501477572040315</v>
+        <v>-0.6922139472444826</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 22.94</t>
+          <t>X &lt; 22.93</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2970</v>
+        <v>2975</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.5658661610773805</v>
+        <v>0.5619547544799772</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.6541516503565816</v>
+        <v>0.6456640428395062</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.5362210662996745</v>
+        <v>0.5276120458628029</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.4763965569052999</v>
+        <v>0.4677268928663523</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.497986508997208</v>
+        <v>0.4848403361083697</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.5034881062412779</v>
+        <v>0.4903655692451423</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.3185612625607348</v>
+        <v>0.3055712258748287</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.02567049920492792</v>
+        <v>0.01310131946225823</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.1534365674226237</v>
+        <v>0.1406549504454659</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.03537655729090261</v>
+        <v>0.02261540326942679</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.07296592110537148</v>
+        <v>-0.08549375467148934</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.2321614521482402</v>
+        <v>-0.2444917498527701</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.3647297803484122</v>
+        <v>-0.3770921261861488</v>
       </c>
       <c r="P22" s="4" t="n">
+        <v>-0.6454715823341104</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>-0.6136817468678402</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>-0.435167972043601</v>
+      </c>
+      <c r="S22" s="4" t="n">
+        <v>-0.5492881509400291</v>
+      </c>
+      <c r="T22" s="4" t="n">
+        <v>-0.5001354545747887</v>
+      </c>
+      <c r="U22" s="4" t="n">
         <v>-0.6335030268867357</v>
       </c>
-      <c r="Q22" s="4" t="n">
-        <v>-0.6015073229447836</v>
-      </c>
-      <c r="R22" s="4" t="n">
-        <v>-0.4228166362683439</v>
-      </c>
-      <c r="S22" s="4" t="n">
-        <v>-0.5370910390832435</v>
-      </c>
-      <c r="T22" s="4" t="n">
-        <v>-0.4878247390314812</v>
-      </c>
-      <c r="U22" s="4" t="n">
-        <v>-0.6214560590591418</v>
-      </c>
       <c r="V22" s="4" t="n">
-        <v>-0.5490372202284419</v>
+        <v>-0.5611724702242782</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.3998877094316313</v>
+        <v>-0.4124007922704394</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.5567799707530412</v>
+        <v>-0.5690543240539867</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.6994809474038561</v>
+        <v>-0.7114629934855969</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.6882316388019873</v>
+        <v>-0.7002572056860146</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 23.56</t>
+          <t>X &lt; 23.55</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3012</v>
+        <v>3017</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.4744282039770411</v>
+        <v>0.4709949918311835</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.6223375224162098</v>
+        <v>0.6147018532725141</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4860871498784718</v>
+        <v>0.4783912722352852</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.4501657612010561</v>
+        <v>0.4423855683121545</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.4004000545843027</v>
+        <v>0.3887324417953693</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.4083882348083492</v>
+        <v>0.3967368881545568</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.1822602694711648</v>
+        <v>0.170823852963899</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.0774527505533058</v>
+        <v>-0.08852237787439066</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.01604661136550334</v>
+        <v>0.004823992370617702</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.1111639699360509</v>
+        <v>-0.1223348647263123</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.2142403051493957</v>
+        <v>-0.2251944717311432</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.4412865732451934</v>
+        <v>-0.4519274487098102</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.5877099670263561</v>
+        <v>-0.5983359580355341</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.8889896373806963</v>
+        <v>-0.8991682121631328</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.7673821174763873</v>
+        <v>-0.7778975069737299</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.6491786108368061</v>
+        <v>-0.6597796143250676</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.6975572299739312</v>
+        <v>-0.7081114611717894</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.6504912133041287</v>
+        <v>-0.6611508078492534</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.7461611615177546</v>
+        <v>-0.7566269636546821</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.705343242893484</v>
+        <v>-0.7158467159289899</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.5327250364193006</v>
+        <v>-0.543628025979892</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.6885338943451487</v>
+        <v>-0.6992008387432307</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.825458102607989</v>
+        <v>-0.8358510736070173</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.815466805877783</v>
+        <v>-0.8258981813338053</v>
       </c>
     </row>
     <row r="24">
@@ -7304,243 +7304,243 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3064</v>
+        <v>3067</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.3075915626758174</v>
+        <v>0.3073729512929475</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.4468154312404096</v>
+        <v>0.4756548191991214</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.320945309260857</v>
+        <v>0.3506057438504371</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3708133114134071</v>
+        <v>0.4007758736479516</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.2832625460004436</v>
+        <v>0.3101336100617544</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.2293437242573688</v>
+        <v>0.2561832713821133</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.1237540991597115</v>
+        <v>0.1510736291707744</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.2012325374770754</v>
+        <v>-0.2058927803634276</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.2060854118577709</v>
+        <v>-0.2107652062959104</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.2793189293155933</v>
+        <v>-0.2835597109571495</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.3435709561806419</v>
+        <v>-0.3478853122437613</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.5065210906903772</v>
+        <v>-0.5105466790126272</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.5394297091658942</v>
+        <v>-0.5428864089708298</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.8393428700397365</v>
+        <v>-0.8424046824572002</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.7309304777827492</v>
+        <v>-0.7337848019130391</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.5395362957153935</v>
+        <v>-0.5428677014042904</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.5567686564880105</v>
+        <v>-0.5600226948331937</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.544806105708652</v>
+        <v>-0.5480252628223354</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.6351577274097622</v>
+        <v>-0.6383967629046339</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.6244189071474082</v>
+        <v>-0.6277625561060347</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.5617290220341076</v>
+        <v>-0.564876165419463</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.6835776800098614</v>
+        <v>-0.6865730920869026</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.8135142096677228</v>
+        <v>-0.8165189999904783</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.7723407894907695</v>
+        <v>-0.7753531716889768</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 24.79</t>
+          <t>X &lt; 24.78</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3114</v>
+        <v>3119</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.1168320158435918</v>
+        <v>0.1147225873955335</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.4392929796155585</v>
+        <v>0.4337998386161885</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.1329698453321484</v>
+        <v>0.1277583130725759</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.1705909893145403</v>
+        <v>0.1652156989416795</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.01470580862729065</v>
+        <v>0.006701138656737271</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.02840770802004045</v>
+        <v>0.02040276899749216</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.03984898471070863</v>
+        <v>0.03171168205730623</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.2844241062916453</v>
+        <v>-0.2920885723823332</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.06484885136192986</v>
+        <v>-0.0728625605943094</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.08530115778627589</v>
+        <v>-0.09339673913547131</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.1440756237686145</v>
+        <v>-0.1520434784708868</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.3408107889882217</v>
+        <v>-0.3485089768505958</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.3271370262390647</v>
+        <v>-0.3350214620217571</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.6257260416071517</v>
+        <v>-0.6331697407516401</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.5615542605377186</v>
+        <v>-0.5691989811540239</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.4597305154997215</v>
+        <v>-0.4674584023800463</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.4788101916980168</v>
+        <v>-0.4865315730851947</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.4686973610331293</v>
+        <v>-0.4764548104956248</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.554110621364984</v>
+        <v>-0.5617055550514465</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.5725896414043987</v>
+        <v>-0.5801332456039106</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.5516870119123851</v>
+        <v>-0.5593464269030619</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.6407040408501601</v>
+        <v>-0.6482366313878885</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.7320266959533583</v>
+        <v>-0.7393786262399402</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.724821039553234</v>
+        <v>-0.73220021693988</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 25.41</t>
+          <t>X &lt; 25.4</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3168</v>
+        <v>3173</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.2095977009715213</v>
+        <v>0.2077135874441254</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.3323740364897247</v>
+        <v>0.3279754622401256</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.1322496663676702</v>
+        <v>0.1279976152673825</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.1257715123192042</v>
+        <v>0.12144561291705</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.09643233226606185</v>
+        <v>-0.1027383299957663</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.1112117477887793</v>
+        <v>-0.1174770485919652</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.1445128960512321</v>
+        <v>-0.1508182264578224</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.4366629362240602</v>
+        <v>-0.4425459610434075</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.34582379344549</v>
+        <v>-0.3518482912258492</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.2534464636226517</v>
+        <v>-0.2597083519745382</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.2437439957087904</v>
+        <v>-0.2499935618096387</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.3790174307873713</v>
+        <v>-0.385090545576162</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.3532383159528081</v>
+        <v>-0.3594848331906988</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.6505244113208306</v>
+        <v>-0.6563333053380731</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.5357020210534529</v>
+        <v>-0.5417708809548571</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.5199394495776986</v>
+        <v>-0.5259685823973825</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.4465067961075704</v>
+        <v>-0.4526707104480252</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.5643664997079441</v>
+        <v>-0.5703610703257596</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.7077090285734542</v>
+        <v>-0.7134570733724388</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.7227368159682399</v>
+        <v>-0.7284434615925619</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.6484190356756301</v>
+        <v>-0.6543091276196833</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.7056987967249952</v>
+        <v>-0.7115113237815507</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.7276909534802556</v>
+        <v>-0.7334409596217455</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.6903360159063539</v>
+        <v>-0.6961574882698898</v>
       </c>
     </row>
     <row r="27">
@@ -7550,735 +7550,735 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3198</v>
+        <v>3203</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.2666893485354791</v>
+        <v>0.2649185406287913</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.4160010541497314</v>
+        <v>0.4119729874430291</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.2354118352514476</v>
+        <v>0.2315183295098038</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.1602193679743138</v>
+        <v>0.1563692003215849</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.02994562590426142</v>
+        <v>0.02426679921458685</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.07619380548522514</v>
+        <v>-0.08169261100842107</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.1785956761904401</v>
+        <v>-0.1840159133286789</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.439516344522545</v>
+        <v>-0.4445624453643688</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.4113856763827712</v>
+        <v>-0.416474573906477</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.3893878149192176</v>
+        <v>-0.3945914872325034</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.3461113785000407</v>
+        <v>-0.3513582075077011</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.4827616264024854</v>
+        <v>-0.4878271779728678</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.4677714918046547</v>
+        <v>-0.4729762166793989</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.5773514594964908</v>
+        <v>-0.5824111822946918</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.5321097846418965</v>
+        <v>-0.5373092963722073</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.5421152817312063</v>
+        <v>-0.5472429055424968</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.4706324855445914</v>
+        <v>-0.4758882499766202</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.5259575166079031</v>
+        <v>-0.5311410055719747</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.6971414065668569</v>
+        <v>-0.7020397387982342</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.7415026724277425</v>
+        <v>-0.7463163099681012</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.6729797142951526</v>
+        <v>-0.6779581107134049</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.730442487576731</v>
+        <v>-0.7353421982763777</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.7496586104210152</v>
+        <v>-0.754503950354021</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.7133736151634693</v>
+        <v>-0.7182865216896488</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 26.64</t>
+          <t>X &lt; 26.63</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3235</v>
+        <v>3237</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.1760472322364564</v>
+        <v>0.1935087147888908</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.4116053617375925</v>
+        <v>0.4275672511516362</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.2167019027484116</v>
+        <v>0.2032999489478158</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.2571300823793621</v>
+        <v>0.2442964799839658</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1242128093655097</v>
+        <v>0.1100941196787844</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.009301858824429132</v>
+        <v>-0.02350114381754054</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.05781344192952531</v>
+        <v>-0.07134044844456611</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.318898630227757</v>
+        <v>-0.3320369748139456</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.2598091483356555</v>
+        <v>-0.273024102733018</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.3391664037521736</v>
+        <v>-0.3824482161393377</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.3548175961969022</v>
+        <v>-0.3675656319240872</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.3699040353551126</v>
+        <v>-0.4131924177619197</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.3678714686296942</v>
+        <v>-0.3794429984009895</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.5403292230997963</v>
+        <v>-0.5824111822946918</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.3489792482882024</v>
+        <v>-0.3906396525764961</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.3828586920305384</v>
+        <v>-0.4250128402670796</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.3445186192749574</v>
+        <v>-0.3865980770813451</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.3695173833434282</v>
+        <v>-0.4115075394502909</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.5670935733241009</v>
+        <v>-0.5474678095836367</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.6396444443482281</v>
+        <v>-0.6201267525869127</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.5780819455118902</v>
+        <v>-0.5581403307791817</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.635727087514951</v>
+        <v>-0.6156812216551586</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.6206492746080201</v>
+        <v>-0.6008394836859736</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.5546963893471073</v>
+        <v>-0.534858701520676</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 27.26</t>
+          <t>X &lt; 27.25</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3261</v>
+        <v>3266</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.1152206638493851</v>
+        <v>0.114093598030486</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.4373892330423104</v>
+        <v>0.4343517573179696</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.2630982242818476</v>
+        <v>0.2602237869815696</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.2670835874317277</v>
+        <v>0.2641516502983521</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.1323266504916347</v>
+        <v>0.1281757131028414</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.001357595788363142</v>
+        <v>-0.002583264269354402</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.02239148917430356</v>
+        <v>-0.02635258842700949</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.2225737229928129</v>
+        <v>-0.2262517183226365</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.2856943742208813</v>
+        <v>-0.289275560584386</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.3400404248837532</v>
+        <v>-0.3435952553242743</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.3533882122764211</v>
+        <v>-0.3569057215386522</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.4316781367348312</v>
+        <v>-0.4350980644235705</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.4080563416424781</v>
+        <v>-0.4115934844727462</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.4892005436037081</v>
+        <v>-0.4926316807504847</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.3351781871902162</v>
+        <v>-0.3388930519453055</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.3334594022974287</v>
+        <v>-0.3371374095259227</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.2658766820933636</v>
+        <v>-0.2696697131516785</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.2914882065512501</v>
+        <v>-0.2952518765102923</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.4551281684417745</v>
+        <v>-0.4586288529892144</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.5255771358421697</v>
+        <v>-0.5289592098173372</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.5300728561442014</v>
+        <v>-0.5334886269697279</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.6491426867799177</v>
+        <v>-0.6523839227850132</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.6933105295427353</v>
+        <v>-0.6964669924192179</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.720507788833423</v>
+        <v>-0.7236301801054168</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 27.87</t>
+          <t>X &lt; 27.86</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3287</v>
+        <v>3292</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.145984120101609</v>
+        <v>0.1449749076841726</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.372106086726042</v>
+        <v>0.3695782608193028</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.2483057281853718</v>
+        <v>0.2458801300414422</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.2768805813674433</v>
+        <v>0.2743692033193597</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.140312869192293</v>
+        <v>0.1368272859468362</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.04210652342995047</v>
+        <v>0.0387781290649869</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.04805971243096963</v>
+        <v>-0.05129862995508461</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.09748977705856277</v>
+        <v>-0.1006720845870461</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.1294639030297802</v>
+        <v>-0.1325973885172829</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.2197252763398154</v>
+        <v>-0.2227691151209541</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.2004662004662023</v>
+        <v>-0.2035251338442521</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.2802930222092002</v>
+        <v>-0.2832492875605723</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.2656791729946661</v>
+        <v>-0.2687248723206537</v>
       </c>
       <c r="P30" s="4" t="n">
+        <v>-0.3508224838231868</v>
+      </c>
+      <c r="Q30" s="4" t="n">
+        <v>-0.2034356032425038</v>
+      </c>
+      <c r="R30" s="4" t="n">
+        <v>-0.2272727272727266</v>
+      </c>
+      <c r="S30" s="4" t="n">
+        <v>-0.1613588778172073</v>
+      </c>
+      <c r="T30" s="4" t="n">
+        <v>-0.157211632812178</v>
+      </c>
+      <c r="U30" s="4" t="n">
         <v>-0.3478864504994092</v>
       </c>
-      <c r="Q30" s="4" t="n">
-        <v>-0.2002356379785013</v>
-      </c>
-      <c r="R30" s="4" t="n">
-        <v>-0.2241416795039655</v>
-      </c>
-      <c r="S30" s="4" t="n">
-        <v>-0.1581179813214462</v>
-      </c>
-      <c r="T30" s="4" t="n">
-        <v>-0.1539563019100498</v>
-      </c>
-      <c r="U30" s="4" t="n">
-        <v>-0.344931354402064</v>
-      </c>
       <c r="V30" s="4" t="n">
-        <v>-0.4133121670633315</v>
+        <v>-0.4161545128071538</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.4220322994960242</v>
+        <v>-0.4248950470533686</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.5103242905563619</v>
+        <v>-0.5130593543214488</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.5215136381098731</v>
+        <v>-0.5242174841125049</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.6098901670927006</v>
+        <v>-0.6124660746527937</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 28.49</t>
+          <t>X &lt; 28.48</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3300</v>
+        <v>3305</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.05585881019073469</v>
+        <v>0.05506634810649302</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.2495406789361141</v>
+        <v>0.2473998333339367</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.2409963376119535</v>
+        <v>0.2387923969743611</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.2967817767143046</v>
+        <v>0.2944556513234389</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.1291942788545697</v>
+        <v>0.1260602006268243</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.09238014213651269</v>
+        <v>0.08930939835628493</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.02970024598997867</v>
+        <v>0.02668182544276476</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.05076177783864466</v>
+        <v>-0.05367534295497478</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.05226767020594281</v>
+        <v>-0.05517855078352341</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.1451881442515059</v>
+        <v>-0.1480011518990665</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.1249052788443024</v>
+        <v>-0.1277362629807826</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.2054917722330032</v>
+        <v>-0.2082175886523814</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.1953291132218382</v>
+        <v>-0.1981307164065385</v>
       </c>
       <c r="P31" s="4" t="n">
+        <v>-0.3109179696250095</v>
+      </c>
+      <c r="Q31" s="4" t="n">
+        <v>-0.1666789429374873</v>
+      </c>
+      <c r="R31" s="4" t="n">
+        <v>-0.1880791006960649</v>
+      </c>
+      <c r="S31" s="4" t="n">
+        <v>-0.153131014887002</v>
+      </c>
+      <c r="T31" s="4" t="n">
+        <v>-0.1494092049383866</v>
+      </c>
+      <c r="U31" s="4" t="n">
         <v>-0.3082733993598126</v>
       </c>
-      <c r="Q31" s="4" t="n">
-        <v>-0.1637801928406404</v>
-      </c>
-      <c r="R31" s="4" t="n">
-        <v>-0.1852420973074942</v>
-      </c>
-      <c r="S31" s="4" t="n">
-        <v>-0.1502323698726045</v>
-      </c>
-      <c r="T31" s="4" t="n">
-        <v>-0.1464976309386685</v>
-      </c>
-      <c r="U31" s="4" t="n">
-        <v>-0.305611718297115</v>
-      </c>
       <c r="V31" s="4" t="n">
-        <v>-0.3427090915392839</v>
+        <v>-0.3453066193010699</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.3535121092296336</v>
+        <v>-0.3561235215475378</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.4417348861230721</v>
+        <v>-0.4442186089723563</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.4214831231365253</v>
+        <v>-0.4239847037679709</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.4794774300477727</v>
+        <v>-0.4818969417619812</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 29.11</t>
+          <t>X &lt; 29.1</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3312</v>
+        <v>3316</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.1024560352014632</v>
+        <v>0.117763248951988</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.3541314404948253</v>
+        <v>0.3383365435807164</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.1904492774858824</v>
+        <v>0.2051763379585765</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.3034711994713604</v>
+        <v>0.318247144444733</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.135173155240075</v>
+        <v>0.1493067001207535</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.1291981536380717</v>
+        <v>0.1133009888434913</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.06396849081920664</v>
+        <v>0.04833962036133954</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.0171978221923581</v>
+        <v>-0.03266422848209061</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.01853842627141944</v>
+        <v>-0.03401916089735835</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.1139062885624682</v>
+        <v>-0.1290819615426955</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.09269677690730305</v>
+        <v>-0.1079727765967675</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.1739905252632283</v>
+        <v>-0.1891034969105405</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.167917044295038</v>
+        <v>-0.1827577200173778</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.3113472947127818</v>
+        <v>-0.3259646469758195</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.1697587959932534</v>
+        <v>-0.1843846435196639</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.1889934995306533</v>
+        <v>-0.2037523246909529</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.1847260206629215</v>
+        <v>-0.1994612327653229</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.1813950009459617</v>
+        <v>-0.1961128478225334</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.3391618932770584</v>
+        <v>-0.3537498192129789</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.3754580787668189</v>
+        <v>-0.3900549690008646</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.3580328863101201</v>
+        <v>-0.3725180810311812</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.4462127048368387</v>
+        <v>-0.4605775006360275</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.4250401131110308</v>
+        <v>-0.4395054012838102</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.4529073817385978</v>
+        <v>-0.4673249495507505</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 29.73</t>
+          <t>X &lt; 29.71</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3320</v>
+        <v>3325</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.06353741494233844</v>
+        <v>0.06285659027174262</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.2538821905243509</v>
+        <v>0.2520426552932165</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.08711359222625248</v>
+        <v>0.08546044624042537</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.1981236712385055</v>
+        <v>0.19627297490144</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.0006272060011127678</v>
+        <v>-0.003057309262125329</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.05373623275973216</v>
+        <v>0.05123144044386407</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.01321305585974386</v>
+        <v>-0.01565241618522606</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.09487606421412664</v>
+        <v>-0.09720665724647404</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.09613713818688296</v>
+        <v>-0.0984654709191588</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1631628233048374</v>
+        <v>-0.1654255827919755</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1713632901751652</v>
+        <v>-0.1736033329887476</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.223143760564561</v>
+        <v>-0.2253196687369154</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.1897800763741557</v>
+        <v>-0.1920559622171254</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.2733442103520787</v>
+        <v>-0.2755058114507065</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.1336685181985118</v>
+        <v>-0.1360694945193828</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.1514153021256561</v>
+        <v>-0.153765376537649</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.1474693335902089</v>
+        <v>-0.1498325940694016</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.1443877259898798</v>
+        <v>-0.1467616252659667</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.301243763614643</v>
+        <v>-0.3033742403821122</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.3369909014302195</v>
+        <v>-0.3390609659535286</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.3209042127614836</v>
+        <v>-0.3230234029539147</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.4391458289373631</v>
+        <v>-0.4410920152843829</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.4474714337786594</v>
+        <v>-0.4493945073321868</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.4453408838630324</v>
+        <v>-0.447271800997818</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 30.34</t>
+          <t>X &lt; 30.33</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3331</v>
+        <v>3336</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.006600564010398102</v>
+        <v>0.006071612379287217</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1056365525353371</v>
+        <v>0.1041854985815291</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.06535494255425078</v>
+        <v>-0.06660691672578878</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.01305960063307765</v>
+        <v>0.01166285287916935</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.1564429163085208</v>
+        <v>-0.1583636077953301</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.07182998707354926</v>
+        <v>-0.07387087910851164</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1112682775531582</v>
+        <v>-0.1132810749619964</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.1936079541130269</v>
+        <v>-0.1955097963034831</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.1947578816107409</v>
+        <v>-0.1966576273404286</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.2641381439357744</v>
+        <v>-0.2659651133512142</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.2415347810084683</v>
+        <v>-0.243386198338861</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.2940844910296505</v>
+        <v>-0.2958693042811831</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.2944763440128497</v>
+        <v>-0.2963048009710434</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.3785257163117919</v>
+        <v>-0.380238262917743</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.2115721881790762</v>
+        <v>-0.2135607227311382</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.2273229178327938</v>
+        <v>-0.2292663476873997</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.1938966707555068</v>
+        <v>-0.1958964877692679</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.191185316589717</v>
+        <v>-0.1931944873358447</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.34682534346355</v>
+        <v>-0.3485945579759644</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.3818511427896922</v>
+        <v>-0.3835619309805125</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.3676237283227195</v>
+        <v>-0.3693778935890606</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.4857398923172056</v>
+        <v>-0.4873212528729525</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.4931446262715582</v>
+        <v>-0.4947054590315645</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.4912856958338239</v>
+        <v>-0.492853380846725</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 30.96</t>
+          <t>X &lt; 30.95</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3350</v>
+        <v>3355</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.02888060895793387</v>
+        <v>-0.02924261372799464</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.06753395572131637</v>
+        <v>0.06642524427388707</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.08095727580664658</v>
+        <v>-0.08188940631040253</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.06636219382662034</v>
+        <v>-0.06733772099624957</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1479457760082283</v>
+        <v>-0.1494058286178443</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.09244272714770574</v>
+        <v>-0.09398041286609526</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1063271435797546</v>
+        <v>-0.1078681712363192</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.2194822616091585</v>
+        <v>-0.2208646940732493</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1906812480041893</v>
+        <v>-0.1921060828703318</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.2640403885765537</v>
+        <v>-0.2653803258018783</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2102788677275811</v>
+        <v>-0.2116913399452756</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.264100059800505</v>
+        <v>-0.2654418544988957</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.2410864460545952</v>
+        <v>-0.2424968928950477</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.3258967629046339</v>
+        <v>-0.3271887367042723</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.1933710198102361</v>
+        <v>-0.194880562270157</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.2056593290189497</v>
+        <v>-0.2071337820668759</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.1433865091997362</v>
+        <v>-0.1449585445090662</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.1412700207929163</v>
+        <v>-0.1428493359344785</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.2649832165689361</v>
+        <v>-0.2663729533808237</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.2987263366775466</v>
+        <v>-0.3000611742326242</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.2876337615084452</v>
+        <v>-0.2890023224114699</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.4054872369800719</v>
+        <v>-0.4066834755199622</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.4112676498767058</v>
+        <v>-0.4124479089635713</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.4098256887542391</v>
+        <v>-0.4110112539521111</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/vix/vix_level.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/vix/vix_level.xlsx
@@ -618,2133 +618,2133 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 13.38</t>
+          <t>X ≈ 13.73</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>8.118985889402509</v>
+        <v>-1.360369608484945</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4.176325461607028</v>
+        <v>-1.604200644993185</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.9418833870032515</v>
+        <v>-4.291601576689906</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.2338765673418735</v>
+        <v>-10.64390881843454</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>5.32419554342313</v>
+        <v>-9.479883951709795</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.93672575938405</v>
+        <v>-7.885397546312369</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>6.554443592988356</v>
+        <v>-7.236525419212576</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8.088888233468808</v>
+        <v>-6.099981734727656</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.132945600243076</v>
+        <v>-7.417086759985217</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.555355055153832</v>
+        <v>-6.768793566209418</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>4.019095304737093</v>
+        <v>-3.612271057868789</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>3.742829195184918</v>
+        <v>-2.444707153640337</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>2.624710053119152</v>
+        <v>-2.112049254505195</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>6.03064759146865</v>
+        <v>0.5297641186542421</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>5.376203987915851</v>
+        <v>-0.1502723730438262</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>5.970631579876041</v>
+        <v>-1.036361385760564</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>9.467189462768076</v>
+        <v>0.305470487194107</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>9.365356023148337</v>
+        <v>1.619463781512508</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>9.583849369512258</v>
+        <v>0.387035004295825</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>9.773287815315783</v>
+        <v>0.6013352726908963</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>7.417742250470148</v>
+        <v>-1.413332052548313</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>9.161244429920195</v>
+        <v>-1.488971295580285</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>9.438446975876957</v>
+        <v>-1.245896045066949</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>7.547259983007642</v>
+        <v>-1.408515805884328</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 14</t>
+          <t>X ≈ 14.34</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-3.004872418746388</v>
+        <v>-1.060741690716739</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.111913367955268</v>
+        <v>3.612395416949219</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-4.767553175901519</v>
+        <v>-3.534616981588812</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-10.38488508576628</v>
+        <v>-4.12355740539131</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-8.266927653967414</v>
+        <v>-4.398761750066754</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-10.53942181440552</v>
+        <v>-6.213649871788178</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-17.45039498410729</v>
+        <v>-9.960807993275523</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-15.2758719320075</v>
+        <v>-11.25278612205011</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-14.0100934730133</v>
+        <v>-10.1432487357695</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-11.09600038089959</v>
+        <v>-12.91062940504969</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-8.367015303802511</v>
+        <v>-9.685310680792085</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-7.417030291516724</v>
+        <v>-12.92300111531919</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-6.077668792321397</v>
+        <v>-12.06458269417843</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-5.069176197164325</v>
+        <v>-8.367767818890115</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-5.726903552003293</v>
+        <v>-7.07580258207512</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-6.367422358862306</v>
+        <v>-7.505912425824903</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-6.503409309334089</v>
+        <v>-8.600343429642933</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-6.610069551324344</v>
+        <v>-9.72406786931468</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-7.629075759552869</v>
+        <v>-10.50144049105068</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-8.677905418287935</v>
+        <v>-12.26827761755622</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-9.222472185563959</v>
+        <v>-10.86057719977083</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-10.53494211531775</v>
+        <v>-10.93918568173446</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-11.49792742501896</v>
+        <v>-7.729714767269513</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-9.108183339102062</v>
+        <v>-8.884480793686571</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 14.61</t>
+          <t>X ≈ 14.94</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>174</v>
+        <v>249</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.334362166550619</v>
+        <v>1.066727861225466</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2.326985878730412</v>
+        <v>0.02565410027106196</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.9003134808636446</v>
+        <v>0.3769277817217613</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.335612153244952</v>
+        <v>1.385344777305441</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.144590732681849</v>
+        <v>3.905335387679656</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.04558677241995923</v>
+        <v>4.860798460984903</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-2.435116735896123</v>
+        <v>1.277649661765324</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-5.000109235046068</v>
+        <v>0.9745806764103619</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-8.391709393887957</v>
+        <v>-2.893673818719712</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-10.88016331309858</v>
+        <v>-3.686700714951272</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-11.18319736479584</v>
+        <v>-6.216549273693055</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-12.03679667828891</v>
+        <v>-5.69372557283193</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-11.44181469049161</v>
+        <v>-6.806545644602757</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-10.52035953871966</v>
+        <v>-9.058087902148841</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-10.03380079569763</v>
+        <v>-7.338934481872137</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-11.7372519424454</v>
+        <v>-7.983429315754485</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-14.16874816248465</v>
+        <v>-10.09360458112924</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-13.70449169422183</v>
+        <v>-11.83299942646633</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-14.64084928845116</v>
+        <v>-12.82564677840772</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-17.3289164631498</v>
+        <v>-13.01695359230786</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-16.72819792985428</v>
+        <v>-13.58829505354052</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-15.66087624988511</v>
+        <v>-15.27357280333169</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-15.39162469049521</v>
+        <v>-17.44421174170075</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-17.19673165753572</v>
+        <v>-18.81728130265335</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 15.23</t>
+          <t>X ≈ 15.54</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.408325880771734</v>
+        <v>4.55569928922862</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.885097662044679</v>
+        <v>2.666708213806203</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.830642844080565</v>
+        <v>3.073148948466304</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-2.183107085422897</v>
+        <v>1.168021879499989</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.3895029226201672</v>
+        <v>1.553154621504596</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.215989176749034</v>
+        <v>0.7189962571726127</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.16173561034924</v>
+        <v>0.5926659398302263</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.595802505933442</v>
+        <v>-0.7009901907803595</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.4925702904328801</v>
+        <v>-0.5722605434051573</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1600456490106552</v>
+        <v>-0.7028263959443066</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.07714919261919562</v>
+        <v>-1.093329615885452</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.2001879541759237</v>
+        <v>-0.3767758763927844</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.809314742065851</v>
+        <v>-0.8254636094066825</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.454939278298639</v>
+        <v>-2.397206991680214</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-3.621135828467565</v>
+        <v>-3.078777754177111</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-6.947125249877544</v>
+        <v>-4.17681669801496</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-8.864844462810098</v>
+        <v>-4.613801562952837</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-9.685799901340204</v>
+        <v>-3.422440443286568</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-10.54331327008823</v>
+        <v>-3.541447126678008</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-9.290830571524644</v>
+        <v>-3.992601287639047</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-8.766130015467688</v>
+        <v>-3.233951006633831</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-12.41439726139946</v>
+        <v>-4.306808508144847</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-13.57288395195075</v>
+        <v>-4.729750411269663</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-15.43975300400542</v>
+        <v>-6.887835946477814</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 15.84</t>
+          <t>X ≈ 16.14</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.5039652834386104</v>
+        <v>-1.717148776042421</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.014759061415283</v>
+        <v>-1.530452753229248</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.307181384181916</v>
+        <v>-3.383248482502175</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.239134083496758</v>
+        <v>-6.00803995447135</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-2.006569275456684</v>
+        <v>-7.151630001738113</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.25351512953894</v>
+        <v>-5.841226639821372</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.2590452963393162</v>
+        <v>-4.185166099832671</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.8713043282816315</v>
+        <v>-2.477950632090575</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.5961226681516365</v>
+        <v>-1.898062332218252</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.4568194108648029</v>
+        <v>-2.246154920559128</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.324686091046701</v>
+        <v>-0.07229755615352218</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.742699725400215</v>
+        <v>-2.200541801837552</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-2.149168581351965</v>
+        <v>-3.720820835048862</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.226438015467345</v>
+        <v>-5.236165774278206</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-4.740930038699908</v>
+        <v>-5.341335022593753</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-1.86495844760352</v>
+        <v>-3.051316761030122</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-1.142414993800891</v>
+        <v>-4.023778343068336</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-1.819786037083261</v>
+        <v>-3.869820003372446</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-1.319406812809611</v>
+        <v>-3.947086924490414</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-1.992451313145025</v>
+        <v>-4.314180386563621</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-1.10503223597145</v>
+        <v>-1.988839861187728</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-1.468210692544602</v>
+        <v>-3.224045157995747</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-3.200229936454868</v>
+        <v>-4.141866779546966</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-2.991942934418766</v>
+        <v>-2.857791168202503</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 16.46</t>
+          <t>X ≈ 16.75</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.525973806055013</v>
+        <v>1.412863592639248</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.1022483323231356</v>
+        <v>2.24032951998602</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.702496806893322</v>
+        <v>1.634565384992726</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.058336631950517</v>
+        <v>2.643948686837014</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-3.486335887777706</v>
+        <v>1.703752425196903</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-5.20954760140441</v>
+        <v>0.1179714703107422</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-5.443034347780603</v>
+        <v>1.477783059944471</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-4.906835876288206</v>
+        <v>-0.5771507602934207</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.956612711688116</v>
+        <v>1.994990002472441</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.370497062842297</v>
+        <v>1.72742294563502</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.823595667370618</v>
+        <v>1.733880115923625</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.013655186286698</v>
+        <v>1.448084410704041</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.5063403466608278</v>
+        <v>3.302203084417769</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.101999427997882</v>
+        <v>3.314832866901206</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-1.77391496833058</v>
+        <v>2.24900040453273</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-1.829587074626289</v>
+        <v>-0.004830782358034469</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-2.616456184074003</v>
+        <v>1.144805268111639</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-2.277388007721328</v>
+        <v>1.180272031553436</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-2.337833873665552</v>
+        <v>2.107569351678606</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-2.976121002516741</v>
+        <v>0.04389339022992544</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-1.874746037298173</v>
+        <v>0.2914567049259986</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-1.403407995364837</v>
+        <v>1.032023265923208</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.5166406867025017</v>
+        <v>2.091486992078693</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>1.538268974016702</v>
+        <v>3.018289864850452</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 17.08</t>
+          <t>X ≈ 17.35</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>316</v>
+        <v>291</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.265318917197781</v>
+        <v>0.5370278670079642</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.8495548746655359</v>
+        <v>0.9704760405559298</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.14998188692519</v>
+        <v>3.460605271116592</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.987153773511409</v>
+        <v>2.008522833406488</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.704283133268206</v>
+        <v>1.0414478523507</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.209677007047226</v>
+        <v>-0.5184210608742745</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>5.570575189953885</v>
+        <v>0.7342472050337179</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>4.524390355668096</v>
+        <v>0.7645061381315017</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>4.751093968337443</v>
+        <v>-0.1356717088434536</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>4.28341742234646</v>
+        <v>0.7702686535996932</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>6.009757675490391</v>
+        <v>2.079778929638699</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>5.59908617579876</v>
+        <v>1.44897531951176</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.730664803373237</v>
+        <v>0.3164514621079348</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.873546514922495</v>
+        <v>-1.318342629228496</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>4.841946664991632</v>
+        <v>-1.668843982597863</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>3.860931317827479</v>
+        <v>-0.07238051113791499</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>4.356195359744717</v>
+        <v>0.1652658800265598</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>4.249847380926411</v>
+        <v>-2.030884434434363</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>4.032355502860163</v>
+        <v>-1.472074326006584</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>3.470101723489002</v>
+        <v>-0.2307916634847302</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>3.12679792367264</v>
+        <v>-1.272334192118954</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>1.786944864664598</v>
+        <v>-2.509013971285547</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>1.427794327599479</v>
+        <v>-2.047516011651275</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>2.932760558381496</v>
+        <v>-2.678499370802236</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 17.7</t>
+          <t>X ≈ 17.95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.868491228952685</v>
+        <v>1.687498794901956</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.9497370003769205</v>
+        <v>2.278412042880092</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.07555265762872</v>
+        <v>2.278948066511525</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1.535805209802561</v>
+        <v>2.941775993226265</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.771136062375284</v>
+        <v>6.013498187854964</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.5901529864984454</v>
+        <v>5.752021752012134</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.581067169900543</v>
+        <v>1.191249363210332</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-3.26551690433665</v>
+        <v>1.723149003483776</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.223192909588185</v>
+        <v>3.106308038690841</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-3.378731927541601</v>
+        <v>2.310256543471503</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.497064751991665</v>
+        <v>0.4904413488708173</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-4.180987909765669</v>
+        <v>2.30590960360454</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-4.680260341170573</v>
+        <v>1.609427527994782</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-5.458293373667786</v>
+        <v>1.779603508402673</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-6.913994812072573</v>
+        <v>1.097449126517716</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-6.318698981063996</v>
+        <v>-0.4332970638677409</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-4.861892896876633</v>
+        <v>0.2996426080892576</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-5.76307986276796</v>
+        <v>-0.67006158075435</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-4.751751128839118</v>
+        <v>-3.38446964649561</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-4.167489612057295</v>
+        <v>-3.588293243277775</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-4.31292304289812</v>
+        <v>-3.737327702817218</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-5.590773009927709</v>
+        <v>-3.812490224772645</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-5.721797997555377</v>
+        <v>-3.987265781335168</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-7.135825855456588</v>
+        <v>-2.894174650101725</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 18.31</t>
+          <t>X ≈ 18.55</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>5.461101070739794</v>
+        <v>3.228206605222738</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.791909137140344</v>
+        <v>-0.6635335638144113</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.619768897802224</v>
+        <v>-4.001560999039384</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.026453703668736</v>
+        <v>-3.031463197847607</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.224195970341533</v>
+        <v>-3.307021337946942</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.877140698411914</v>
+        <v>-3.670921065282251</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.1544321586049122</v>
+        <v>-2.903503077514905</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.277720786517619</v>
+        <v>-5.29175685425686</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.789323412103684</v>
+        <v>-4.122161277906088</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.8722684213708192</v>
+        <v>-5.439046106458754</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.062637342513383</v>
+        <v>-3.60431109185442</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.467300279737003</v>
+        <v>-3.360059712992388</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.328973198568896</v>
+        <v>-4.474951830443217</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.03422394634589</v>
+        <v>-3.681519225209598</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>1.306201526566909</v>
+        <v>-3.32200694042799</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.4430381382876476</v>
+        <v>-4.844036254941663</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.8308635533638764</v>
+        <v>-3.385416666666671</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>1.191715164039834</v>
+        <v>0.1275325615050633</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.878778431561663</v>
+        <v>-1.220505211349163</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-2.162679940861501</v>
+        <v>0.03574790037654907</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-3.646720747363055</v>
+        <v>-1.052529934337642</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-1.077110808082736</v>
+        <v>-0.6068591229594702</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.4442616771186181</v>
+        <v>0.6784420289855717</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>2.246363696195864</v>
+        <v>3.120469701362715</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 18.93</t>
+          <t>X ≈ 19.16</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.630544292631775</v>
+        <v>-0.46205800773145</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-8.058643787251718</v>
+        <v>0.2399024551427686</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-9.518722318461087</v>
+        <v>-0.5408579974596037</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-8.946556053209243</v>
+        <v>0.28854075159947</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-7.47003289457539</v>
+        <v>0.4869162607892861</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-8.818152692585706</v>
+        <v>-1.725818379658172</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-8.577982195493718</v>
+        <v>-1.573033093312752</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-7.325581395348834</v>
+        <v>0.01778106043508387</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-6.263686050168822</v>
+        <v>-1.276090977748112</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.975377236409393</v>
+        <v>0.297525773477993</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.6400931044515588</v>
+        <v>0.09582713879334648</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.1015656553657536</v>
+        <v>1.714979781478334</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.5113923298577063</v>
+        <v>3.917623209051428</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.2222671246716459</v>
+        <v>3.19545549832916</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.1399977410131044</v>
+        <v>6.304770310756844</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>1.754792826221397</v>
+        <v>7.813941628154652</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>2.131079770876575</v>
+        <v>7.236127567140592</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>3.046647230320701</v>
+        <v>5.681442514111652</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>4.282946774510386</v>
+        <v>5.895904741257482</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>3.959588502845826</v>
+        <v>4.688690238449155</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>3.417042334879682</v>
+        <v>4.121245737068421</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>4.361604536735889</v>
+        <v>6.415751461558578</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>3.615671085952634</v>
+        <v>4.763651349680565</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>4.560246995994667</v>
+        <v>6.023313303258455</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 19.54</t>
+          <t>X ≈ 19.76</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.09258814348625322</v>
+        <v>1.585578400094533</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>5.200871361652375</v>
+        <v>-1.865456640737477</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>8.215485570822686</v>
+        <v>3.290105667627287</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>8.070135566059193</v>
+        <v>0.1336009047165021</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.572099879734736</v>
+        <v>-2.70605979948548</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4.688908703200866</v>
+        <v>0.01497637061521573</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>5.452630049404242</v>
+        <v>-0.1390800005917185</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.198228128460691</v>
+        <v>-1.085026085026087</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>4.02542959608968</v>
+        <v>2.248031029786226</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.25251392005319</v>
+        <v>0.8109538935412459</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.145621181262733</v>
+        <v>-1.48091365595706</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.918842507899555</v>
+        <v>-2.398521251453857</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>4.505614472863378</v>
+        <v>0.3327404772490752</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4.879773691654961</v>
+        <v>3.93066026196982</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>3.626392298836159</v>
+        <v>0.6844033159821947</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>4.816017316017238</v>
+        <v>3.168784257878919</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>4.086862083801677</v>
+        <v>2.423878205128126</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>5.172497570456756</v>
+        <v>5.496122305094872</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>3.602674665666726</v>
+        <v>5.710584532240588</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>2.003806189920475</v>
+        <v>5.925170977299572</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>3.842212402906952</v>
+        <v>7.921829040021393</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>4.956842631974048</v>
+        <v>9.128717800117393</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>5.231317344455974</v>
+        <v>10.01337792642135</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>3.965008900756565</v>
+        <v>7.928162009055093</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 20.16</t>
+          <t>X ≈ 20.36</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-5.413896758822077</v>
+        <v>-8.42984477322338</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-5.039453699015866</v>
+        <v>-7.923871909679171</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-4.349813173578767</v>
+        <v>-3.915408116833873</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.644327476709336</v>
+        <v>-0.7484118194014897</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-5.398557665568745</v>
+        <v>-2.52772935799706</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.171387243932806</v>
+        <v>2.140482443489788</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.3994385600425474</v>
+        <v>3.601039529001334</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>2.958106547913573</v>
+        <v>5.551758183337128</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>5.8364731624524</v>
+        <v>4.927807393773108</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>7.191217060884</v>
+        <v>6.387394996298227</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>5.337617128577783</v>
+        <v>5.907750311654347</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>3.640428008817771</v>
+        <v>5.63116835718305</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.808046083805628</v>
+        <v>2.260637141987921</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>5.133066498139058</v>
+        <v>3.516162479051054</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>7.311802633182815</v>
+        <v>5.089647194910491</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>7.906189555125763</v>
+        <v>6.402830912978146</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>7.772272418148333</v>
+        <v>5.547070802005102</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>6.958211856171005</v>
+        <v>4.662306997595294</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>7.883323095251392</v>
+        <v>8.636167720981703</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>13.74392777046765</v>
+        <v>12.61015266228129</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>13.20138160250158</v>
+        <v>12.04270816090056</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>13.83475549924844</v>
+        <v>13.47130503744152</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>14.81845006988671</v>
+        <v>15.21869892121621</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>14.74261781666332</v>
+        <v>14.30468022767847</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 20.77</t>
+          <t>X ≈ 20.96</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.914708442123533</v>
+        <v>-1.459293394777262</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>6.7081367719789</v>
+        <v>8.711466436185653</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>8.688921141751386</v>
+        <v>9.540105667627294</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>13.10417225051367</v>
+        <v>15.19770346881913</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>9.349578359163019</v>
+        <v>12.83881199538639</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>10.39124539996125</v>
+        <v>15.07907893471782</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>13.89280098957519</v>
+        <v>17.4089969224851</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>10.19578612601869</v>
+        <v>15.02074314574314</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>4.25436732502741</v>
+        <v>10.98200538876059</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>5.190853358392623</v>
+        <v>12.26928722687457</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.3367078723494714</v>
+        <v>7.333188908145587</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.476761887704846</v>
+        <v>6.014940287007612</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>5.772403239652142</v>
+        <v>9.066714836223518</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>5.551324363205609</v>
+        <v>9.860147441457123</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>7.457283629727606</v>
+        <v>13.34465972623867</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>12.32517482517487</v>
+        <v>15.98929707839173</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>10.48185597879564</v>
+        <v>16.92708333333332</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>11.23171612967536</v>
+        <v>17.83586589483846</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>14.01171007470221</v>
+        <v>18.05032812198411</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>15.05325673937114</v>
+        <v>22.43158123370976</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>15.36541142610587</v>
+        <v>21.86413673232903</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>16.14426631939772</v>
+        <v>19.7056408770404</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>16.41874103187972</v>
+        <v>18.90760869565218</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>15.48820792395569</v>
+        <v>18.74546970136266</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 21.39</t>
+          <t>X ≈ 21.57</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.7837042562890346</v>
+        <v>-1.542626728110676</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-8.261338197496066</v>
+        <v>-1.788533563814624</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-6.842214389384289</v>
+        <v>-4.376560999039377</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>5.301974448315917</v>
+        <v>3.031036802152393</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>10.68046969005435</v>
+        <v>6.755478662053065</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>10.86743587615173</v>
+        <v>8.245745601384478</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>10.09548719226138</v>
+        <v>3.450663589151837</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>11.24584717607974</v>
+        <v>3.14574314574314</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>5.573048643708724</v>
+        <v>-0.7263279445727449</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>7.657275824815088</v>
+        <v>1.144287226874575</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>9.359906895548356</v>
+        <v>4.083188908145573</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>6.224014634957598</v>
+        <v>6.473273620340947</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>5.10085256810148</v>
+        <v>8.025048169556833</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>7.736916548797737</v>
+        <v>10.44348077479032</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>11.3644875369314</v>
+        <v>11.0946597262386</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>10.53030303030303</v>
+        <v>12.98929707839159</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>7.539243036182782</v>
+        <v>8.885416666666664</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>10.29154518950438</v>
+        <v>11.41919922817165</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>13.36457942757155</v>
+        <v>12.96699478865084</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>14.97999666611092</v>
+        <v>13.18158123370982</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>15.86602192671641</v>
+        <v>15.28080339899576</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>14.36160453673596</v>
+        <v>15.20564087704047</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>11.77893639207508</v>
+        <v>12.78260869565218</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>8.845961281708874</v>
+        <v>8.620469701362786</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 22.01</t>
+          <t>X ≈ 22.17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-7.807513780098638</v>
+        <v>-4.311857497341236</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>5.74659831044044</v>
+        <v>4.673004897724041</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>5.69746815029842</v>
+        <v>6.495233872755449</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>4.984514130855601</v>
+        <v>5.902831673947269</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>6.037612547197213</v>
+        <v>10.24265814923245</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>9.002356511072378</v>
+        <v>13.47651483215375</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>11.0081856049598</v>
+        <v>17.29681743530543</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>9.341085271317823</v>
+        <v>15.45343545343545</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>12.16035023101031</v>
+        <v>17.119825901581</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>9.998545666084937</v>
+        <v>14.78531286790022</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>8.883716419358045</v>
+        <v>15.05754788250447</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>11.38274479368766</v>
+        <v>14.78096592803325</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>8.870693837942746</v>
+        <v>10.58915073365949</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>10.03850385038504</v>
+        <v>8.802455133764845</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>6.602582775026626</v>
+        <v>8.120300751879618</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>7.196969696969688</v>
+        <v>10.22006630916081</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>5.674163671103344</v>
+        <v>3.962339743589737</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>8.347100745059933</v>
+        <v>6.906378715351309</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>8.562992125984259</v>
+        <v>7.120840942496898</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>7.360949047063386</v>
+        <v>2.720042772171453</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>8.207291767986256</v>
+        <v>5.2295213477137</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>9.52033469546604</v>
+        <v>6.692820364219948</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>9.794809407948094</v>
+        <v>8.474916387959702</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>9.718977154724733</v>
+        <v>9.851238932131771</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 22.62</t>
+          <t>X ≈ 22.77</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.192571251363006</v>
+        <v>-1.36871368463234</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.251485980747297</v>
+        <v>-3.788533563814404</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-7.137780891847257</v>
+        <v>-5.043227665705928</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-4.402459049221029</v>
+        <v>-3.461716821036134</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.434164271335149</v>
+        <v>-3.737274961135228</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-4.551283335670924</v>
+        <v>-12.27599352905037</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.874956157492313</v>
+        <v>-10.89716249780464</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.153167602245489</v>
+        <v>-9.028169897735118</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.336595441738275</v>
+        <v>-4.552414901094373</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>4.01195562777076</v>
+        <v>-1.000640309357436</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.8377394078638147</v>
+        <v>-5.076231381709377</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.5589900044157119</v>
+        <v>-7.526726379659053</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.159965868593986</v>
+        <v>-6.467705453631687</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.7852509388869962</v>
+        <v>-6.715939515064797</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.2807436945670361</v>
+        <v>-7.398093896949611</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.875130616509928</v>
+        <v>-11.18461596508634</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.9829244515021216</v>
+        <v>-6.940670289855078</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-4.536041017392179</v>
+        <v>-11.42138048197319</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-6.044287567502337</v>
+        <v>-13.38083129830556</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-4.133303826499827</v>
+        <v>-6.644505722812042</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-2.951712063431366</v>
+        <v>-7.211950224192535</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-4.751695955875057</v>
+        <v>-9.461025789626319</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-2.753083312358314</v>
+        <v>-11.39130434782608</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.104777634547013</v>
+        <v>-7.205617255158906</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 23.24</t>
+          <t>X ≈ 23.38</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-6.021799494384354</v>
+        <v>-0.3511373664085298</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.594671530829395</v>
+        <v>-0.5970442021123432</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-3.032690579860386</v>
+        <v>0.275921270464103</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.364692218350747</v>
+        <v>1.811178646124034</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-6.462387452802787</v>
+        <v>-2.719698642911482</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-6.275421266705408</v>
+        <v>-2.562765036913397</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-9.428322331548145</v>
+        <v>-3.357847049146116</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-7.325581395348699</v>
+        <v>-5.790427067022819</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-9.665046594386517</v>
+        <v>-3.534838582870627</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-10.43796227042301</v>
+        <v>-4.330890078089844</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-10.16390262826121</v>
+        <v>-10.44163378688988</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-15.2045567936137</v>
+        <v>-6.462896592425011</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-16.32771886046982</v>
+        <v>-9.705448284343866</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-18.92975011786879</v>
+        <v>-9.953682345776855</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-12.44503627259235</v>
+        <v>-2.125198429789577</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-16.61255411255411</v>
+        <v>-5.81921355990638</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-11.98456648762696</v>
+        <v>-1.66777482269503</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-12.08940719144801</v>
+        <v>-1.800658927856759</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-9.492563429571163</v>
+        <v>-1.586196700710857</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-11.68667000055566</v>
+        <v>-7.754588979056138</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-9.848263787569167</v>
+        <v>-6.194373905968966</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-9.924109748978267</v>
+        <v>-8.397196002391915</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-9.649635036496484</v>
+        <v>-6.025901942645696</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-9.725467289719759</v>
+        <v>-6.188040936935039</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 23.86</t>
+          <t>X ≈ 23.98</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-9.640847113431967</v>
+        <v>-14.94613550004043</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-7.975623911781781</v>
+        <v>-8.174498476095174</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-7.41364296081283</v>
+        <v>-9.429192577986754</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.126596980255513</v>
+        <v>-8.267208811882696</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-4.462387452802787</v>
+        <v>-12.05153888180659</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-8.275421266705408</v>
+        <v>-15.40337720563307</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.047369950595751</v>
+        <v>-5.672143428392154</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-7.325581395348834</v>
+        <v>-7.731449836713004</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-13.28409421343413</v>
+        <v>-11.11229285685346</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-10.05700988947062</v>
+        <v>-8.399572422248276</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-7.782950247308698</v>
+        <v>-2.86417951290705</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-4.061699650756694</v>
+        <v>-3.140761467378347</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.815138282387245</v>
+        <v>6.270662204644502</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.594059405940541</v>
+        <v>2.513656213386795</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>1.935916108360097</v>
+        <v>0.07711586658950864</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>6.530303030303031</v>
+        <v>2.392805850321544</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>8.396385893325672</v>
+        <v>4.043311403508767</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>6.291545189504376</v>
+        <v>2.156041333434892</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>6.507436570428588</v>
+        <v>4.124889525492897</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>4.694282380396729</v>
+        <v>4.339475970551923</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.848263787569415</v>
+        <v>-1.491126425565604</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>0.07589025102154068</v>
+        <v>0.1880970173912999</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.3503649635037078</v>
+        <v>2.186117467582108</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>2.274532710280432</v>
+        <v>0.2695925083801569</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 24.48</t>
+          <t>X ≈ 24.58</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-11.33315480573966</v>
+        <v>-4.653737839221712</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.052546988704854</v>
+        <v>-0.4552002304810685</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-13.10595065312041</v>
+        <v>-6.154338776817163</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-13.81890467256321</v>
+        <v>-2.302296531180936</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-18.00084899126432</v>
+        <v>-4.800076893502499</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-13.9677289590131</v>
+        <v>-6.865365509726637</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-7.047369950595758</v>
+        <v>-3.216003077514841</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-5.402504472271907</v>
+        <v>-3.520923520923525</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>8.100521171181256</v>
+        <v>7.718116499871691</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>11.17375934129861</v>
+        <v>13.58873167131908</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>11.44781898346059</v>
+        <v>13.86096668592329</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>9.245992656935613</v>
+        <v>11.36216250922983</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>11.96898443623329</v>
+        <v>16.91393705844579</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>11.7479055597867</v>
+        <v>18.88792521923485</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>9.166685339129209</v>
+        <v>13.76132639290534</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>3.991841491841491</v>
+        <v>9.878185967280558</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>3.857924354864018</v>
+        <v>9.77430555555555</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>3.753083651042836</v>
+        <v>9.641421450393949</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>3.968975031967162</v>
+        <v>7.633661455317565</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>2.232743918858269</v>
+        <v>5.626025678154264</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.2328791721846883</v>
+        <v>5.058581176773529</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1.614351789483081</v>
+        <v>9.42786309926263</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>3.811903425042054</v>
+        <v>9.671497584541065</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>1.812994248741859</v>
+        <v>9.509358590251601</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 25.09</t>
+          <t>X ≈ 25.18</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>5.618412145827286</v>
+        <v>5.641046741277158</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-5.827475763633636</v>
+        <v>-0.7273090740185779</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.1419125947427844</v>
+        <v>-6.063635828971357</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.422893276551804</v>
+        <v>-8.696854354310133</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-6.462387452802787</v>
+        <v>-8.972412494409468</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-8.127273118557262</v>
+        <v>-6.774662561880831</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-10.75107365429952</v>
+        <v>-11.65137722717471</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-9.177433247200689</v>
+        <v>-9.915481344052779</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-16.54335347269339</v>
+        <v>-17.95081774049106</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-9.908861741322475</v>
+        <v>-14.66523658264917</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-5.931098395456893</v>
+        <v>-10.31136891498362</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.506144095201137</v>
+        <v>-10.58795086945497</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.777454310205407</v>
+        <v>-11.70284298690574</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.99853318665194</v>
+        <v>-7.869444395277625</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>1.047027219471154</v>
+        <v>-4.469966124101575</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-3.914141414141355</v>
+        <v>-12.07192741140425</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>1.507497004436672</v>
+        <v>-6.05335884353736</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-6.004751106791915</v>
+        <v>-12.30869192829091</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-9.492563429571298</v>
+        <v>-12.09422970114508</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-9.305717619603271</v>
+        <v>-11.8796432560861</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-6.144560083865592</v>
+        <v>-12.44708775746683</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-4.368554193422845</v>
+        <v>-10.48143395289151</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.3903757772370966</v>
+        <v>-6.156166814551902</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>1.38564382139149</v>
+        <v>-4.277489482310763</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 25.71</t>
+          <t>X ≈ 25.79</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>6.359152886568033</v>
+        <v>7.995834810350942</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>9.357709421551547</v>
+        <v>0.0576202823393217</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>11.25302370585384</v>
+        <v>10.3413877189094</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.873403019744487</v>
+        <v>2.056677827793315</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>13.53761254719721</v>
+        <v>9.473427380001667</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.724578733294635</v>
+        <v>-1.908100552461732</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.714036617262323</v>
+        <v>-6.549336410848355</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.6589147286820705</v>
+        <v>-3.008103008103014</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-7.284094213434031</v>
+        <v>-6.726327944572965</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-14.72367655613719</v>
+        <v>-15.2146871320999</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-11.11628358064203</v>
+        <v>-11.09629827134171</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-11.39503298409003</v>
+        <v>0.1655813126486336</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-12.51819505094605</v>
+        <v>-4.795464650955978</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.26072607260717</v>
+        <v>6.494762826072339</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.0640838916399602</v>
+        <v>5.812608444187624</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-2.80303030303039</v>
+        <v>6.373912463007173</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-2.936947440007678</v>
+        <v>2.423878205127984</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>3.624878522837705</v>
+        <v>6.137147946120677</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.5074365704288013</v>
+        <v>2.505456327112377</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-2.639050952936508</v>
+        <v>-1.126111073982493</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-3.181597120902538</v>
+        <v>2.152598270790627</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-3.257443082311823</v>
+        <v>2.077435748835342</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-2.98296836982977</v>
+        <v>2.321070234113719</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-3.058800623052861</v>
+        <v>2.158931239824255</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 26.32</t>
+          <t>X ≈ 26.39</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-6.582023584020206</v>
+        <v>-7.828341013824883</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.90672902939469</v>
+        <v>3.354323579042671</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-2.472466490224491</v>
+        <v>4.956772334293916</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>8.579285372685661</v>
+        <v>15.79294156405716</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>8.24349490013843</v>
+        <v>12.66024056681496</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>5.489284615647492</v>
+        <v>12.81717417281309</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>10.59968887293366</v>
+        <v>17.73637787486608</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>10.32147742818049</v>
+        <v>17.43145743145743</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>13.30414108068339</v>
+        <v>17.55938634114161</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.7665195222939971</v>
+        <v>8.191906274493576</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.900597306132227</v>
+        <v>2.749855574812287</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>6.644182702184438</v>
+        <v>5.330416477483801</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>8.462197105916566</v>
+        <v>4.215524360033029</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.5824111822946918</v>
+        <v>1.110147441457151</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>13.46532787306592</v>
+        <v>11.8565644881434</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>11.11853832442068</v>
+        <v>9.560725649820199</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>8.043444716854879</v>
+        <v>9.456845238095319</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>10.87978048362203</v>
+        <v>12.18110399007645</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>14.0368483351345</v>
+        <v>6.681280502936474</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>11.28251767451421</v>
+        <v>4.038724090852675</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>10.73997150654827</v>
+        <v>3.471279589471941</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>10.66412554513925</v>
+        <v>3.396117067516734</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>13.87977672820954</v>
+        <v>6.496894409937887</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>16.74512094557441</v>
+        <v>9.191898272791214</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 26.94</t>
+          <t>X ≈ 27</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-8.813260906535362</v>
+        <v>-9.542626728110598</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.196789881321664</v>
+        <v>2.211466436185539</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.655322556428608</v>
+        <v>0.9567723342939587</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.494092674916892</v>
+        <v>-3.635629864514272</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.158302202369576</v>
+        <v>-3.911188004613606</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.345268388466998</v>
+        <v>-3.754254398615522</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>5.021595566645622</v>
+        <v>-0.549336410848305</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>11.63993584603048</v>
+        <v>11.14574314574314</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.111680420330636</v>
+        <v>-4.726327944572752</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.011955627770703</v>
+        <v>2.477620560207967</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.8377394078636655</v>
+        <v>2.749855574812301</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.889285857653249</v>
+        <v>-1.526726379658989</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-4.012447924509409</v>
+        <v>1.358381502890175</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>9.559576647319858</v>
+        <v>13.11014744145712</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>5.453157487670332</v>
+        <v>8.42799305957201</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>9.495820271682348</v>
+        <v>12.98929707839167</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>12.81017899677379</v>
+        <v>16.88541666666666</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>12.70533829295265</v>
+        <v>16.75253256150501</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>9.472953811808019</v>
+        <v>20.96699478865095</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>9.659799621776131</v>
+        <v>21.18158123370988</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>2.220701729672122</v>
+        <v>12.61413673232909</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-4.751695955874908</v>
+        <v>0.5389742103736879</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-11.37377296753068</v>
+        <v>-3.217391304347814</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-21.79443280696096</v>
+        <v>-15.37953029863717</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 27.55</t>
+          <t>X ≈ 27.6</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>26</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.051460578875677</v>
+        <v>0.3035271180432986</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-7.821777757935628</v>
+        <v>-7.634687409968315</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.567489114658926</v>
+        <v>-1.197073819552202</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.565710712052173</v>
+        <v>2.056677827793415</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.229920239504899</v>
+        <v>1.78111968769408</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>5.263040271756189</v>
+        <v>5.784207139845961</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-3.201216104441912</v>
+        <v>1.142971281459445</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>15.75134168157423</v>
+        <v>16.22266622266621</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>19.6389827096428</v>
+        <v>20.19674897850418</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>15.0199131874525</v>
+        <v>15.55454363713098</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>19.14012667576828</v>
+        <v>19.67293249788912</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>18.86137727232028</v>
+        <v>19.39635054341782</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>17.73821520546412</v>
+        <v>18.28145842596711</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>17.51713632901763</v>
+        <v>18.03322436453394</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>16.85899303143702</v>
+        <v>17.35106998264889</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>13.6072261072261</v>
+        <v>14.0662201553147</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>13.47330897024868</v>
+        <v>13.96233974358973</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>17.21462211258131</v>
+        <v>17.675609484582</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>13.58435964735182</v>
+        <v>14.0439178655739</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>13.77120545731979</v>
+        <v>14.25850431063279</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>13.22865928935372</v>
+        <v>13.69105980925215</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>16.99896717409857</v>
+        <v>21.30820497960463</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>21.11959573273437</v>
+        <v>21.55183946488301</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>13.3514557872034</v>
+        <v>13.69739277828578</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 28.17</t>
+          <t>X ≈ 28.2</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-22.87161634420125</v>
+        <v>-20.20929339477745</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-30.8987008348587</v>
+        <v>-28.78853356381447</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-1.567489114658926</v>
+        <v>3.290105667627287</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.411864558206027</v>
+        <v>11.03103680215239</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-2.61623360664894</v>
+        <v>2.422145328719729</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>12.95534796406371</v>
+        <v>19.24574560138461</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>19.87570697248118</v>
+        <v>18.45066358915176</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>11.90518783542028</v>
+        <v>9.812409812409697</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>19.63898270964269</v>
+        <v>18.27367205542712</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>18.86606703360631</v>
+        <v>17.47762056020791</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>19.14012667576824</v>
+        <v>17.74985557481237</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>18.86137727232034</v>
+        <v>17.47327362034108</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>17.73821520546412</v>
+        <v>16.35838150289018</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>9.824828636709711</v>
+        <v>7.776814108123723</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>9.166685339129266</v>
+        <v>7.094659726238667</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>9.761072261072258</v>
+        <v>7.65596374505833</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>1.934847431787212</v>
+        <v>-0.7812499999998863</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>1.83000672796603</v>
+        <v>-0.9141341051614873</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>9.738205801197815</v>
+        <v>7.633661455317494</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>17.61735930347366</v>
+        <v>16.18158123370995</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>17.07481313550763</v>
+        <v>15.61413673232909</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>16.99896717409853</v>
+        <v>15.53897421037367</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>24.96574957888826</v>
+        <v>24.11594202898539</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>32.58222501797268</v>
+        <v>32.28713636802937</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 28.79</t>
+          <t>X ≈ 28.8</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>19.08642561384082</v>
+        <v>13.12403993855613</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>27.84255790640005</v>
+        <v>29.54479976951887</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-9.959097506267319</v>
+        <v>-13.37656099903938</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7.50976665610812</v>
+        <v>2.697703468819064</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>7.173976183560846</v>
+        <v>2.422145328719786</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>7.360942369658225</v>
+        <v>10.91241226805121</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>6.588993685767875</v>
+        <v>10.11733025581849</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6.310782241014934</v>
+        <v>9.812409812409982</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>6.352269422929638</v>
+        <v>9.94033872209409</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>5.579353746893013</v>
+        <v>9.144287226874567</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.853413389054936</v>
+        <v>9.416522241479029</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>5.574663985606811</v>
+        <v>9.139940287007605</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>4.451501918750957</v>
+        <v>8.025048169556833</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-4.860486048604862</v>
+        <v>-0.5565192252095983</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-5.518629346185541</v>
+        <v>-1.23867360709454</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-4.92424242424255</v>
+        <v>-0.6773695882748783</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-14.14906865212924</v>
+        <v>-9.114583333333336</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-14.25390935595043</v>
+        <v>-9.247467438494937</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-14.03801797502584</v>
+        <v>-9.033005211349163</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-13.85117216505768</v>
+        <v>-8.818418766290058</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-5.302809242114627</v>
+        <v>-1.052529934337464</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-5.378655203523863</v>
+        <v>-1.127692456292749</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-5.104180491041809</v>
+        <v>-0.8840579710144851</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>3.910896346644009</v>
+        <v>7.2871363680295</v>
       </c>
     </row>
     <row r="32">
@@ -2754,243 +2754,243 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-20.30751378009864</v>
+        <v>-10.68548387096774</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-31.75340168955956</v>
+        <v>-39.50281927810018</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-44.30253184970174</v>
+        <v>-40.75751337999176</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-45.0154858691444</v>
+        <v>-41.34991557879999</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-56.46238745280271</v>
+        <v>-55.91118800461381</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-22.94208793337199</v>
+        <v>-27.18282582718705</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-23.71403661726243</v>
+        <v>-27.97790783941967</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-23.99224806201551</v>
+        <v>-28.28282828282839</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-23.9507608801008</v>
+        <v>-28.15489937314428</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-13.61256544502618</v>
+        <v>-14.66523658264924</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-24.44961691397537</v>
+        <v>-28.67871585375939</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-13.61725520631225</v>
+        <v>-14.6695835225164</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-3.629306162057411</v>
+        <v>-1.498761354252686</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>18.37183718371853</v>
+        <v>26.82443315574277</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>17.71369388613797</v>
+        <v>26.14227877385752</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>18.30808080808096</v>
+        <v>26.70358279267718</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>18.17416367110349</v>
+        <v>26.59970238095217</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>18.0693229672823</v>
+        <v>26.46681827579057</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>18.28521434820633</v>
+        <v>26.68128050293654</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>18.47206015817419</v>
+        <v>26.89586694799533</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>17.92951399020816</v>
+        <v>26.3284224466146</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>6.742556917688098</v>
+        <v>11.96754563894503</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-4.094079480940948</v>
+        <v>-2.074534161490682</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>6.941199376946876</v>
+        <v>12.04904112993395</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 30.02</t>
+          <t>X ≈ 30.01</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-17.2772107497956</v>
+        <v>-20.20929339477727</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-44.88471482087269</v>
+        <v>-45.45520023048114</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-46.32273386990368</v>
+        <v>-46.70989433237277</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-56.12659698025551</v>
+        <v>-55.63562986451427</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-47.37147836189376</v>
+        <v>-47.57785467128021</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-38.09360308488729</v>
+        <v>-39.08758773194886</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-29.77464267786849</v>
+        <v>-31.5493364108483</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-30.0528541226215</v>
+        <v>-31.8542568542568</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-30.01136694070679</v>
+        <v>-31.72632794457269</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-30.78428261674328</v>
+        <v>-32.52237943979203</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-21.41931388367233</v>
+        <v>-23.91681109185443</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-21.6980632871204</v>
+        <v>-24.19339304632577</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-31.91213444488554</v>
+        <v>-33.64161849710982</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-32.13321332133226</v>
+        <v>-33.88985255854293</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-23.70044752800354</v>
+        <v>-26.2386736070946</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-23.10606060606055</v>
+        <v>-25.67736958827494</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-14.14906865212899</v>
+        <v>-17.44791666666666</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-14.25390935595017</v>
+        <v>-17.58080077182827</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-14.03801797502584</v>
+        <v>-17.36633854468262</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-13.85117216505768</v>
+        <v>-17.15175209962351</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-14.39371833302371</v>
+        <v>-17.71919660100424</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-14.46956429443281</v>
+        <v>-17.79435912295953</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-14.19508958195076</v>
+        <v>-17.55072463768115</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-14.27092183517404</v>
+        <v>-17.71286363197061</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 30.64</t>
+          <t>X ≈ 30.61</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-6.272426060800392</v>
+        <v>-9.098182283666155</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-6.607202859150206</v>
+        <v>-3.788533563814468</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-2.782064013444312</v>
+        <v>0.5123278898495442</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-14.02133382236078</v>
+        <v>-11.19118542006983</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1.432349389302509</v>
+        <v>-0.3556324490580494</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-3.643842319337026</v>
+        <v>-0.1986988430599652</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.8473668915095089</v>
+        <v>4.561774700262873</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-4.69400244798048</v>
+        <v>-1.298701298701346</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.6106426286711368</v>
+        <v>4.38478316653832</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.162273047365403</v>
+        <v>3.588731671318982</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>5.37494448953337</v>
+        <v>9.416522241478901</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>5.096195086085451</v>
+        <v>9.139940287007661</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>9.236190913966134</v>
+        <v>13.58060372511239</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>9.015112037519501</v>
+        <v>13.33236966367928</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>3.093810845202107</v>
+        <v>7.094659726238639</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>3.688197767145098</v>
+        <v>7.655963745058301</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>8.817438524904546</v>
+        <v>13.10763888888888</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>8.712597821083364</v>
+        <v>12.97475478372728</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>14.19164709674457</v>
+        <v>18.74477256642869</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>14.37849290671255</v>
+        <v>18.95935901148763</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>13.83594673874652</v>
+        <v>18.3919145101069</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>13.76010077733738</v>
+        <v>18.31675198815159</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>14.03457548981943</v>
+        <v>18.56038647342996</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>13.95874323659616</v>
+        <v>18.3982474791405</v>
       </c>
     </row>
   </sheetData>
@@ -3180,2133 +3180,2133 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 13.07</t>
+          <t>X &gt; 13.43</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3354</v>
+        <v>3377</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2502637554218978</v>
+        <v>-0.1602737869341269</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.302638129791255</v>
+        <v>-0.03743029814808807</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.3321614793312833</v>
+        <v>-0.04028475811335142</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2878299381689686</v>
+        <v>-0.02774055041359702</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1623578056044508</v>
+        <v>0.007539910580739217</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.166287221628302</v>
+        <v>-0.02524114382907072</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.1503067645975378</v>
+        <v>0.05054573411345586</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.1742460837761328</v>
+        <v>0.02755864824830212</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.1157950148588824</v>
+        <v>0.05433243278574196</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.09976523388866809</v>
+        <v>0.07125075778974832</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.07579254015099224</v>
+        <v>0.1244868432488246</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.01060042318687948</v>
+        <v>0.1894140747522854</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.04247854984632937</v>
+        <v>0.2426790235513323</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.1065445426825775</v>
+        <v>0.3070768775361898</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.150010666790017</v>
+        <v>0.3807396632341522</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.1079353919924984</v>
+        <v>0.3393709336353936</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.008255582425711339</v>
+        <v>0.1939273049645394</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.03583576287658019</v>
+        <v>0.1672532236392641</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.01919602264663212</v>
+        <v>0.2218735586094454</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.04425246177123654</v>
+        <v>0.1582153656234482</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.02662450554955598</v>
+        <v>0.259107146530269</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.001582931338361959</v>
+        <v>0.2311908425134845</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>0.1119148889879966</v>
+        <v>0.3444796251962927</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.08371577527739049</v>
+        <v>0.2888143859940371</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 13.69</t>
+          <t>X &gt; 14.03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3299</v>
+        <v>3308</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.3897935312525576</v>
+        <v>-0.1352415584918631</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.3773101508663999</v>
+        <v>-0.004749780030692818</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.3534019969573521</v>
+        <v>0.04839143913023491</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.2965276822741885</v>
+        <v>0.1936970585626554</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.2538280796864498</v>
+        <v>0.2054335763903055</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.35139353079947</v>
+        <v>0.1387101233327641</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.2620864765306194</v>
+        <v>0.2025432883998803</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.3120067347153537</v>
+        <v>0.1553701012184732</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.2533156980448723</v>
+        <v>0.2101752152226197</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.1940458085771652</v>
+        <v>0.2139239918755749</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1440613584198118</v>
+        <v>0.2024301005575069</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.07317654595452439</v>
+        <v>0.2443579576903474</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.0005716874013259599</v>
+        <v>0.291795181709098</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.007779563087773056</v>
+        <v>0.302431950197267</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.06288104185459531</v>
+        <v>0.3918157909557891</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.01019417030907732</v>
+        <v>0.3680666803217107</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.1662275368014789</v>
+        <v>0.1916006787330318</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.1925697878027322</v>
+        <v>0.1369622537199078</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.1402631874405458</v>
+        <v>0.2184285345005179</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.2079277316226467</v>
+        <v>0.1489725380576488</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.09659813039183263</v>
+        <v>0.2939917610213314</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.1543430116260893</v>
+        <v>0.2670708871109682</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.04357443043573994</v>
+        <v>0.377652515537342</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.04071433427858295</v>
+        <v>0.3242181898754168</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 14.3</t>
+          <t>X &gt; 14.64</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3218</v>
+        <v>3207</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.323969606489662</v>
+        <v>-0.1060942203706574</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.3336486031398067</v>
+        <v>-0.1186667319779886</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2422937789665198</v>
+        <v>0.1612333008366988</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.04259450959461475</v>
+        <v>0.3296629771343262</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.05213104254637813</v>
+        <v>0.3504362979282405</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.09495155100702135</v>
+        <v>0.3387688571984313</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1705589520317545</v>
+        <v>0.5226238869185025</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.06464742345141161</v>
+        <v>0.5146540982718335</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.0929549668937355</v>
+        <v>0.5362418878294832</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.08036634815314159</v>
+        <v>0.6272635282302659</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.06291790496614169</v>
+        <v>0.5138307300917475</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1116749622463971</v>
+        <v>0.6590455992163697</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.1523943988319019</v>
+        <v>0.6809420995340574</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.1355711779356454</v>
+        <v>0.5754878206923735</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.208615209692546</v>
+        <v>0.6269980346963919</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.1707246050085445</v>
+        <v>0.6160466895891901</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.006714881868241207</v>
+        <v>0.4684907176934274</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.03103545565691235</v>
+        <v>0.4475216682588794</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.04823706686060092</v>
+        <v>0.5560358845412523</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.005269345014980331</v>
+        <v>0.5400365435821328</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.1331084570752168</v>
+        <v>0.6452893803041562</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>0.1069461516427168</v>
+        <v>0.6199963356464764</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>0.244742099260101</v>
+        <v>0.6329827604900871</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>0.1875221447116928</v>
+        <v>0.6142333433957674</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 14.92</t>
+          <t>X &gt; 15.24</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3044</v>
+        <v>2958</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.2662139213876245</v>
+        <v>-0.2048206227768148</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.4857348054543209</v>
+        <v>-0.1308154430091051</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.3076070717426234</v>
+        <v>0.1430764631962731</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.121375048140635</v>
+        <v>0.24079726778929</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.1776992386336644</v>
+        <v>0.05119022850698229</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1029849505721643</v>
+        <v>-0.04188880721767418</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.3195036201327568</v>
+        <v>0.4590669504963003</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.3541571667426666</v>
+        <v>0.475938169280461</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.5779522069646958</v>
+        <v>0.8249670436546239</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.7068880830604414</v>
+        <v>0.9904065628996932</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.705764178599054</v>
+        <v>1.080384016414399</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.8061013963637222</v>
+        <v>1.193812340879667</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.8151382823871884</v>
+        <v>1.31122757901008</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.7446815408456402</v>
+        <v>1.386427764907204</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.7940883979113025</v>
+        <v>1.297558276963322</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.8514039477342266</v>
+        <v>1.339937671783439</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.8028100165638392</v>
+        <v>1.357592046093302</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.7505615829470003</v>
+        <v>1.481277500776315</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.8878891778409752</v>
+        <v>1.682485845012629</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.9961196507379384</v>
+        <v>1.68124362398666</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>1.096928204554104</v>
+        <v>1.843451153132868</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>1.00826057275502</v>
+        <v>1.957893129292721</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>1.138542303405124</v>
+        <v>2.154693859558897</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>1.181234418558951</v>
+        <v>2.2499490793208</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 15.54</t>
+          <t>X &gt; 15.84</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2764</v>
+        <v>2657</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.5371513832561519</v>
+        <v>-0.7441192654240254</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2426734451629713</v>
+        <v>-0.447734758290018</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.1533198010282106</v>
+        <v>-0.1888587336672174</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.08748347951459579</v>
+        <v>0.1357560152018209</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.1562430043658551</v>
+        <v>-0.1189607998303472</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2366002746133873</v>
+        <v>-0.1280861743164579</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.2341834474624918</v>
+        <v>0.4439321007448811</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.2283754391835373</v>
+        <v>0.609267275933945</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.6863987696533087</v>
+        <v>0.9832528937505955</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.7622845669728591</v>
+        <v>1.182225577055533</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.7694444231990474</v>
+        <v>1.326634601029475</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.9080409832490659</v>
+        <v>1.371737464477334</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.283606750855661</v>
+        <v>1.553284051615812</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.372718382148243</v>
+        <v>1.81505932747131</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>1.241361474389613</v>
+        <v>1.793334394905841</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>1.641414141414145</v>
+        <v>1.964906834489234</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>1.782167199713143</v>
+        <v>2.034065315315317</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>1.807790676868997</v>
+        <v>2.036798427070224</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>2.045898108890242</v>
+        <v>2.274282542219574</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>2.038213016234877</v>
+        <v>2.32400889248472</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>2.096080267363838</v>
+        <v>2.418648010524571</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>2.368008833812631</v>
+        <v>2.667593992246687</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>2.628845976161877</v>
+        <v>2.934602676088595</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>2.864981335461273</v>
+        <v>3.285129091652514</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 16.15</t>
+          <t>X &gt; 16.44</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2415</v>
+        <v>2312</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.6876067524803631</v>
+        <v>-0.5989223877582148</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.7134162794469461</v>
+        <v>-0.2861700055849852</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.3643818770689364</v>
+        <v>0.2878127470196574</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.4237110279580421</v>
+        <v>1.052542178496481</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1111540426779101</v>
+        <v>0.930464318966429</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.08964239288707887</v>
+        <v>0.724436948780081</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.2305905757200293</v>
+        <v>1.134692861644226</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.3872939645853464</v>
+        <v>1.06994641878363</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.6994448812160741</v>
+        <v>1.413206939148182</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.9384614979315984</v>
+        <v>1.693813497331078</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.072074464388173</v>
+        <v>1.535385290574517</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.435622145699831</v>
+        <v>1.904798168144566</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.779688983129148</v>
+        <v>2.340293647593022</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.037358375012765</v>
+        <v>2.867253384609526</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>2.105883105059704</v>
+        <v>2.85798013410885</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>2.148132167735966</v>
+        <v>2.713435009426156</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>2.204808684407311</v>
+        <v>2.93802554980595</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>2.332024330355267</v>
+        <v>2.918192613273831</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>2.532229958858458</v>
+        <v>3.202644335478638</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>2.620698254724964</v>
+        <v>3.314569143899803</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>2.558684103249554</v>
+        <v>3.076339756087187</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>2.922394181513944</v>
+        <v>3.546752948489619</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>3.471225890655973</v>
+        <v>3.990563732400986</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>3.711385712350769</v>
+        <v>4.201784580255449</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 16.77</t>
+          <t>X &gt; 17.05</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2051</v>
+        <v>1945</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.080460640002009</v>
+        <v>-0.9785241640080287</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.858175869249159</v>
+        <v>-0.7628925381734462</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.05057367361662557</v>
+        <v>0.03369541121703179</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.8642109539486427</v>
+        <v>0.7522613617556075</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.7496164194140533</v>
+        <v>0.7845534012355486</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.8190097260306715</v>
+        <v>0.838870280707205</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.237513770334481</v>
+        <v>1.069955533738728</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.326866496071425</v>
+        <v>1.380735449488654</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.348301518864609</v>
+        <v>1.303430906119907</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.525716942164507</v>
+        <v>1.687471765954442</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.585981791526258</v>
+        <v>1.497931511189876</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.870306177315186</v>
+        <v>1.990975005666755</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.185400673057735</v>
+        <v>2.158791969796283</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>2.771988428789406</v>
+        <v>2.782800083837778</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>2.794447950849104</v>
+        <v>2.972887877427326</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>2.854075514503322</v>
+        <v>3.226341716667712</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>3.060459787345977</v>
+        <v>3.276386394732334</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>3.15007703199344</v>
+        <v>3.246119016097161</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>3.396541628794459</v>
+        <v>3.409272879979724</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>3.613990409593811</v>
+        <v>3.931709504617977</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>3.345504469490102</v>
+        <v>3.601816403786998</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>3.690113339185267</v>
+        <v>4.02125464180677</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>3.995589135043609</v>
+        <v>4.34889852093481</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>4.097058307549993</v>
+        <v>4.42509695072004</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 17.39</t>
+          <t>X &gt; 17.65</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1735</v>
+        <v>1654</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.8646593630026658</v>
+        <v>-1.245166026780488</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.169209249697012</v>
+        <v>-1.067856417502497</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.513929493764067</v>
+        <v>-0.569225247326365</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.2954213683683378</v>
+        <v>0.5312383337928566</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.3936079574094933</v>
+        <v>0.7393561308156507</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.3835913624564782</v>
+        <v>1.077668213234539</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.4483221803634621</v>
+        <v>1.129019090965542</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.744493274381206</v>
+        <v>1.489153061099856</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.7285422024188293</v>
+        <v>1.556622478643689</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.023449880644328</v>
+        <v>1.848841841949145</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.7802681434958956</v>
+        <v>1.395562950870286</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.191173912461693</v>
+        <v>2.086332870643247</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.539692623962807</v>
+        <v>2.482928056699123</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.389226264398594</v>
+        <v>3.504343330211597</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>2.421531758532652</v>
+        <v>3.789540822570807</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>2.670694284618342</v>
+        <v>3.806709412128072</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>2.824464144188617</v>
+        <v>3.823747984683592</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>2.949773037605645</v>
+        <v>4.174539816644121</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>3.280739217149069</v>
+        <v>4.268083059509365</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>3.640197225045746</v>
+        <v>4.664047980989139</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>3.385338053627471</v>
+        <v>4.459360432450012</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>4.036742294775202</v>
+        <v>5.170171308318182</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>4.463268189310099</v>
+        <v>5.474265285736827</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>4.309114842845226</v>
+        <v>5.674883244288957</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 18</t>
+          <t>X &gt; 18.25</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1484</v>
+        <v>1415</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.496074995469499</v>
+        <v>-1.740506586767843</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.527602449675818</v>
+        <v>-1.633056532012347</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.782770477591292</v>
+        <v>-1.050294803515236</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.08562598817967171</v>
+        <v>0.1240874499733593</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3467960549533231</v>
+        <v>-0.1514706901259757</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.3486540527296995</v>
+        <v>0.2881484282395945</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.9607054195253681</v>
+        <v>1.118508112119954</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.422736235875931</v>
+        <v>1.449630071538195</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.396928666781207</v>
+        <v>1.29487346885481</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.768023757904885</v>
+        <v>1.770906779289184</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.503725391991438</v>
+        <v>1.548442147250405</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>2.099807751665914</v>
+        <v>2.049245351789708</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.591719709035914</v>
+        <v>2.630466308543888</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.716535852777746</v>
+        <v>3.795659808948237</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>4.00051906932908</v>
+        <v>4.24424747653314</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>4.191137485215549</v>
+        <v>4.522865982985316</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>4.124515099247496</v>
+        <v>4.418985571260308</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>4.423442901482844</v>
+        <v>4.992815247017433</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>4.639334282407169</v>
+        <v>5.560634364622572</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>4.960769594394037</v>
+        <v>6.05790632204905</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>4.687402430465688</v>
+        <v>5.843818711127668</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>5.665115840247189</v>
+        <v>6.687384104366735</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>6.185944478328437</v>
+        <v>7.07236134582886</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>6.244883114593044</v>
+        <v>7.122236485815016</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 18.62</t>
+          <t>X &gt; 18.86</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1271</v>
+        <v>1223</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.661990418052177</v>
+        <v>-2.520549867930711</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.251485980747297</v>
+        <v>-1.7852629178619</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.68815276473434</v>
+        <v>-0.5869725553217506</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.2396268075710566</v>
+        <v>0.6194805197866273</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.6100700922371942</v>
+        <v>0.3439223796872923</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.0925032615964767</v>
+        <v>0.9096867297573326</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.095824384573397</v>
+        <v>1.749927693812431</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.447038588915525</v>
+        <v>2.507967184990889</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.33116935855643</v>
+        <v>2.145299201788653</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.210496011394838</v>
+        <v>2.902804534042737</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.933808210598464</v>
+        <v>2.357378060503166</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.205806250108765</v>
+        <v>2.898457594175774</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.970921130538251</v>
+        <v>3.745953048270394</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4.166049964555867</v>
+        <v>4.969509665496318</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>4.452045140618104</v>
+        <v>5.432081367012735</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>4.967753856424196</v>
+        <v>5.993385385832397</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>4.676480307172923</v>
+        <v>5.644206527664217</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>4.965030634036239</v>
+        <v>5.756620868945788</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>5.731669457918862</v>
+        <v>6.625212286606683</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>6.154549886297602</v>
+        <v>7.003331029294444</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>6.084072955152969</v>
+        <v>6.926483420800054</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>6.795009055112864</v>
+        <v>7.832514684617458</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>7.148161973731817</v>
+        <v>8.076149169895835</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>6.914973308234742</v>
+        <v>7.750477877977595</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 19.23</t>
+          <t>X &gt; 19.46</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1075</v>
+        <v>1012</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.667723851152083</v>
+        <v>-2.949741352616527</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.19269255742185</v>
+        <v>-2.207505895830273</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.2604396181943898</v>
+        <v>-0.596587349500517</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.347869129308094</v>
+        <v>0.6884808074224864</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.6406766140495819</v>
+        <v>0.3141084380741361</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.717143789056671</v>
+        <v>1.459184336562345</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.859606793590288</v>
+        <v>2.442758450811844</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>3.04651162790698</v>
+        <v>3.027166070644327</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.71590578656587</v>
+        <v>2.858652292581397</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.338338947738684</v>
+        <v>3.44600000684823</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2.40309626431921</v>
+        <v>2.828906958211448</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.589463139940982</v>
+        <v>3.145210379234236</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.605835956805791</v>
+        <v>3.710160159016652</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4.966152429196413</v>
+        <v>5.33939645331477</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>5.238241689755391</v>
+        <v>5.250127446923791</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>5.553558844256514</v>
+        <v>5.613803007245437</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>5.140571939837187</v>
+        <v>5.312294137022398</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>5.314801003457859</v>
+        <v>5.772295407354875</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>5.995808663451946</v>
+        <v>6.777271468492728</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>6.554747496675787</v>
+        <v>7.485929059796774</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>6.570340863593493</v>
+        <v>7.511369933910117</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>7.238680948696022</v>
+        <v>8.127907016697911</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>7.792225428619929</v>
+        <v>8.766798418972336</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>7.344300152140839</v>
+        <v>8.11058827843781</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 19.85</t>
+          <t>X &gt; 20.06</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>907</v>
+        <v>856</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-3.144705988845423</v>
+        <v>-3.776271587923681</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.376946954780685</v>
+        <v>-2.269841975029422</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.830401505465474</v>
+        <v>-1.3049099086967</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.1027304728867193</v>
+        <v>0.7896037803455442</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.09770075006380807</v>
+        <v>0.8645129299658336</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.166695602092823</v>
+        <v>1.722381115403174</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.379311416548674</v>
+        <v>2.91328041158166</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.203635804210151</v>
+        <v>3.776584267238469</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.473347903434664</v>
+        <v>2.969933737670239</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.354235976020007</v>
+        <v>3.926218691049037</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>2.636013369008836</v>
+        <v>3.614341556120657</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>3.239292631492482</v>
+        <v>4.15551661099515</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>3.439173563533828</v>
+        <v>4.325671222516341</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>4.982152018950515</v>
+        <v>5.596128749868278</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>5.536798137025976</v>
+        <v>6.082198667048651</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>5.690170726003146</v>
+        <v>6.059390536335599</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>5.335746422542769</v>
+        <v>5.838687694704056</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>5.341159301963032</v>
+        <v>5.82262601944899</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>6.439079348819</v>
+        <v>6.971667685847095</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>7.39770024147721</v>
+        <v>7.770366280438793</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>7.075661239994083</v>
+        <v>7.436566638871142</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>7.661336778033721</v>
+        <v>7.945516266448571</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>8.266572240240151</v>
+        <v>8.53961804144658</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>7.970232820533958</v>
+        <v>8.143834187344019</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 20.47</t>
+          <t>X &gt; 20.66</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>766</v>
+        <v>723</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.72700899332753</v>
+        <v>-2.920220089106451</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.886851065828779</v>
+        <v>-1.229750714575182</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.366645571778825</v>
+        <v>-0.8246937791223701</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.7924630719638017</v>
+        <v>1.072530578086003</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.10941411377685</v>
+        <v>1.488535370213498</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.165831997002165</v>
+        <v>1.645468976211582</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.743752764808939</v>
+        <v>2.786763174214002</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.248831137288242</v>
+        <v>3.450030835922945</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.854286987610259</v>
+        <v>2.609771640489491</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.647950946038513</v>
+        <v>3.473471182614553</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.138720770968071</v>
+        <v>3.192455851437416</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.165454396240698</v>
+        <v>3.884062002083688</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>3.739420266721396</v>
+        <v>4.705546094868041</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>4.9543727218675</v>
+        <v>5.978750484333965</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>5.210067544391372</v>
+        <v>6.264784207566471</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>5.282261254846119</v>
+        <v>5.996212707713937</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>4.887247512124517</v>
+        <v>5.892332295988929</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>5.043503414047464</v>
+        <v>6.03607336371806</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>6.17323291507622</v>
+        <v>6.665473350199932</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>6.229530422172189</v>
+        <v>6.880059795258916</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>5.948080859950274</v>
+        <v>6.589240466768914</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>6.524976412901502</v>
+        <v>6.929015704149727</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>7.06054773112767</v>
+        <v>7.31096277587347</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>6.72361887216028</v>
+        <v>7.010511195138641</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 21.08</t>
+          <t>X &gt; 21.27</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>649</v>
+        <v>627</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.563805510966631</v>
+        <v>-3.143902645175991</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.436332694524459</v>
+        <v>-2.75185094818449</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-3.179436489318171</v>
+        <v>-2.411648718337631</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.427059229870309</v>
+        <v>-1.090175319059732</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.3761008580416174</v>
+        <v>-0.2493060269421505</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.4973010818055599</v>
+        <v>-0.4113516872917629</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.7338318984027055</v>
+        <v>0.5479522653878064</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.996452502956245</v>
+        <v>1.678438520543779</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.421606865148306</v>
+        <v>1.327898530706349</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.189523238418438</v>
+        <v>2.126743367225451</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.463582880580361</v>
+        <v>2.558468015003633</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.109332706716337</v>
+        <v>3.557803125923087</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>3.372919484236185</v>
+        <v>4.037807340210755</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>4.846755862026882</v>
+        <v>5.384469610516071</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>4.804945384168967</v>
+        <v>5.180784128152546</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>4.012583461736</v>
+        <v>4.466171081581457</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>3.878666324758527</v>
+        <v>4.202801036682615</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>3.927908825868009</v>
+        <v>4.229406564694848</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>4.760133026514985</v>
+        <v>4.922337691362159</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>4.638812426621683</v>
+        <v>4.498965603725772</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>4.250349463586325</v>
+        <v>4.25050036869272</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>4.790836321899867</v>
+        <v>4.972786012606655</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>5.37347744424325</v>
+        <v>5.535399764232714</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>5.143561986089303</v>
+        <v>5.213771136769417</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 21.7</t>
+          <t>X &gt; 21.87</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>579</v>
+        <v>552</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-3.899914470944921</v>
+        <v>-3.361467307820739</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.852998695892317</v>
+        <v>-2.882736462365187</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.736613599845583</v>
+        <v>-2.144676941068369</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.240586617561213</v>
+        <v>-1.650122618137466</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.712819231731977</v>
+        <v>-1.201043077077372</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.871276188985199</v>
+        <v>-1.587587731948858</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.3979744410966219</v>
+        <v>0.1535621398763922</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.8782182592280279</v>
+        <v>1.479076479076475</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.9197054411427317</v>
+        <v>1.607005388760584</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.528482338508653</v>
+        <v>2.260229255860082</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.629830408995282</v>
+        <v>2.351304850174564</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.732773578949697</v>
+        <v>3.1616794174424</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3.164015657171298</v>
+        <v>3.496062662310464</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>4.497340925802433</v>
+        <v>4.697103963196199</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>4.011909199897168</v>
+        <v>4.377268421890847</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>3.224603548437749</v>
+        <v>3.308137658101813</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>3.436109554810869</v>
+        <v>3.566576086956523</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>3.158557279314394</v>
+        <v>3.252532561505063</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>3.719871803589328</v>
+        <v>3.829313629230548</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>3.388582898531446</v>
+        <v>3.31926239313011</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>2.846036730565416</v>
+        <v>2.751817891749376</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>3.633748627532817</v>
+        <v>3.582452471243371</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>4.599069626716087</v>
+        <v>4.550724637681157</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>4.695948945168119</v>
+        <v>4.750904483971404</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 22.32</t>
+          <t>X &gt; 22.47</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>507</v>
+        <v>487</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-3.344989125266288</v>
+        <v>-3.234618514558242</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-4.074243241170343</v>
+        <v>-3.891202968331918</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.934353019984371</v>
+        <v>-3.29784778890933</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-3.266636427987265</v>
+        <v>-2.658217133508117</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.813472265426064</v>
+        <v>-2.728436464572532</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.41546071443716</v>
+        <v>-3.598196903748999</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.017784151779189</v>
+        <v>-2.134552016597723</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.3236090087610606</v>
+        <v>-0.3860843696572687</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.6765991444005977</v>
+        <v>-0.4634942690080663</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.3256331085569926</v>
+        <v>0.5885035170867638</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.5996927507189156</v>
+        <v>0.6553997226561918</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.504375299933649</v>
+        <v>1.610850622394338</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.353599820848729</v>
+        <v>2.549346595292633</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.710430214619102</v>
+        <v>4.149161815173692</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>3.644002893369908</v>
+        <v>3.877685051358462</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>2.660480545095929</v>
+        <v>2.38560097982905</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>3.118279384449814</v>
+        <v>3.513753422313485</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>2.421722704297274</v>
+        <v>2.764852890047152</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>3.032091402775841</v>
+        <v>3.389992735262751</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>2.824459895189626</v>
+        <v>3.399240371286815</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>2.084675068446479</v>
+        <v>2.421118251836276</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>2.797783742145853</v>
+        <v>3.167310966020622</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>3.861213089736395</v>
+        <v>4.026961878403725</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>3.982619495290244</v>
+        <v>4.070161693149167</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 22.93</t>
+          <t>X &gt; 23.08</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-3.75220568804221</v>
+        <v>-3.429248043303346</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-4.309699635612517</v>
+        <v>-3.901912248621727</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-3.520547192438606</v>
+        <v>-3.115790023982697</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.119915465778895</v>
+        <v>-2.574405374718353</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-3.232988789105683</v>
+        <v>-2.623206145203177</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-3.26873975222879</v>
+        <v>-2.693029908819604</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.03623409313473</v>
+        <v>-1.220538224907202</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.08727404568290353</v>
+        <v>0.5153576582147963</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.9366554606501651</v>
+        <v>-0.03698554094463447</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.1505510921432247</v>
+        <v>0.7542645511376236</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.5689428484596704</v>
+        <v>1.253256935356461</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.626496340334626</v>
+        <v>2.563976568186753</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.507788616462918</v>
+        <v>3.489900777266591</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>4.29116408300073</v>
+        <v>5.282483042364099</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>4.078455083861151</v>
+        <v>5.053843399708065</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>2.891104812040226</v>
+        <v>3.80108846161162</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>3.648056271944711</v>
+        <v>4.604237528344669</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>3.320498418903043</v>
+        <v>4.24459605356855</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>4.204541247488834</v>
+        <v>5.13933038955787</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>3.723235609795395</v>
+        <v>4.446887356158804</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>2.735255143388379</v>
+        <v>3.425928115549034</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>3.772994928081729</v>
+        <v>4.484552441666324</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>4.715621088225248</v>
+        <v>5.635216405402751</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>4.639788835001973</v>
+        <v>5.24632004149877</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 23.55</t>
+          <t>X &gt; 23.68</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-3.517996990581842</v>
+        <v>-3.796433834709582</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-4.589874526032396</v>
+        <v>-4.296147777012436</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-3.570891118060928</v>
+        <v>-3.520385026112137</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-3.301044154702687</v>
+        <v>-3.097558798524425</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.899733890149228</v>
+        <v>-2.611695618826801</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.958467949752091</v>
+        <v>-2.708569119427708</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.273414176639982</v>
+        <v>-0.9655800656705793</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.6596765899091537</v>
+        <v>1.267570556910655</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.03593696527688195</v>
+        <v>0.3802710401988207</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.9110490785883485</v>
+        <v>1.360869291172378</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.676509212150762</v>
+        <v>2.648332732172655</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.363361774304728</v>
+        <v>3.640786310696278</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4.451501918750822</v>
+        <v>5.063965259235353</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>6.687425499306684</v>
+        <v>7.099995157193099</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>5.783581956025891</v>
+        <v>5.910226562110076</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>4.903767403767404</v>
+        <v>4.948687941335841</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>5.261250758190428</v>
+        <v>5.352421742808794</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>4.910709808668997</v>
+        <v>4.965730531048209</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>5.618001680993807</v>
+        <v>5.941614077990934</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>5.31344699956135</v>
+        <v>5.902393416450934</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>4.033800094494573</v>
+        <v>4.573527595273255</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>5.186455361586702</v>
+        <v>6.021207712911867</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>6.198030811169502</v>
+        <v>7.026263517987211</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>6.122198557946227</v>
+        <v>6.610317417098749</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 24.17</t>
+          <t>X &gt; 24.28</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.660454956569225</v>
+        <v>-1.910579250365792</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-4.115679934190744</v>
+        <v>-3.640165611292211</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-3.032690579860386</v>
+        <v>-2.520972472827708</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-3.4655325544852</v>
+        <v>-2.223166956502403</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.680874847760769</v>
+        <v>-1.01504557137919</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.213796616845464</v>
+        <v>-0.5613760603365918</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.30507303182825</v>
+        <v>-0.1695144523912617</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.778060061233802</v>
+        <v>2.78966005968973</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.819547243148506</v>
+        <v>2.32411715928481</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.447191791201647</v>
+        <v>3.011745189288035</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.001363478181496</v>
+        <v>3.580716108936876</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.403286343641064</v>
+        <v>4.787813679688128</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.680684500874577</v>
+        <v>4.859865182415405</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>7.260726072607255</v>
+        <v>7.875726076471899</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>6.322470730208771</v>
+        <v>6.89683578954233</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>4.675961293608353</v>
+        <v>5.380988473050422</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>4.822156201448806</v>
+        <v>5.573843966369928</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>4.717315497627624</v>
+        <v>5.440959861208327</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>5.493430968187802</v>
+        <v>6.248893898443129</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>5.400164733337903</v>
+        <v>6.166744438457599</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>4.857618565371872</v>
+        <v>5.599299937076864</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>5.902220783234476</v>
+        <v>7.007816940344121</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>7.017031630170308</v>
+        <v>7.844923235711526</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>6.661087332129107</v>
+        <v>7.682784241422063</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 24.78</t>
+          <t>X &gt; 24.88</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.181830719989343</v>
+        <v>-1.487832207562654</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-4.467427190470303</v>
+        <v>-4.13099931723913</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.315282305075065</v>
+        <v>-1.961035884884133</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.700367472058794</v>
+        <v>-2.210972330267694</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.06894482985197214</v>
+        <v>-0.4317359498190854</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.2098474962136052</v>
+        <v>0.4101291630283157</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.326058475185917</v>
+        <v>0.2999786576449139</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.002287457110185</v>
+        <v>3.76218150190752</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.7486926718117743</v>
+        <v>1.49285013761903</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.9593835531523283</v>
+        <v>1.381730149249009</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.561312047773264</v>
+        <v>1.996430917278005</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.577644611538389</v>
+        <v>3.774643483354645</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.438089102059315</v>
+        <v>3.002217119328535</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>6.495698750202891</v>
+        <v>6.178640592141996</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>5.837555452622333</v>
+        <v>5.838951963681588</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>4.792598112270241</v>
+        <v>4.687927215377975</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>4.986549827751787</v>
+        <v>4.926512557077622</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>4.881709123930605</v>
+        <v>4.793628451916021</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>5.75333820977297</v>
+        <v>6.035487939335766</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>5.940184019740997</v>
+        <v>6.25007438439475</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>5.725506704233972</v>
+        <v>5.682629883014016</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>6.633267300201929</v>
+        <v>6.634864621332703</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>7.563479717602007</v>
+        <v>7.563430613460405</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>7.487647464378732</v>
+        <v>7.401291619170941</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 25.4</t>
+          <t>X &gt; 25.49</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-2.644831177176989</v>
+        <v>-2.925342777493313</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-4.174827099032775</v>
+        <v>-4.817340148176612</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.62878240304385</v>
+        <v>-1.13376264512992</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.544923673482607</v>
+        <v>-0.9031195764484323</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.30653684998606</v>
+        <v>1.290458085921365</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.493503036083439</v>
+        <v>1.858914325664315</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.916773475699067</v>
+        <v>2.709922848411011</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.622625775965908</v>
+        <v>6.520228742450961</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>4.468893834374633</v>
+        <v>5.413589750900492</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.297571783836155</v>
+        <v>4.617538255681154</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.173225051496082</v>
+        <v>4.478250636540636</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>4.886507520558048</v>
+        <v>6.670804484538479</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>4.560158202705914</v>
+        <v>5.967435000832559</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>8.323143071279233</v>
+        <v>9.011382009358307</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>6.868187024694699</v>
+        <v>7.9177049937284</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>6.665761197633699</v>
+        <v>8.067486378803196</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>5.73503131165225</v>
+        <v>7.14056069958847</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>7.223816105839035</v>
+        <v>8.242244495661453</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>9.033332984771327</v>
+        <v>9.691274624041782</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>9.220178794739354</v>
+        <v>9.905861069100766</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>8.279226252271336</v>
+        <v>9.338416567720031</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>9.000193039866225</v>
+        <v>10.08629931325446</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>9.274667752348279</v>
+        <v>10.32993379853284</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>8.800429124623001</v>
+        <v>9.756272170498512</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 26.02</t>
+          <t>X &gt; 26.09</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.867091457323369</v>
+        <v>-4.233870967741936</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-6.011823006804406</v>
+        <v>-5.401436789620917</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.377443865790141</v>
+        <v>-2.50866545372449</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-2.280443134101667</v>
+        <v>-1.257749680182478</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.353790167734914</v>
+        <v>0.310010152068422</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.190642081710877</v>
+        <v>2.310261730416741</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.681136836734559</v>
+        <v>3.819327183621809</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>6.475323582026725</v>
+        <v>7.661872178001204</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>6.064322076158625</v>
+        <v>6.868142101510202</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.743895087904939</v>
+        <v>6.993749592465974</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.112977354501254</v>
+        <v>6.344325620895198</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>7.096671389967284</v>
+        <v>7.45023214568657</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.878486698676774</v>
+        <v>7.256999014410916</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>8.467362573361413</v>
+        <v>9.3129124184156</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>7.809219275780855</v>
+        <v>8.169928543442971</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>7.951117509941042</v>
+        <v>8.270403069175075</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>6.912222997397947</v>
+        <v>7.705693164362522</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>7.712359669142387</v>
+        <v>8.494468045376024</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>10.19069448898073</v>
+        <v>10.55224824487203</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>10.83002898673156</v>
+        <v>11.22766418301858</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>9.834994130982729</v>
+        <v>10.19939018855028</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>10.66412554513925</v>
+        <v>11.04588665277011</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>10.9386002576213</v>
+        <v>11.28952113804849</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>10.41027931661521</v>
+        <v>10.66655265067147</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 26.63</t>
+          <t>X &gt; 26.69</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-3.373467434287583</v>
+        <v>-3.542626728110598</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-7.451559740658787</v>
+        <v>-7.085236860517767</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-3.541985206802082</v>
+        <v>-3.944326566804953</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-4.254939226244822</v>
+        <v>-4.536728765613177</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.916932907348247</v>
+        <v>-2.06503415845976</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.4090707119042207</v>
+        <v>0.2897016453405215</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.241400102880178</v>
+        <v>1.142971281459445</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>5.776022882726032</v>
+        <v>5.783105783105775</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.747991348063202</v>
+        <v>4.812133593888788</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>6.648872463470553</v>
+        <v>6.763334845922202</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>6.38817274734371</v>
+        <v>7.035569860526536</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>7.178942060473261</v>
+        <v>7.857889004956334</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>6.590539351905896</v>
+        <v>7.841897986406657</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>10.1127759834807</v>
+        <v>10.89036722167685</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>6.780835894456295</v>
+        <v>7.460960092539032</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>7.375222816399287</v>
+        <v>8.022264111358695</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>6.706546321133047</v>
+        <v>7.368933150183146</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>7.136464975600632</v>
+        <v>7.785499594472086</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>9.491393789680039</v>
+        <v>11.29666511832117</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>10.74775831622561</v>
+        <v>12.61015266228125</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>9.670452789970803</v>
+        <v>11.49325761144996</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>10.66412554513925</v>
+        <v>12.51699618839577</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>10.40384089933254</v>
+        <v>12.21118012422361</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>9.258489929531713</v>
+        <v>10.95014003103305</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 27.25</t>
+          <t>X &gt; 27.3</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.375024328621848</v>
+        <v>-2.587212715371741</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-9.038915051022286</v>
+        <v>-8.565603627508736</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-5.413642960812773</v>
+        <v>-4.724756328126432</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-5.49368558785045</v>
+        <v>-4.680215851775415</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-2.664919098372408</v>
+        <v>-1.771060616078579</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.05369265734522344</v>
+        <v>0.9336436905564511</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.547566758264999</v>
+        <v>1.412447028642205</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4.699735060347365</v>
+        <v>4.929182636188997</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>6.007045027072202</v>
+        <v>6.330996896191579</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>7.132863528250908</v>
+        <v>7.445773426449946</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>7.406923170412831</v>
+        <v>7.71800844105428</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>9.026907944180024</v>
+        <v>9.352254512060682</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>8.536657269728956</v>
+        <v>8.874305069769157</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>10.21431257049757</v>
+        <v>10.53689903381375</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>7.024523703296758</v>
+        <v>7.306973951291745</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>6.985999232834672</v>
+        <v>7.231335294952174</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>5.586259311047087</v>
+        <v>5.853569532908701</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>6.114329999630954</v>
+        <v>6.357628102906332</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>9.494778342580595</v>
+        <v>9.756803705848284</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>10.94744693735875</v>
+        <v>11.24527550122573</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>11.03781216179778</v>
+        <v>11.31477367500425</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>13.49361177000895</v>
+        <v>14.42432452884514</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>14.40099787489605</v>
+        <v>14.66795901412352</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>14.95807701407784</v>
+        <v>15.14276269499329</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 27.86</t>
+          <t>X &gt; 27.9</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.640847113431967</v>
+        <v>-3.160947338797627</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-9.278654214812086</v>
+        <v>-8.750365624883173</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-6.171218718388531</v>
+        <v>-5.424907055019027</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-6.884172737831271</v>
+        <v>-6.01730925382725</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-3.432084422499756</v>
+        <v>-2.476073500796815</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.9723909636751102</v>
+        <v>-0.02906355892086054</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.285963382737577</v>
+        <v>1.465930764724277</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2.522903453136017</v>
+        <v>2.687727878567564</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.321966392626479</v>
+        <v>3.579015566877629</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>5.579353746893013</v>
+        <v>5.836399186162105</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.095837631479178</v>
+        <v>5.345275422140496</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>7.089815500758462</v>
+        <v>7.358769803547048</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>6.724229191478095</v>
+        <v>7.007236464722233</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>8.775877587758771</v>
+        <v>9.049078739166994</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>5.087431259875196</v>
+        <v>5.313489242778111</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>5.681818181818187</v>
+        <v>5.874793261597773</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>4.032749529689191</v>
+        <v>4.244195292620859</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>3.927908825868009</v>
+        <v>4.111311187459258</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>8.689254752246875</v>
+        <v>8.905926086360765</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>10.39125207736643</v>
+        <v>10.64723008867166</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>10.60628166697615</v>
+        <v>10.84314436591687</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>12.80316297829433</v>
+        <v>13.05805817983944</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>13.07763769077638</v>
+        <v>13.30169266511782</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>15.27453271028038</v>
+        <v>15.42963000670623</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 28.48</t>
+          <t>X &gt; 28.5</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>119</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-1.540006777297506</v>
+        <v>-1.441786391976137</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-6.91680038237002</v>
+        <v>-6.729710034402707</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-6.674147162493448</v>
+        <v>-6.303731867386723</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-8.227437316389967</v>
+        <v>-7.736470200648725</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-3.521210982214548</v>
+        <v>-2.970011534025367</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-2.49390866166339</v>
+        <v>-1.972741793573505</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.7448489421923981</v>
+        <v>-0.2468154024448808</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.497948016415876</v>
+        <v>1.96927255750785</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1.53943519833058</v>
+        <v>2.097201467191958</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>4.127864060109211</v>
+        <v>4.662494509787741</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>3.561587567817355</v>
+        <v>4.094393389938297</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>5.803846567730695</v>
+        <v>6.338819838828336</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>5.521020635328362</v>
+        <v>6.064263855831349</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>8.6612862966969</v>
+        <v>9.177374332213368</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>4.641798461301214</v>
+        <v>5.133875412513184</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>5.236185383244205</v>
+        <v>5.695179431332846</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>4.261932111812946</v>
+        <v>4.750962885154053</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>4.157091407991764</v>
+        <v>4.618078779992452</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>8.574663461185004</v>
+        <v>9.034221679407139</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>9.601845405606809</v>
+        <v>10.0891442589199</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>9.899635372094558</v>
+        <v>10.36203589199295</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>12.34479781404681</v>
+        <v>12.80788177339901</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>11.77893639207508</v>
+        <v>12.21118012422361</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>13.38377640775936</v>
+        <v>13.7297133988417</v>
       </c>
     </row>
     <row r="32">
@@ -5316,79 +5316,79 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-3.640847113431967</v>
+        <v>-3.075337008484432</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-10.45710539326326</v>
+        <v>-10.79787935820699</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-6.339568886738697</v>
+        <v>-5.510517385332214</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-9.830300683959216</v>
+        <v>-8.906657901897447</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-4.610535600950939</v>
+        <v>-3.57473940648277</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-3.497643488927629</v>
+        <v>-3.417805800484686</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.491814395040201</v>
+        <v>-1.409149494960396</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.007751937984501</v>
+        <v>1.089668379387994</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.049239119899205</v>
+        <v>1.217597289072103</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>3.980027147566418</v>
+        <v>4.159863550862113</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>3.328160863802417</v>
+        <v>3.497519126214108</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.827189238132192</v>
+        <v>6.02467548949982</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.629953097201998</v>
+        <v>5.844362811301387</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>10.03850385038504</v>
+        <v>10.26902594612996</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>5.676656849100787</v>
+        <v>5.848553807235554</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>6.271043771043779</v>
+        <v>6.409857826055216</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>6.137126634066306</v>
+        <v>6.305977414330208</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>6.032285930245123</v>
+        <v>6.173093309168607</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>10.87780694079907</v>
+        <v>11.06045273257607</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>11.99057867669302</v>
+        <v>12.20961861688738</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>11.44803250872699</v>
+        <v>11.64217411550665</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>14.14996432509567</v>
+        <v>14.37074991130837</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>13.4985131116518</v>
+        <v>13.67980495733442</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>14.34860678435445</v>
+        <v>14.45224540229729</v>
       </c>
     </row>
     <row r="33">
@@ -5398,243 +5398,243 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.125695598280451</v>
+        <v>-2.542626728110598</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-8.521078457236328</v>
+        <v>-8.788533563814468</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-2.88839043556024</v>
+        <v>-3.043227665706048</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-6.631647485306019</v>
+        <v>-6.635629864514272</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.1032691128537735</v>
+        <v>0.08881199538640061</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.729966721250868</v>
+        <v>-1.754254398615522</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.5283876251618196</v>
+        <v>0.4506635891517519</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>3.280479210711775</v>
+        <v>3.14574314574314</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3.321966392626479</v>
+        <v>3.273672055427248</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>5.579353746893013</v>
+        <v>5.47762056020791</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>5.853413389054936</v>
+        <v>5.749855574812244</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.594866005808967</v>
+        <v>7.473273620340947</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>6.471703938952849</v>
+        <v>6.358381502890175</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>9.280928092809276</v>
+        <v>9.110147441457066</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>4.58238075482469</v>
+        <v>4.42799305957201</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>5.176767676767682</v>
+        <v>4.989297078391672</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>5.042850539790209</v>
+        <v>4.885416666666664</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>4.938009835969027</v>
+        <v>4.752532561505063</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>10.2044062673984</v>
+        <v>9.966994788650837</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>11.40135308746744</v>
+        <v>11.18158123370982</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>10.85880691950141</v>
+        <v>10.61413673232909</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>14.82336499849635</v>
+        <v>14.5389742103738</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>15.09783971097841</v>
+        <v>14.78260869565218</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>15.02200745775513</v>
+        <v>14.62046970136272</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 30.33</t>
+          <t>X &gt; 30.31</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>88</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.2317562043410604</v>
+        <v>-0.1335358190196914</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-3.975623911781781</v>
+        <v>-3.788533563814468</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.540902493732688</v>
+        <v>2.911317788839412</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.4447787984373335</v>
+        <v>0.04618831730390838</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>6.037612547197213</v>
+        <v>6.588811995386394</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>2.815487824203686</v>
+        <v>3.336654692293571</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>4.316266413040609</v>
+        <v>4.814299952788126</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>7.447145877378432</v>
+        <v>7.918470418470406</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>7.488633059293136</v>
+        <v>8.046399328154514</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>10.12480829234755</v>
+        <v>10.65943874202608</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>9.262504298145849</v>
+        <v>9.795310120266791</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>11.25648216742513</v>
+        <v>11.79145543852277</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>11.26968373693264</v>
+        <v>11.81292695743563</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>14.45769576957696</v>
+        <v>14.97378380509343</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>8.117734290178213</v>
+        <v>8.609811241390183</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>8.712121212121204</v>
+        <v>9.171115260209845</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>7.441840438780105</v>
+        <v>7.930871212121211</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>7.336999734958923</v>
+        <v>7.79798710695961</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>13.23470929770144</v>
+        <v>13.69426751592357</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>14.55791874403309</v>
+        <v>15.04521759734618</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>14.01537257606706</v>
+        <v>14.47777309596545</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>18.4849811601125</v>
+        <v>18.94806511946471</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>18.75945587259456</v>
+        <v>19.19169960474309</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>18.68362361937128</v>
+        <v>19.02956061045362</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 30.95</t>
+          <t>X &gt; 30.91</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.431616654683978</v>
+        <v>2.171658986175117</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-3.25098623062236</v>
+        <v>-3.788533563814468</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>4.006646894259688</v>
+        <v>3.528200905722528</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3.293692874816948</v>
+        <v>2.935798706914305</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>7.30572848922619</v>
+        <v>8.374526281100685</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>4.594143950685904</v>
+        <v>4.245745601384478</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>5.271470629114383</v>
+        <v>4.87923501772319</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>10.79036063363668</v>
+        <v>10.28860028860028</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>9.382572453232527</v>
+        <v>8.987957769712956</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>12.95748286415257</v>
+        <v>12.47762056020791</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>10.33299178167682</v>
+        <v>9.892712717669383</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>12.95279310286649</v>
+        <v>12.47327362034095</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>11.82963103601038</v>
+        <v>11.35838150289018</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>15.95637824652032</v>
+        <v>15.39586172717136</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>9.501133499664384</v>
+        <v>8.99942163100058</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>10.09552042160738</v>
+        <v>9.560725649820242</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>7.063052559992215</v>
+        <v>6.599702380952372</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>6.958211856171033</v>
+        <v>6.466818275790772</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>12.97120468637073</v>
+        <v>12.39556621722227</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>14.60732585865759</v>
+        <v>14.03872409085267</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>14.06477969069156</v>
+        <v>13.47127958947193</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>19.78603517855783</v>
+        <v>19.11040278180237</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>20.06050989103989</v>
+        <v>19.35403726708075</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>19.98467763781661</v>
+        <v>19.19189827279128</v>
       </c>
     </row>
   </sheetData>
@@ -5824,2133 +5824,2133 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 13.07</t>
+          <t>X &lt; 13.43</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>13.52333199104564</v>
+        <v>7.326938489280714</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>16.17362981956151</v>
+        <v>1.283930204301477</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>17.72068539739619</v>
+        <v>1.478511464728733</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>14.02265675108778</v>
+        <v>0.8861092659205099</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>9.20925433824199</v>
+        <v>-2.287999598816498</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.8887578377722</v>
+        <v>0.767484731819259</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10.11680915388185</v>
+        <v>-1.476872642732296</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>11.33113502256161</v>
+        <v>-0.3325177238220789</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.387547577610647</v>
+        <v>-3.103139538775643</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>7.614631901574157</v>
+        <v>-3.899191033994981</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>6.396154230303246</v>
+        <v>-6.525506744028334</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>3.132330199989575</v>
+        <v>-9.700639423137311</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.516630819700616</v>
+        <v>-12.26480690290693</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-2.689522683611642</v>
+        <v>-15.41159168897772</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-4.840203294625034</v>
+        <v>-18.99229679550045</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-2.753279059249209</v>
+        <v>-16.98171741436195</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>3.082953057504668</v>
+        <v>-9.83922101449275</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>4.470649667116319</v>
+        <v>-8.522829757335515</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>1.70146642117497</v>
+        <v>-11.20691825482742</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>4.873386858008672</v>
+        <v>-8.093781085130757</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>1.345766063176967</v>
+        <v>-11.55977631114917</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>2.762457415200707</v>
+        <v>-11.63493883310446</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-2.933217126048589</v>
+        <v>-17.18840579710145</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-1.516512065839024</v>
+        <v>-14.45199406675323</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 13.69</t>
+          <t>X &lt; 14.03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10.35915288656803</v>
+        <v>3.194961924371675</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>10.02437608821822</v>
+        <v>0.1121756560436893</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>9.386357039187224</v>
+        <v>-1.142518445847891</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>7.873403019744487</v>
+        <v>-4.57180007728023</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6.737612547197216</v>
+        <v>-4.847358217379565</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>9.324578733294601</v>
+        <v>-3.271984895069423</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6.952630049404242</v>
+        <v>-4.776286765458174</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>8.274418604651174</v>
+        <v>-3.662767492554735</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>6.71590578656587</v>
+        <v>-4.953278299182685</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.142990110529382</v>
+        <v>-5.04010993624599</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3.817049752691304</v>
+        <v>-4.767874921641656</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.938300349243306</v>
+        <v>-5.753676734268986</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.01513828238718418</v>
+        <v>-6.868568851719758</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.2059405940594061</v>
+        <v>-7.116802913152867</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-1.664083891639962</v>
+        <v>-9.217397011349981</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.2696969696969731</v>
+        <v>-8.656092992530318</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>4.396385893325558</v>
+        <v>-4.504654255319153</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>5.091545189504373</v>
+        <v>-3.219098644168696</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>3.707436570428705</v>
+        <v>-5.132295991491006</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>5.494282380396726</v>
+        <v>-3.499269830119964</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>2.551736212430697</v>
+        <v>-6.903593764124814</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>4.075890251021598</v>
+        <v>-6.269536427924074</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>1.150364963503648</v>
+        <v>-8.862781375269812</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>1.074532710280373</v>
+        <v>-7.606480653247218</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 14.3</t>
+          <t>X &lt; 14.64</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5.09701696423793</v>
+        <v>1.416050957839808</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5.247677059091998</v>
+        <v>1.583367262631818</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3.809658010061007</v>
+        <v>-2.150665682234973</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.6695195245988543</v>
+        <v>-4.395960443026674</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.8191659452554632</v>
+        <v>-4.671518583126009</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.491569024556725</v>
+        <v>-4.514584977127925</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-2.67843791176081</v>
+        <v>-6.962559551344107</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.014901783698349</v>
+        <v>-6.85425685425686</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.458851494987528</v>
+        <v>-7.139551085068618</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-1.260893384616253</v>
+        <v>-8.348825720783822</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.9868337424543299</v>
+        <v>-6.83692128469189</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.751020039106209</v>
+        <v>-8.766395801146658</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-2.388745212758444</v>
+        <v>-9.054841637605691</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-2.124387196001152</v>
+        <v>-7.650183137055336</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-3.267967386785593</v>
+        <v>-8.332337518940392</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-2.673580464842601</v>
+        <v>-8.184256640616596</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.10512375740322</v>
+        <v>-6.22202134986226</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.4857199467859274</v>
+        <v>-5.941682314527995</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.7546993519014009</v>
+        <v>-7.380112649365699</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.08241664872949173</v>
+        <v>-7.165526204306715</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-2.081273496307169</v>
+        <v>-8.559416986679182</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-1.671682564512388</v>
+        <v>-8.221356368138601</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-3.824392318049746</v>
+        <v>-8.390945023356089</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-2.929350784865257</v>
+        <v>-8.139860877149687</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 14.92</t>
+          <t>X &lt; 15.24</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>380</v>
+        <v>491</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.148626570778553</v>
+        <v>1.243523984720362</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.919112930323486</v>
+        <v>0.7939511612364498</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.481093881292495</v>
+        <v>-0.8680749162152068</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.9786661776392265</v>
+        <v>-1.46047711502343</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.43234938930248</v>
+        <v>-0.310373340662494</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.8298418911893322</v>
+        <v>0.2538922408956807</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.573685740069443</v>
+        <v>-2.78151563691749</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.851897184822519</v>
+        <v>-2.882770092546068</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.652515266065713</v>
+        <v>-4.995167048442404</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-5.688588836839045</v>
+        <v>-5.994884531441791</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-5.677687089413965</v>
+        <v>-6.537313467957617</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-6.482752282335639</v>
+        <v>-7.22122739798899</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-6.553282770244394</v>
+        <v>-7.928787539879686</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.984887962480457</v>
+        <v>-8.38068758909283</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-6.379873365324173</v>
+        <v>-7.840846044297642</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-6.838118022328551</v>
+        <v>-8.094205976598147</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-6.445719369832339</v>
+        <v>-8.198086388323155</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-6.024244284179836</v>
+        <v>-8.941968456824874</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-7.124142376939723</v>
+        <v>-10.15316814413939</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-7.989928145919059</v>
+        <v>-10.14224768686044</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-8.795632208621932</v>
+        <v>-11.11702416380126</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-8.082004485820512</v>
+        <v>-11.80318464909666</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-9.123319247022664</v>
+        <v>-12.98521207827857</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-9.462309394982782</v>
+        <v>-13.55468304812812</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 15.54</t>
+          <t>X &lt; 15.84</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>660</v>
+        <v>792</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.26824379565894</v>
+        <v>2.517979332495457</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.024376088218226</v>
+        <v>1.514496739215829</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.6469630997932825</v>
+        <v>0.6385905161121315</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.3690212226797485</v>
+        <v>-0.4588621877465897</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.6588246684093306</v>
+        <v>0.4019433085177084</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.9973060060218657</v>
+        <v>0.4326142882531627</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.9867638899897031</v>
+        <v>-1.498831360343189</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.9619450317124745</v>
+        <v>-2.056277056277061</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2.89015481949474</v>
+        <v>-3.317237035481845</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-3.208525040985776</v>
+        <v>-3.987025904438553</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.237495701854158</v>
+        <v>-4.472366647409977</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.819275408332444</v>
+        <v>-4.622685975618644</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-5.39698292973403</v>
+        <v>-5.232527588018918</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-5.769576957695762</v>
+        <v>-6.112074780765155</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-5.215599043155116</v>
+        <v>-6.036653405074453</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-6.893939393939391</v>
+        <v>-6.611713022618424</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-7.482401985462317</v>
+        <v>-6.841856060606062</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-7.587242689283499</v>
+        <v>-6.848477539505033</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-8.583472520480392</v>
+        <v>-7.644116322460278</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-8.548141862027514</v>
+        <v>-7.808317756189176</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-8.787657726963239</v>
+        <v>-8.123237005044651</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-9.924109748978402</v>
+        <v>-8.955975284575693</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-11.01327140013271</v>
+        <v>-9.848704435660956</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-11.9981945624469</v>
+        <v>-11.02094444005143</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 16.15</t>
+          <t>X &lt; 16.44</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1009</v>
+        <v>1137</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.661432371206281</v>
+        <v>1.217198599400312</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.723087683857472</v>
+        <v>0.5820958068149054</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.8797168013279659</v>
+        <v>-0.5851857076640883</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.022533551117753</v>
+        <v>-2.139126368010771</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2681357184122959</v>
+        <v>-1.890208983634587</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.2161545509358191</v>
+        <v>-1.471037615398743</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.5557941329545315</v>
+        <v>-2.306116813297933</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.933113605457855</v>
+        <v>-2.173591937371469</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.684490645545132</v>
+        <v>-2.873438277322315</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.25919026608112</v>
+        <v>-3.447006959511633</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.579778790420683</v>
+        <v>-3.127337407643893</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.453176360370172</v>
+        <v>-3.88317940863184</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-4.279014343975547</v>
+        <v>-4.775186159675727</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.896525331423128</v>
+        <v>-5.855551766986203</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-5.059128490252448</v>
+        <v>-5.834100168220424</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-5.158497762561197</v>
+        <v>-5.536648392144826</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-5.29241489953867</v>
+        <v>-5.992331794195245</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-5.59547165886034</v>
+        <v>-5.949314404194148</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-6.073336472187748</v>
+        <v>-6.526408905280562</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-6.282922773220712</v>
+        <v>-6.751576198128348</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-6.131712746935015</v>
+        <v>-6.263611728532823</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-7.00042293034609</v>
+        <v>-7.218281726301655</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-8.311676661868006</v>
+        <v>-8.118006959580889</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-8.88304905384252</v>
+        <v>-8.543998196614425</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 16.77</t>
+          <t>X &lt; 17.05</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1373</v>
+        <v>1504</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.624221877127219</v>
+        <v>1.253693902638418</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.289445078777405</v>
+        <v>0.9780673566326072</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.07595232900449389</v>
+        <v>-0.04322766570604131</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.297257837190877</v>
+        <v>-0.9645772329353264</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.124696820994508</v>
+        <v>-1.00664554246746</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.2282171998935</v>
+        <v>-1.077047547495624</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-1.854922601285665</v>
+        <v>-1.374649528844287</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.987890763540555</v>
+        <v>-1.775101181433641</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.019025222874944</v>
+        <v>-1.676822994077696</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.283589410167785</v>
+        <v>-2.172313389593938</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.372637974251326</v>
+        <v>-1.929589236820277</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.796630660197508</v>
+        <v>-2.56640891934159</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.266197955811798</v>
+        <v>-2.784570184733916</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.140871603500216</v>
+        <v>-3.591839313509816</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-4.177455984663212</v>
+        <v>-3.839733911932299</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-4.269696969696966</v>
+        <v>-4.169854115242281</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-4.581780045539077</v>
+        <v>-4.237343784560942</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-4.719379792287327</v>
+        <v>-4.200986694803042</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-5.086154106920169</v>
+        <v>-4.415065012013613</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-5.40914078056467</v>
+        <v>-5.095014510971026</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-5.004855193250293</v>
+        <v>-4.665118586819851</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-5.517700426327274</v>
+        <v>-5.205706640690032</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-5.971557833291683</v>
+        <v>-5.626965772432925</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-6.120223298459614</v>
+        <v>-5.722615405020257</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 17.39</t>
+          <t>X &lt; 17.65</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1689</v>
+        <v>1795</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.8885646512739171</v>
+        <v>1.132840818644077</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.200846676453509</v>
+        <v>0.9720608225366547</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.5275335097754663</v>
+        <v>0.5184463431045216</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.3030675684908104</v>
+        <v>-0.4841147129991228</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.403563923391026</v>
+        <v>-0.6741428006444821</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.3930683255289367</v>
+        <v>-0.9831567703750395</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.4591346564781063</v>
+        <v>-1.030572613938752</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.7628974636242916</v>
+        <v>-1.360054755968626</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.7469917399358934</v>
+        <v>-1.422460541257827</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.048764895359895</v>
+        <v>-1.690428085452673</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.8000392278626194</v>
+        <v>-1.276693097754126</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.222077009247258</v>
+        <v>-1.90968155398113</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.57872964214112</v>
+        <v>-2.2739551527023</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.448393424248081</v>
+        <v>-3.211182198432127</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-2.482962947687156</v>
+        <v>-3.47444596481823</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-2.740062967335696</v>
+        <v>-3.492122777404226</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-2.899538501240293</v>
+        <v>-3.509699870514247</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-3.029967812859688</v>
+        <v>-3.833808360205104</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-3.371924754231259</v>
+        <v>-3.921894100238049</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-3.743587442088483</v>
+        <v>-4.288124158174561</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-3.483550939730343</v>
+        <v>-4.102214769339433</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-4.151463212566327</v>
+        <v>-4.758744209214406</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-4.587468073796529</v>
+        <v>-5.041444756463633</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-4.426473802449046</v>
+        <v>-5.229112471339235</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 18</t>
+          <t>X &lt; 18.25</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1940</v>
+        <v>2034</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.141761582220205</v>
+        <v>1.197285765812595</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.165041049855049</v>
+        <v>1.123917798053242</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.5965872182153547</v>
+        <v>0.7231956919581819</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.06521590608670635</v>
+        <v>-0.0854838080391005</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.263955258194656</v>
+        <v>0.1043989413191753</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2651910876772803</v>
+        <v>-0.1986988430599652</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.7302344007236385</v>
+        <v>-0.7716669813016779</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.081978529432767</v>
+        <v>-1.000598317671489</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.062896056752102</v>
+        <v>-0.8942147186088647</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.34594431570013</v>
+        <v>-1.22355131479209</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.145328514863799</v>
+        <v>-1.070369144288875</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.600161189218234</v>
+        <v>-1.417244463725531</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.976036679131539</v>
+        <v>-1.820102604689289</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.835098704942361</v>
+        <v>-2.627621638777768</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-3.053298067294818</v>
+        <v>-2.939603611989419</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-3.200426671649687</v>
+        <v>-3.134111344722925</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-3.151171947291409</v>
+        <v>-3.063627919320595</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-3.381294316668466</v>
+        <v>-3.463153713004736</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-3.548147577795689</v>
+        <v>-3.858900257940633</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-3.795933891487927</v>
+        <v>-4.206053702502153</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-3.588603818481211</v>
+        <v>-4.059402786571255</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-4.334207636665163</v>
+        <v>-4.647666261138973</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-4.729490780957967</v>
+        <v>-4.917637004593523</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-4.777013681472198</v>
+        <v>-4.954751537575341</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 18.62</t>
+          <t>X &lt; 18.86</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2153</v>
+        <v>2226</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.566526158457435</v>
+        <v>1.370668069577263</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.323915258725137</v>
+        <v>0.971252913053867</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.9918869931042806</v>
+        <v>0.3194781642894995</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.1406841257352696</v>
+        <v>-0.3373217612195276</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.3578890448930707</v>
+        <v>-0.1873572696470092</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.05422311002337921</v>
+        <v>-0.4957873754426174</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.6418399966787049</v>
+        <v>-0.9541513907858175</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.8479419301575035</v>
+        <v>-1.368083794488797</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.7804041765337644</v>
+        <v>-1.170772389017195</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.296511504606755</v>
+        <v>-1.584879439792097</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.134750801325318</v>
+        <v>-1.287661173736211</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.294956001795953</v>
+        <v>-1.583920302804721</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.74493565476623</v>
+        <v>-2.047966284324843</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.448011791470407</v>
+        <v>-2.718117317040246</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-2.617275381001654</v>
+        <v>-2.972454367721056</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-2.921802476406825</v>
+        <v>-3.281069976218888</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-2.751762254822587</v>
+        <v>-3.091296275563515</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-2.922905945280249</v>
+        <v>-3.154277474337228</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-3.37578863809771</v>
+        <v>-3.631839814666058</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-3.626533567679303</v>
+        <v>-3.840840290953857</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-3.586668240259471</v>
+        <v>-3.80039893388895</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-4.007636431112971</v>
+        <v>-4.299445897346125</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-4.217880161844541</v>
+        <v>-4.43517307354405</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-4.0821788549774</v>
+        <v>-4.258236498098199</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 19.23</t>
+          <t>X &lt; 19.46</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2349</v>
+        <v>2437</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.215571805486945</v>
+        <v>1.213470832865013</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.5429571692993065</v>
+        <v>0.9084977497276228</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.1184516337818238</v>
+        <v>0.2456250600872778</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.613288995464643</v>
+        <v>-0.2835745124589195</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.2916351282043053</v>
+        <v>-0.129429046958883</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.7809157721999114</v>
+        <v>-0.6015049077804946</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.299271894805393</v>
+        <v>-1.007364120709688</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.384778012684983</v>
+        <v>-1.24887568833757</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.235024839491658</v>
+        <v>-1.179835285518912</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.518711116724113</v>
+        <v>-1.422828236201717</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.093703845953911</v>
+        <v>-1.168511772126536</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.179022818905786</v>
+        <v>-1.299694938254405</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.642488836256881</v>
+        <v>-1.533775359854928</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.263083451202263</v>
+        <v>-2.208201557316947</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-2.388087284345637</v>
+        <v>-2.172170472725618</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-2.532912922178937</v>
+        <v>-2.323586357191154</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-2.345549590545403</v>
+        <v>-2.199689716312058</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.426076891175029</v>
+        <v>-2.391143246927193</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-2.738102936793048</v>
+        <v>-2.80859898694294</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-2.994625396908837</v>
+        <v>-3.103547811763349</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-3.003025692331207</v>
+        <v>-3.115371464392226</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-3.309903028433958</v>
+        <v>-3.372464904017349</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-3.564528653517627</v>
+        <v>-3.639048400328136</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-3.361056902320733</v>
+        <v>-3.368040762322146</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 19.85</t>
+          <t>X &lt; 20.06</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2517</v>
+        <v>2593</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.122932414127085</v>
+        <v>1.235660733663103</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.8491102355203068</v>
+        <v>0.7430151933557028</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.6541269367443547</v>
+        <v>0.4273155630621304</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.03672705514711794</v>
+        <v>-0.2586685174036703</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.03494265785010242</v>
+        <v>-0.2833166416733306</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.4174331010249333</v>
+        <v>-0.5646718631884795</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.8516319869019995</v>
+        <v>-0.9554666790474684</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.14713686317355</v>
+        <v>-1.239078625050261</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.8859899480312805</v>
+        <v>-0.9747942022414691</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.202011864974367</v>
+        <v>-1.289161181257377</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.945005583277073</v>
+        <v>-1.187212729101795</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.16173919207737</v>
+        <v>-1.36549797274926</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.2339123505242</v>
+        <v>-1.421956438738093</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.788212062203442</v>
+        <v>-1.840294356468412</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-1.988074390452304</v>
+        <v>-2.000907785931446</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-2.043954395439549</v>
+        <v>-1.994170818571028</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-1.91740174534322</v>
+        <v>-1.922275641025635</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1.920107604788136</v>
+        <v>-1.917725229953192</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-2.315719654789383</v>
+        <v>-2.297054480017366</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-2.661528805640557</v>
+        <v>-2.561198897210467</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-2.546676485982005</v>
+        <v>-2.4521190457911</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-2.758567867279311</v>
+        <v>-2.620948718335256</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-2.977673161992776</v>
+        <v>-2.818008112366321</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-2.872070388646918</v>
+        <v>-2.688438898714416</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 20.47</t>
+          <t>X &lt; 20.66</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2658</v>
+        <v>2726</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.7791454266650177</v>
+        <v>0.7680316931334872</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.5393014613525438</v>
+        <v>0.3235479500137686</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.3907616677799908</v>
+        <v>0.2170562804169975</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.2266716628544714</v>
+        <v>-0.2823887865827359</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.3174490889626611</v>
+        <v>-0.392062321553496</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.3337172308309704</v>
+        <v>-0.4335546901607117</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.7856877076051063</v>
+        <v>-0.7345350984166004</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.9306674088118143</v>
+        <v>-0.9096908440453362</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.5313819051662705</v>
+        <v>-0.6883855877686713</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.7591056978538546</v>
+        <v>-0.9165400237337025</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.6133508463352868</v>
+        <v>-0.8426964514747226</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.9081415983222314</v>
+        <v>-1.025630689374175</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.073209413379018</v>
+        <v>-1.243006878549359</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.42243234818234</v>
+        <v>-1.579911038075103</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.496404851519983</v>
+        <v>-1.656102004413363</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.517708972697712</v>
+        <v>-1.585684633385945</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-1.404739810239164</v>
+        <v>-1.558783845590924</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.450196552237372</v>
+        <v>-1.597394232052771</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.775702746131564</v>
+        <v>-1.764605357815661</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.792569610587492</v>
+        <v>-1.822081769953186</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-1.712224704517816</v>
+        <v>-1.74570203645068</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.878996967023511</v>
+        <v>-1.836392358541147</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-2.033990057180823</v>
+        <v>-1.938330064890543</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.937656905972453</v>
+        <v>-1.859354216465604</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 21.08</t>
+          <t>X &lt; 21.27</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2775</v>
+        <v>2822</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.8266296556888406</v>
+        <v>0.6928741506240215</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.7973471286186467</v>
+        <v>0.6066844389984709</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.7380022466264222</v>
+        <v>0.5318690631015457</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3313636637516382</v>
+        <v>0.2405136963583558</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.08736201033250524</v>
+        <v>0.05502107669578749</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.1155561769036169</v>
+        <v>0.09081602391969312</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.1705791196501991</v>
+        <v>-0.1210165799218501</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.4642413738511593</v>
+        <v>-0.3708178126782826</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.3306891955129885</v>
+        <v>-0.2934763407659204</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.5095018220629512</v>
+        <v>-0.4701932620769966</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.5734810937936317</v>
+        <v>-0.5658410742177367</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.7240606123641555</v>
+        <v>-0.7871356951142374</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.7857231677204979</v>
+        <v>-0.8936481476569398</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.129459445046834</v>
+        <v>-1.192112445548581</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-1.120118374398579</v>
+        <v>-1.147421988114317</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.9357408072823148</v>
+        <v>-0.9895015081807657</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.9048362490180821</v>
+        <v>-0.9314797631671965</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.9166533002475177</v>
+        <v>-0.9377078911116286</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-1.111268465542523</v>
+        <v>-1.091724701975266</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-1.083335467750089</v>
+        <v>-0.9981781435017894</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.992972210895438</v>
+        <v>-0.9433853915647248</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-1.119644498708325</v>
+        <v>-1.104085279711185</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-1.256263278571275</v>
+        <v>-1.229435229250406</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.202944767197103</v>
+        <v>-1.158410525426802</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 21.7</t>
+          <t>X &lt; 21.87</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2845</v>
+        <v>2897</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.7873258293853311</v>
+        <v>0.635455463670219</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.5761723909737171</v>
+        <v>0.5451423525952634</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.5528608772891133</v>
+        <v>0.4057099628066325</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.4528096515071383</v>
+        <v>0.3122618050092143</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.346271765074313</v>
+        <v>0.2273579487471551</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.3784383211395053</v>
+        <v>0.3006341091031715</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.08051264898495702</v>
+        <v>-0.02908932780088236</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.1777309933914779</v>
+        <v>-0.2802781381566248</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.1861921155320303</v>
+        <v>-0.3046246478694528</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.3095457411670139</v>
+        <v>-0.4285972343644033</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.3301860765599258</v>
+        <v>-0.4460207138475525</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.5538242569869993</v>
+        <v>-0.5999474178164945</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.6414443506660277</v>
+        <v>-0.6636267502047346</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.9120701912572926</v>
+        <v>-0.8919165420310691</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.8139086989279747</v>
+        <v>-0.8314701200563448</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.6544148105662231</v>
+        <v>-0.628603093725367</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.6975832511344748</v>
+        <v>-0.6779442148760353</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.6414607733156927</v>
+        <v>-0.6184629603688592</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.7557213243081478</v>
+        <v>-0.7283877061803068</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.6886590025446537</v>
+        <v>-0.6315866394373728</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.5786008662209952</v>
+        <v>-0.523794302153668</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.7390026186657934</v>
+        <v>-0.682136517463384</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.9356504967915029</v>
+        <v>-0.8668046928916411</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.9556957607213832</v>
+        <v>-0.9052465568354151</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 22.32</t>
+          <t>X &lt; 22.47</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2917</v>
+        <v>2962</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.5768399613979653</v>
+        <v>0.5277250306833707</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.7028381501440464</v>
+        <v>0.6350589294831224</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.6789370255725231</v>
+        <v>0.5384015666104176</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.563903530469716</v>
+        <v>0.434121979885461</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.4858414300309946</v>
+        <v>0.4457392010220786</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.5899961097852255</v>
+        <v>0.5880274805791075</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.3486764025058093</v>
+        <v>0.3489516052645456</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.05593923199518258</v>
+        <v>0.06313737005476128</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.1169971917500519</v>
+        <v>0.07582187067749402</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.05632752850167577</v>
+        <v>-0.0963041709748893</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.1037693599366776</v>
+        <v>-0.107287282330617</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.2604022796402745</v>
+        <v>-0.2637808517505178</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.4075393132412302</v>
+        <v>-0.41760235180206</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.6427017829900521</v>
+        <v>-0.6798929353935321</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.6314113010726317</v>
+        <v>-0.6356218848911368</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.4611499611499639</v>
+        <v>-0.3911743020797118</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.5406866100944114</v>
+        <v>-0.5763549736162545</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.4200524841186137</v>
+        <v>-0.4536668994113739</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.5261021017136684</v>
+        <v>-0.556429545693625</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.4902434669158424</v>
+        <v>-0.558135556580126</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.3619624177062875</v>
+        <v>-0.3976676521565778</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.4859459942678868</v>
+        <v>-0.5204050069001482</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.6708824662427446</v>
+        <v>-0.6618732483235163</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.6922139472444826</v>
+        <v>-0.6691994411085957</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 22.93</t>
+          <t>X &lt; 23.08</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2975</v>
+        <v>3008</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.5619547544799772</v>
+        <v>0.4989437106884793</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.6456640428395062</v>
+        <v>0.5679020797498922</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.5276120458628029</v>
+        <v>0.453635985664036</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.4677268928663523</v>
+        <v>0.3749381671898249</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.4848403361083697</v>
+        <v>0.3821717575271322</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.4903655692451423</v>
+        <v>0.3924739556475316</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.3055712258748287</v>
+        <v>0.1779363164244856</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.01310131946225823</v>
+        <v>-0.07515632515632831</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.1406549504454659</v>
+        <v>0.00539550895023666</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.02261540326942679</v>
+        <v>-0.1100697111355728</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.08549375467148934</v>
+        <v>-0.1829481325694147</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.2444917498527701</v>
+        <v>-0.374408498864355</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.3770921261861488</v>
+        <v>-0.5097867647481209</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.6454715823341104</v>
+        <v>-0.771893645355398</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.6136817468678402</v>
+        <v>-0.738728849609295</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.435167972043601</v>
+        <v>-0.5557957598046102</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.5492881509400291</v>
+        <v>-0.6734556384742945</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.5001354545747887</v>
+        <v>-0.6210573522308351</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.6335030268867357</v>
+        <v>-0.752221938863272</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.5611724702242782</v>
+        <v>-0.6510880889993373</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.4124007922704394</v>
+        <v>-0.5017716037718714</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.5690543240539867</v>
+        <v>-0.6570390786627485</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.7114629934855969</v>
+        <v>-0.8258991142514489</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.7002572056860146</v>
+        <v>-0.7691579582117498</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 23.55</t>
+          <t>X &lt; 23.68</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3017</v>
+        <v>3055</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.4709949918311835</v>
+        <v>0.4859632653916748</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.6147018532725141</v>
+        <v>0.5501079701471809</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4783912722352852</v>
+        <v>0.4509205787672883</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.4423855683121545</v>
+        <v>0.3968904606889794</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.3887324417953693</v>
+        <v>0.3347456323414946</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.3967368881545568</v>
+        <v>0.347275051433293</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.170823852963899</v>
+        <v>0.1238406724850947</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.08852237787439066</v>
+        <v>-0.1626254638302953</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.004823992370617702</v>
+        <v>-0.04880351460532495</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.1223348647263123</v>
+        <v>-0.1747091888960384</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.2251944717311432</v>
+        <v>-0.340105311758812</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.4519274487098102</v>
+        <v>-0.4677110552377926</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.5983359580355341</v>
+        <v>-0.6507509172011439</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.8991682121631328</v>
+        <v>-0.9126910577272653</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.7778975069737299</v>
+        <v>-0.7599964965637653</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.6597796143250676</v>
+        <v>-0.6365599245466242</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.7081114611717894</v>
+        <v>-0.6887178859133485</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.6611508078492534</v>
+        <v>-0.6391694966458701</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.7566269636546821</v>
+        <v>-0.7650313551400103</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.7158467159289899</v>
+        <v>-0.7602298156527141</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.543628025979892</v>
+        <v>-0.589264183302042</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.6992008387432307</v>
+        <v>-0.7760405099402377</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.8358510736070173</v>
+        <v>-0.9058729797404936</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.8258981813338053</v>
+        <v>-0.8525253886536461</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 24.17</t>
+          <t>X &lt; 24.28</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3067</v>
+        <v>3112</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.3073729512929475</v>
+        <v>0.2053796514747219</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.4756548191991214</v>
+        <v>0.391428146459937</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.3506057438504371</v>
+        <v>0.2711674827139987</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.4007758736479516</v>
+        <v>0.2392104930847054</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.3101336100617544</v>
+        <v>0.1092527491391948</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.2561832713821133</v>
+        <v>0.06044208700748044</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.1510736291707744</v>
+        <v>0.01825706949691863</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.2058927803634276</v>
+        <v>-0.300548414359163</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.2107652062959104</v>
+        <v>-0.2504724920623573</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.2835597109571495</v>
+        <v>-0.3246827027479426</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.3478853122437613</v>
+        <v>-0.3861444251877515</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.5105466790126272</v>
+        <v>-0.5164831018101381</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.5428864089708298</v>
+        <v>-0.5244234923067452</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.8424046824572002</v>
+        <v>-0.8501344291387056</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.7337848019130391</v>
+        <v>-0.7447079977814042</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.5428677014042904</v>
+        <v>-0.5812157421211452</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.5600226948331937</v>
+        <v>-0.6022396334295266</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.5480252628223354</v>
+        <v>-0.5880703891042955</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.6383967629046339</v>
+        <v>-0.675610280325742</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.6277625561060347</v>
+        <v>-0.6669425146855588</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.564876165419463</v>
+        <v>-0.6057669594847255</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.6865730920869026</v>
+        <v>-0.7583925205189388</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.8165189999904783</v>
+        <v>-0.8492576711965256</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.7753531716889768</v>
+        <v>-0.8319724580203172</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 24.78</t>
+          <t>X &lt; 24.88</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3119</v>
+        <v>3157</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.1147225873955335</v>
+        <v>0.1366185549082743</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.4337998386161885</v>
+        <v>0.379443787553889</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.1277583130725759</v>
+        <v>0.1801832845771401</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.1652156989416795</v>
+        <v>0.2032118100214504</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.006701138656737271</v>
+        <v>0.03969360747706929</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.02040276899749216</v>
+        <v>-0.0377189655446557</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.03171168205730623</v>
+        <v>-0.02759728041345966</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.2920885723823332</v>
+        <v>-0.3462202957948364</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.0728625605943094</v>
+        <v>-0.1374250441944369</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.09339673913547131</v>
+        <v>-0.1272359519333648</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.1520434784708868</v>
+        <v>-0.1838983684054227</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.3485089768505958</v>
+        <v>-0.3478055844555143</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.3350214620217571</v>
+        <v>-0.2767195072108279</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.6331697407516401</v>
+        <v>-0.5696757350506729</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.5691989811540239</v>
+        <v>-0.5385262076421427</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.4674584023800463</v>
+        <v>-0.4325038694756245</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.4865315730851947</v>
+        <v>-0.4546591866835215</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.4764548104956248</v>
+        <v>-0.4425354119378682</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.5617055550514465</v>
+        <v>-0.5573568875035022</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.5801332456039106</v>
+        <v>-0.5773558115290314</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.5593464269030619</v>
+        <v>-0.5251037740000228</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.6482366313878885</v>
+        <v>-0.6132891641117979</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.7393786262399402</v>
+        <v>-0.6993419059944301</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.73220021693988</v>
+        <v>-0.6845667256249328</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 25.4</t>
+          <t>X &lt; 25.49</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3173</v>
+        <v>3206</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.2077135874441254</v>
+        <v>0.2201481247850339</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.3279754622401256</v>
+        <v>0.3626436356898708</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.1279976152673825</v>
+        <v>0.0853747513996197</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.12144561291705</v>
+        <v>0.06802791601889169</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1027383299957663</v>
+        <v>-0.0972345162415138</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.1174770485919652</v>
+        <v>-0.1401104780199844</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.1508182264578224</v>
+        <v>-0.2043162433024719</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.4425459610434075</v>
+        <v>-0.4917490951010635</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.3518482912258492</v>
+        <v>-0.408414253172559</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.2597083519745382</v>
+        <v>-0.3484663963138246</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.2499935618096387</v>
+        <v>-0.3380599268963635</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.385090545576162</v>
+        <v>-0.5037307301873355</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.3594848331906988</v>
+        <v>-0.450757446441493</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.6563333053380731</v>
+        <v>-0.6808973346623333</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.5417708809548571</v>
+        <v>-0.5984455096348356</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.5259685823973825</v>
+        <v>-0.6099561885653841</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.4526707104480252</v>
+        <v>-0.5400424058512385</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.5703610703257596</v>
+        <v>-0.6235571022558304</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.7134570733724388</v>
+        <v>-0.7334100696487624</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.7284434615925619</v>
+        <v>-0.7498829407450032</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.6543091276196833</v>
+        <v>-0.7071471567329226</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.7115113237815507</v>
+        <v>-0.7640183083294403</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.7334409596217455</v>
+        <v>-0.7827171540515891</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.6961574882698898</v>
+        <v>-0.7394803922118314</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 26.02</t>
+          <t>X &lt; 26.09</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3203</v>
+        <v>3232</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.2649185406287913</v>
+        <v>0.2822580645161281</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.4119729874430291</v>
+        <v>0.3602064484780954</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.2315183295098038</v>
+        <v>0.1673471882748956</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.1563692003215849</v>
+        <v>0.08392733105768713</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.02426679921458685</v>
+        <v>-0.0206927723773731</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.08169261100842107</v>
+        <v>-0.1542543986155138</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.1840159133286789</v>
+        <v>-0.2550920279612043</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.4445624453643688</v>
+        <v>-0.5118923222371521</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.416474573906477</v>
+        <v>-0.4590042611726872</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.3945914872325034</v>
+        <v>-0.4675427176725577</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.3513582075077011</v>
+        <v>-0.4242584467594099</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.4878271779728678</v>
+        <v>-0.4983663303372268</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.4729762166793989</v>
+        <v>-0.4855901283155006</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.5824111822946918</v>
+        <v>-0.6233503993819198</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.5373092963722073</v>
+        <v>-0.547014654096607</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.5472429055424968</v>
+        <v>-0.5539127981515364</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.4758882499766202</v>
+        <v>-0.5162505145621097</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.5311410055719747</v>
+        <v>-0.569271020953245</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.7020397387982342</v>
+        <v>-0.7073950785101175</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.7463163099681012</v>
+        <v>-0.7529057873037814</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.6779581107134049</v>
+        <v>-0.6841631131114028</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.7353421982763777</v>
+        <v>-0.7411742126317691</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.754503950354021</v>
+        <v>-0.7577562904288584</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.7182865216896488</v>
+        <v>-0.7161639620036269</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 26.63</t>
+          <t>X &lt; 26.69</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3237</v>
+        <v>3267</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.1935087147888908</v>
+        <v>0.1959750955976105</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.4275672511516362</v>
+        <v>0.3920684428744892</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.2032999489478158</v>
+        <v>0.2183295119095234</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.2442964799839658</v>
+        <v>0.2511970293098855</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1100941196787844</v>
+        <v>0.1143749899086117</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.02350114381754054</v>
+        <v>-0.01605044123348165</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.07134044844456611</v>
+        <v>-0.06334371900902624</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.3320369748139456</v>
+        <v>-0.3205986148416855</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.273024102733018</v>
+        <v>-0.2668520152613567</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.3824482161393377</v>
+        <v>-0.3751682236994398</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.3675656319240872</v>
+        <v>-0.3903883276267806</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.4131924177619197</v>
+        <v>-0.4361499844166019</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.3794429984009895</v>
+        <v>-0.435395190215381</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.5824111822946918</v>
+        <v>-0.6048357748993638</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.3906396525764961</v>
+        <v>-0.4144977829188292</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.4250128402670796</v>
+        <v>-0.445817425425119</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.3865980770813451</v>
+        <v>-0.4096352575850162</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.4115075394502909</v>
+        <v>-0.4329242059865379</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.5474678095836367</v>
+        <v>-0.6283597345765415</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.6201267525869127</v>
+        <v>-0.7016349081428217</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.5581403307791817</v>
+        <v>-0.6396858976403337</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.6156812216551586</v>
+        <v>-0.6968777321162491</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.6008394836859736</v>
+        <v>-0.680059603001439</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.534858701520676</v>
+        <v>-0.6100169836694249</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 27.25</t>
+          <t>X &lt; 27.3</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3266</v>
+        <v>3292</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.114093598030486</v>
+        <v>0.1225316429301273</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.4343517573179696</v>
+        <v>0.4057935333490832</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.2602237869815696</v>
+        <v>0.2239018241822706</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.2641516502983521</v>
+        <v>0.2218580581910459</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.1281757131028414</v>
+        <v>0.08397961846100088</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.002583264269354402</v>
+        <v>-0.04428461009587892</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.02635258842700949</v>
+        <v>-0.06701546796519153</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.2262517183226365</v>
+        <v>-0.23394246489773</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.289275560584386</v>
+        <v>-0.3005644126707239</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.3435952553242743</v>
+        <v>-0.3535954107539823</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.3569057215386522</v>
+        <v>-0.3666345916022777</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.4350980644235705</v>
+        <v>-0.4444019244532385</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.4115934844727462</v>
+        <v>-0.4218183154567754</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.4926316807504847</v>
+        <v>-0.5009973192939938</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.3388930519453055</v>
+        <v>-0.3475295093465007</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.3371374095259227</v>
+        <v>-0.3440362549416633</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.2696697131516785</v>
+        <v>-0.2785724209356388</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.2952518765102923</v>
+        <v>-0.302652399077104</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.4586288529892144</v>
+        <v>-0.4646097002784941</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.5289592098173372</v>
+        <v>-0.5356517759989217</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.5334886269697279</v>
+        <v>-0.5391257866390475</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.6523839227850132</v>
+        <v>-0.6874981636395532</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.6964669924192179</v>
+        <v>-0.6993226739196459</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.7236301801054168</v>
+        <v>-0.7221791443237962</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 27.86</t>
+          <t>X &lt; 27.9</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3292</v>
+        <v>3318</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.1449749076841726</v>
+        <v>0.1239401680282839</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.3695782608193028</v>
+        <v>0.3432029631316382</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.2458801300414422</v>
+        <v>0.2128370243209048</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.2743692033193597</v>
+        <v>0.2361496441735653</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.1368272859468362</v>
+        <v>0.09720276553922247</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.0387781290649869</v>
+        <v>0.001141284837714807</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.05129862995508461</v>
+        <v>-0.05758228790971032</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.1006720845870461</v>
+        <v>-0.1056065843108485</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.1325973885172829</v>
+        <v>-0.1406693787161615</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.2227691151209541</v>
+        <v>-0.2294622729253462</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.2035251338442521</v>
+        <v>-0.2102164756230636</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.2832492875605723</v>
+        <v>-0.2894891424218144</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.2687248723206537</v>
+        <v>-0.2757428587799922</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.3508224838231868</v>
+        <v>-0.3561987123890873</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.2034356032425038</v>
+        <v>-0.2092176407586166</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.2272727272727266</v>
+        <v>-0.2313884297261879</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.1613588778172073</v>
+        <v>-0.1672149122807127</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.157211632812178</v>
+        <v>-0.1620282086513782</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.3478864504994092</v>
+        <v>-0.3510912781562681</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.4161545128071538</v>
+        <v>-0.4198636789933659</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.4248950470533686</v>
+        <v>-0.4277181306639903</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.5130593543214488</v>
+        <v>-0.5152426570960813</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.5242174841125049</v>
+        <v>-0.5250140822929836</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.6124660746527937</v>
+        <v>-0.6091867181671233</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 28.48</t>
+          <t>X &lt; 28.5</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3305</v>
+        <v>3330</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.05506634810649302</v>
+        <v>0.05116987194904965</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.2473998333339367</v>
+        <v>0.2389127369015185</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.2387923969743611</v>
+        <v>0.2238567866962242</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.2944556513234389</v>
+        <v>0.2748178966797568</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.1260602006268243</v>
+        <v>0.1055334047623262</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.08930939835628493</v>
+        <v>0.07011836124110715</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.02668182544276476</v>
+        <v>0.00877533101014194</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.05367534295497478</v>
+        <v>-0.07003689012057634</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.05517855078352341</v>
+        <v>-0.0746089610152012</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.1480011518990665</v>
+        <v>-0.1659201096485532</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.1277362629807826</v>
+        <v>-0.1457471772068999</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.2082175886523814</v>
+        <v>-0.2257090247817359</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.1981307164065385</v>
+        <v>-0.2159974255743506</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.3109179696250095</v>
+        <v>-0.3269783070459269</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.1666789429374873</v>
+        <v>-0.1829683061063321</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.1880791006960649</v>
+        <v>-0.2030336585765724</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.153131014887002</v>
+        <v>-0.1694230096893392</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.1494092049383866</v>
+        <v>-0.1647336255452956</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.3082733993598126</v>
+        <v>-0.3223605336879913</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.3453066193010699</v>
+        <v>-0.3601104279578493</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.3561235215475378</v>
+        <v>-0.3699616775118955</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.4442186089723563</v>
+        <v>-0.4574243490499725</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.4239847037679709</v>
+        <v>-0.4362445015858896</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.4818969417619812</v>
+        <v>-0.4906414097483918</v>
       </c>
     </row>
     <row r="32">
@@ -7960,79 +7960,79 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3316</v>
+        <v>3342</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.117763248951988</v>
+        <v>0.09778931943769464</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.3383365435807164</v>
+        <v>0.3434521674578264</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.2051763379585765</v>
+        <v>0.175327196024547</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.318247144444733</v>
+        <v>0.2834659118093441</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.1493067001207535</v>
+        <v>0.1138045571239701</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.1133009888434913</v>
+        <v>0.1088408394797185</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.04833962036133954</v>
+        <v>0.0448880607206803</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.03266422848209061</v>
+        <v>-0.03472141649628924</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.03401916089735835</v>
+        <v>-0.03880932675922821</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.1290819615426955</v>
+        <v>-0.1326297377658605</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.1079727765967675</v>
+        <v>-0.1115453193755371</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.1891034969105405</v>
+        <v>-0.1922004404819475</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.1827577200173778</v>
+        <v>-0.1865036745628501</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.3259646469758195</v>
+        <v>-0.3278000525763431</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.1843846435196639</v>
+        <v>-0.1867488085270708</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.2037523246909529</v>
+        <v>-0.2047327723546033</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.1994612327653229</v>
+        <v>-0.2014749427689821</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.1961128478225334</v>
+        <v>-0.1972882270254033</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.3537498192129789</v>
+        <v>-0.3535908103930865</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.3900549690008646</v>
+        <v>-0.3904450663499546</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.3725180810311812</v>
+        <v>-0.3724103528727127</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.4605775006360275</v>
+        <v>-0.4598296173773946</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.4395054012838102</v>
+        <v>-0.4378519684220095</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.4673249495507505</v>
+        <v>-0.4627140209592469</v>
       </c>
     </row>
     <row r="33">
@@ -8042,243 +8042,243 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3325</v>
+        <v>3349</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.06285659027174262</v>
+        <v>0.07540411411953585</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.2520426552932165</v>
+        <v>0.2607099840941629</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.08546044624042537</v>
+        <v>0.09030349156398643</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.19627297490144</v>
+        <v>0.1969614088606164</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.003057309262125329</v>
+        <v>-0.002636935730002676</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.05123144044386407</v>
+        <v>0.05210140774028815</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.01565241618522606</v>
+        <v>-0.01338869842994228</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.09720665724647404</v>
+        <v>-0.09348419452432211</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.0984654709191588</v>
+        <v>-0.09731486490568386</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1654255827919755</v>
+        <v>-0.1628789937617583</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1736033329887476</v>
+        <v>-0.1710248535042354</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.2253196687369154</v>
+        <v>-0.2223526813549768</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.1920559622171254</v>
+        <v>-0.1892375447288686</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.2755058114507065</v>
+        <v>-0.2712160595849156</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.1360694945193828</v>
+        <v>-0.1318639982004726</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.153765376537649</v>
+        <v>-0.1486236841939714</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.1498325940694016</v>
+        <v>-0.1455726062773195</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.1467616252659667</v>
+        <v>-0.1416552179286157</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.3033742403821122</v>
+        <v>-0.2971674057439131</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.3390609659535286</v>
+        <v>-0.3334799055684314</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.3230234029539147</v>
+        <v>-0.3166508571697193</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.4410920152843829</v>
+        <v>-0.4338697168121186</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.4493945073321868</v>
+        <v>-0.4412719013627466</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.447271800997818</v>
+        <v>-0.4365622484730594</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 30.33</t>
+          <t>X &lt; 30.31</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3336</v>
+        <v>3361</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.006071612379287217</v>
+        <v>0.003472562669550427</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1041854985815291</v>
+        <v>0.09854890736495747</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.06660691672578878</v>
+        <v>-0.07575279876341767</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.01166285287916935</v>
+        <v>-0.001202180397143593</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.1583636077953301</v>
+        <v>-0.1715430341994022</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.07387087910851164</v>
+        <v>-0.08689719234147475</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1132810749619964</v>
+        <v>-0.1254169318665959</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.1955097963034831</v>
+        <v>-0.2063445060187803</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.1966576273404286</v>
+        <v>-0.2097402668476391</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.2659651133512142</v>
+        <v>-0.2779349953476498</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.243386198338861</v>
+        <v>-0.2554793392363663</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.2958693042811831</v>
+        <v>-0.3076335839282436</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.2963048009710434</v>
+        <v>-0.308285163776489</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.380238262917743</v>
+        <v>-0.3908908261193176</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.2135607227311382</v>
+        <v>-0.2248259315259205</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.2292663476873997</v>
+        <v>-0.2395542127926618</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.1958964877692679</v>
+        <v>-0.207219912905785</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.1931944873358447</v>
+        <v>-0.2038083948358889</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.3485945579759644</v>
+        <v>-0.3580200657757828</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.3835619309805125</v>
+        <v>-0.3934559133926996</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.3693778935890606</v>
+        <v>-0.378728903818363</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.4873212528729525</v>
+        <v>-0.4958161553710667</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.4947054590315645</v>
+        <v>-0.5023407392080301</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.492853380846725</v>
+        <v>-0.4982449668907805</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 30.95</t>
+          <t>X &lt; 30.91</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3355</v>
+        <v>3379</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.02924261372799464</v>
+        <v>-0.04468434127932142</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.06642524427388707</v>
+        <v>0.07797628622964226</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.08188940631040253</v>
+        <v>-0.07263943041193244</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.06733772099624957</v>
+        <v>-0.06046069711209867</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1494058286178443</v>
+        <v>-0.172518198845502</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.09398041286609526</v>
+        <v>-0.08748960615157841</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1078681712363192</v>
+        <v>-0.1005731599648456</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.2208646940732493</v>
+        <v>-0.2121360884247565</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1921060828703318</v>
+        <v>-0.185373318762494</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.2653803258018783</v>
+        <v>-0.2574221748348293</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2116913399452756</v>
+        <v>-0.2041538591500114</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.2654418544988957</v>
+        <v>-0.2574842681875111</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.2424968928950477</v>
+        <v>-0.2345388510921254</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.3271887367042723</v>
+        <v>-0.3180024552676315</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.194880562270157</v>
+        <v>-0.1859384634504195</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.2071337820668759</v>
+        <v>-0.1975939756384477</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.1449585445090662</v>
+        <v>-0.1364380291395975</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.1428493359344785</v>
+        <v>-0.1337303631625844</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.2663729533808237</v>
+        <v>-0.2564094666683161</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.3000611742326242</v>
+        <v>-0.2904849797102216</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.2890023224114699</v>
+        <v>-0.2788260116094108</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.4066834755199622</v>
+        <v>-0.3956605130807986</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.4124479089635713</v>
+        <v>-0.4008232570105363</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.4110112539521111</v>
+        <v>-0.3975829769444772</v>
       </c>
     </row>
   </sheetData>
